--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\abyss-olaf-update\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\yj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA27ABE9-327A-4F20-9F31-5ADCCE703802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F04ED2C4-43E2-494B-A9BE-7F4DA6C998D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{D70E44A0-0095-462D-9E7F-F8AE19674C27}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{22344033-CCBA-419E-8156-8B9E3B59CE79}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'감정 증강'!$A$1:$G$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">공용!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">올라프!$A$1:$T$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">유진!$A$1:$M$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">유진!$A$1:$M$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'유진 무기'!$A$1:$O$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">적!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">히후미!$A$1:$T$46</definedName>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3488" uniqueCount="983">
   <si>
     <t>Project Abyss — 전투 콘텐츠 명세 (2026-09-25)</t>
   </si>
@@ -1074,7 +1074,7 @@
     <t>표식 (낙점)</t>
   </si>
   <si>
-    <t>이긴 교환마다 적립 · 상한 44에서 소비하고 발화: 바 푸시 50</t>
+    <t>낙점 = 실제 교환에서 이긴 굴림마다 적립(일방 공격 제외) · 상한 44에서 소비하고 발화: 바 푸시 50</t>
   </si>
   <si>
     <t>… 발화: 봉인 1턴 (두 곳 동시 가능)</t>
@@ -1083,18 +1083,36 @@
     <t>… 발화: 확정 체력 피해 (미정), 파괴 권한 없음</t>
   </si>
   <si>
-    <t>대상 수 제한 없음 · 무기를 바꿔도 유지 · 초과분 이월 없음</t>
+    <t>카드 효과 표식은 낙점과 별도 · 대상 수 제한 없음 · 무기를 바꿔도 유지 · 초과분 이월 없음(예외: 성장 집행 3단계)</t>
   </si>
   <si>
     <t>지정</t>
   </si>
   <si>
-    <t>사용시(목표 지정)</t>
+    <t>사용시(목표 지정 1굴림)</t>
   </si>
   <si>
     <t>수치형 N·T. 지정된 부위에 표식이 실제로 쌓일 때마다 현재 지정 총합 N만큼 추가</t>
   </si>
   <si>
+    <t>은신</t>
+  </si>
+  <si>
+    <t>은신 N — 그 부위는 적이 조준 못 함 · 그 부위가 스킬 행동 하나를 마칠 때마다 −1(굴림 수 무관) · 턴 종료로 안 줄어듦 · 다음 턴 부여는 이번 턴 조준을 취소하지 않음 · 한 스킬의 굴림별 부여는 누적</t>
+  </si>
+  <si>
+    <t>재부여 처리 (미정)</t>
+  </si>
+  <si>
+    <t>덫 (폭발 덫 · 공명 덫)</t>
+  </si>
+  <si>
+    <t>부위 스택. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발 = 스택 비례 확정 피해 (미정) / 공명 = 현재 무기의 발화 효과 강화 (미정)</t>
+  </si>
+  <si>
+    <t>덫은 표식을 주지 않음 · 승리 → 덫 설치 → 낙점 → 발화 → 방금 단 덫도 발동</t>
+  </si>
+  <si>
     <t>코인 축</t>
   </si>
   <si>
@@ -1116,12 +1134,24 @@
     <t>살수의 감</t>
   </si>
   <si>
-    <t>획득: 매 턴 +1 (유비무환) · 숨 고르기 · 흔들어놓다 · 파괴 · 처치. 상한 없음 · 전투 종료 초기화. 사용: ① 슬롯 배치 때 지정 → 그 슬롯의 지는 교환 자동 재굴림 ② 잔혹한 마무리 추가타 ③ 패 보기(결투 한정 — 상대 결과를 보고 스택 1로 그 굴림을 접는다)</t>
+    <t>획득: 매 턴 +1 (유비무환) · 카드 효과 · 파괴 · 처치. 상한 없음 · 전투 종료 초기화. 사용: ① 슬롯 배치 때 지정 → 그 슬롯의 지는 교환 자동 재굴림 ② 카드 효과(잔혹한 마무리 · 믿는 구석 · 때를 앞당기다 · 끝장을 보다 · 숨을 죽이다 · 칼을 갈다) ③ 패 보기(결투 한정)</t>
   </si>
   <si>
     <t>⚠ ③은 결투 도중 선택 UI</t>
   </si>
   <si>
+    <t>카드 공통</t>
+  </si>
+  <si>
+    <t>트리거 원칙</t>
+  </si>
+  <si>
+    <t>전투 시작시 = 스킬 전체 구조만 · 사용시 = 그 굴림 발생 시 판정 전(일방 공격 포함) · 승리시/패배시 = 실제 교환만 · 같은 턴에 바뀌는 자원은 하드 게이트 금지(효과 시점에 검사, 모자라면 추가 효과만 실패)</t>
+  </si>
+  <si>
+    <t>굴림 수 = 백우 3 / 적설 2 / 낙일 1 · 효과는 되도록 굴림마다 배치</t>
+  </si>
+  <si>
     <t>무기 효과</t>
   </si>
   <si>
@@ -1134,109 +1164,127 @@
     <t>처형</t>
   </si>
   <si>
-    <t>앞면(크리)이 이미 약화된 부위를 치면 파괴</t>
+    <t>앞면(크리) 타격의 피해가 부위의 남은 체력을 0 이하로 만들 수 있으면 한 타격 안에서 정상 → 약화 → 파괴</t>
+  </si>
+  <si>
+    <t>미리 약화될 필요 없음</t>
   </si>
   <si>
     <t>뒷조사</t>
   </si>
   <si>
-    <t>승리시 표식 +6</t>
-  </si>
-  <si>
-    <t>승리시 표식 +12</t>
-  </si>
-  <si>
-    <t>승리시 표식 +8</t>
+    <t>고유 효과 없음 · 이긴 굴림에 낙점만</t>
+  </si>
+  <si>
+    <t>유진 기준 평타</t>
   </si>
   <si>
     <t>숨 고르기</t>
   </si>
   <si>
-    <t>표식 없음 · 승리시 살수의 감 +1</t>
+    <t>승리시(각 굴림)</t>
+  </si>
+  <si>
+    <t>낙점 없음 · 살수의 감 +(미정)</t>
   </si>
   <si>
     <t>장부 정리</t>
   </si>
   <si>
-    <t>표식 20 이상일 때만 사용 가능 · 사용시 표식 20 소모 → 빛 +1</t>
-  </si>
-  <si>
-    <t>미구현(사용 조건 게이트 필요) · 09-15 브레인스토밍</t>
-  </si>
-  <si>
-    <t>한 발 물러서다</t>
-  </si>
-  <si>
-    <t>자신에게 방어도 +10</t>
-  </si>
-  <si>
-    <t>09-15 브레인스토밍</t>
+    <t>각 굴림 사용시 대상 표식 (미정) 소비 시도 → 성공하면 빛 +(미정). 낙점으로 다시 쌓이면 다음 굴림에서 재시도</t>
+  </si>
+  <si>
+    <t>1굴림 사용시 표식 (미정) 소비 시도 → 빛 +(미정) · 2굴림 승리시 1굴림 정산이 성공했으면 소비한 표식 중 (미정) 되돌림</t>
+  </si>
+  <si>
+    <t>1굴림 사용시 표식 (미정)을 한 번에 소비 시도 → 빛 +(미정)</t>
+  </si>
+  <si>
+    <t>무기별 분기</t>
+  </si>
+  <si>
+    <t>사용 조건 없음 — 표식이 모자라면 그 굴림의 환전만 실패</t>
   </si>
   <si>
     <t>정조준</t>
   </si>
   <si>
-    <t>크리(앞면)면 표식 +6 추가</t>
-  </si>
-  <si>
-    <t>크리(앞면)면 골절(다음 턴)</t>
-  </si>
-  <si>
-    <t>크리(앞면)면 확정 추가 피해 +8</t>
-  </si>
-  <si>
-    <t>무기별 분기</t>
-  </si>
-  <si>
-    <t>미구현(크리 조건 효과 코드 신설 필요) · 09-15 브레인스토밍</t>
+    <t>승리 + 앞면(크리)이면 대상 표식 +(미정)</t>
+  </si>
+  <si>
+    <t>승리 + 앞면이면 다음 턴 골절 (미정)</t>
+  </si>
+  <si>
+    <t>승리 + 앞면이면 확정 추가 피해 (미정)</t>
+  </si>
+  <si>
+    <t>낙점은 별도</t>
   </si>
   <si>
     <t>확인 사살</t>
   </si>
   <si>
-    <t>조준 부위가 「지정」 상태면 바 +10 추가 획득</t>
-  </si>
-  <si>
-    <t>미구현(지정 조건 효과 코드 신설 필요) · 09-15 브레인스토밍, 지정 연계 카드 추가 예정</t>
+    <t>조준 부위가 지정 상태면 기세 바 +(미정)</t>
+  </si>
+  <si>
+    <t>카드 사용은 제한하지 않음</t>
   </si>
   <si>
     <t>손에 익히다</t>
   </si>
   <si>
-    <t>지난 턴 환형 완료(새 무기 활성화 첫 턴)여야 사용 가능 · 사용시 살수의 감 +1</t>
-  </si>
-  <si>
-    <t>미구현(사용 조건 게이트 필요) · 코더 WeaponChanged 이벤트 재사용 가능 · 09-15 브레인스토밍</t>
+    <t>사용시(각 굴림)</t>
+  </si>
+  <si>
+    <t>지난 턴 환형 완료(새 무기 첫 턴)여야 사용 가능 · 살수의 감 +(미정) (최대 3회)</t>
+  </si>
+  <si>
+    <t>… (최대 2회)</t>
+  </si>
+  <si>
+    <t>… (최대 1회)</t>
+  </si>
+  <si>
+    <t>하드 게이트가 지난 턴 확정 사실이라 허용</t>
   </si>
   <si>
     <t>믿는 구석</t>
   </si>
   <si>
-    <t>살수의 감 3 소모 → 코인 3개 전부 확정 크리</t>
-  </si>
-  <si>
-    <t>살수의 감 2 소모 → 코인 2개 전부 확정 크리</t>
-  </si>
-  <si>
-    <t>살수의 감 2 소모 → 코인 1개 확정 크리</t>
-  </si>
-  <si>
-    <t>미구현(전체 굴림 강제 크리 처리 신설 필요) · 09-15 브레인스토밍</t>
+    <t>살수의 감 (미정) 소비 시도 → 성공하면 이 스킬의 모든 굴림을 앞면(크리) 취급</t>
+  </si>
+  <si>
+    <t>확정 크리는 자동 승리가 아님 · 실패해도 스킬은 정상 진행</t>
   </si>
   <si>
     <t>현상수배</t>
   </si>
   <si>
-    <t>모든 적에게 쇠약(다음 턴)</t>
-  </si>
-  <si>
-    <t>모든 적에게 골절(다음 턴)</t>
-  </si>
-  <si>
-    <t>모든 적에게 균열(다음 턴)</t>
-  </si>
-  <si>
-    <t>미구현(전체 적 대상 처리 필요) · 09-15 브레인스토밍</t>
+    <t>다음 턴 모든 적에게 쇠약 (미정)</t>
+  </si>
+  <si>
+    <t>… 골절 (미정)</t>
+  </si>
+  <si>
+    <t>… 균열 (미정)</t>
+  </si>
+  <si>
+    <t>굴림마다 반복 발동</t>
+  </si>
+  <si>
+    <t>은신 부여 평타 (가칭)</t>
+  </si>
+  <si>
+    <t>이 카드를 쓰는 자기 부위에 다음 턴 은신 (미정) 누적</t>
+  </si>
+  <si>
+    <t>은신 보상 평타 (가칭)</t>
+  </si>
+  <si>
+    <t>스킬 시작 시 사용 부위가 은신이면 대상에게 표식 +(미정)</t>
+  </si>
+  <si>
+    <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음(행동이 끝나면 −1)</t>
   </si>
   <si>
     <t>A</t>
@@ -1245,16 +1293,13 @@
     <t>의뢰 대상</t>
   </si>
   <si>
-    <t>승리시 표식 +12 · 바 +15</t>
-  </si>
-  <si>
-    <t>표식 +24 · 바 +15</t>
-  </si>
-  <si>
-    <t>표식 +16 · 바 +15</t>
-  </si>
-  <si>
-    <t>바 +15는 v5 스케일 재확인</t>
+    <t>기세 바 +(미정)</t>
+  </si>
+  <si>
+    <t>대상에게 골절 (미정)</t>
+  </si>
+  <si>
+    <t>이 스킬로 처형에 성공해 부위를 파괴하면 살수의 감 +(미정)</t>
   </si>
   <si>
     <t>B</t>
@@ -1263,10 +1308,10 @@
     <t>잔혹한 마무리</t>
   </si>
   <si>
-    <t>승리시 살수의 감 1 소비 → 코인, 앞면이면 무저항 추가타 (상한 강화 표)</t>
-  </si>
-  <si>
-    <t>자동 시전</t>
+    <t>살수의 감 1 소비 시도 → 성공하면 무저항 추가타 (상한 강화 표)</t>
+  </si>
+  <si>
+    <t>추가타는 승리시를 다시 일으키지 않고 추가타를 다시 만들지 않음</t>
   </si>
   <si>
     <t>C</t>
@@ -1275,286 +1320,250 @@
     <t>목표 지정</t>
   </si>
   <si>
-    <t>상대 부위에 「지정」(3턴)</t>
+    <t>사용시(1굴림)</t>
+  </si>
+  <si>
+    <t>조준 부위에 지정 (미정)만큼 (미정)턴</t>
+  </si>
+  <si>
+    <t>첫 굴림 전 적용 → 1굴림 낙점부터 지정 보너스</t>
   </si>
   <si>
     <t>D</t>
   </si>
   <si>
-    <t>그림자 속으로</t>
-  </si>
-  <si>
-    <t>사용시 / 패배시</t>
-  </si>
-  <si>
-    <t>자신에게 방어도 +15. 패배시 살수의 감 +1</t>
-  </si>
-  <si>
-    <t>09-15: 패배시 라이더 추가</t>
+    <t>숨통을 끊다</t>
+  </si>
+  <si>
+    <t>피해 처리 후(각 굴림)</t>
+  </si>
+  <si>
+    <t>그 굴림이 대상 부위를 약화 · 파괴하면 그 대상에게 표식 +(미정)</t>
+  </si>
+  <si>
+    <t>한 타격의 약화+파괴는 1회 · 처형 포함 · 일방 공격 포함</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>흔들어놓다</t>
-  </si>
-  <si>
-    <t>승리시(결투 대 결투)</t>
+    <t>소문을 내다</t>
+  </si>
+  <si>
+    <t>그 굴림이 대상 부위를 약화 · 파괴하면 모든 적에게 표식 +(미정)</t>
+  </si>
+  <si>
+    <t>숨통을 끊다의 전역판</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>퇴로 차단</t>
+  </si>
+  <si>
+    <t>승리시(굴림 위치별)</t>
+  </si>
+  <si>
+    <t>짓누름이면 1굴림: 상대 다음 턴 빛 최대치 −(미정) · 2굴림: 표식 (미정) 소비 → 빛 +(미정) · 3굴림: 기세 바 +(미정)</t>
+  </si>
+  <si>
+    <t>… 1~2굴림 효과만</t>
+  </si>
+  <si>
+    <t>… 1굴림 효과만</t>
+  </si>
+  <si>
+    <t>굴림 위치별</t>
+  </si>
+  <si>
+    <t>짓누름은 효과 발동 시점에 확인</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>빌려 쓰다</t>
+  </si>
+  <si>
+    <t>안 든 무기 2개 중 무작위 1 → 이 스킬만 그 무기의 전투 프로필 전체(굴림 수 · 앞면 확률 · 크리값 · 타격 타입 · 처형 권한 · 낙점 표식량 · 고유 규칙)</t>
+  </si>
+  <si>
+    <t>환형 아님 · 장착 무기 불변 · 환형 완료 · 손에 익히다 조건을 채우지 않음</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>덫을 놓다</t>
+  </si>
+  <si>
+    <t>대상 부위에 폭발 덫 (미정)스택</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>시한을 정하다</t>
+  </si>
+  <si>
+    <t>대상 부위에 공명 덫 (미정)스택</t>
+  </si>
+  <si>
+    <t>카드명은 작명 단계에서 바뀔 수 있음 · 구 「시한」 상태 폐기</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>마침표를 찍다</t>
+  </si>
+  <si>
+    <t>그 굴림으로 적을 처치하면 살수의 감 +(미정)</t>
+  </si>
+  <si>
+    <t>그 굴림으로 적을 흐트러뜨리면 살수의 감 +(미정)</t>
+  </si>
+  <si>
+    <t>그 굴림으로 처형에 성공하면 살수의 감 +(미정)</t>
+  </si>
+  <si>
+    <t>한 굴림의 중복 조건은 1회</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>때를 앞당기다</t>
+  </si>
+  <si>
+    <t>살수의 감 (미정) 소비 시도 → 대상 표식 +(미정), 44에 닿으면 즉시 발화</t>
+  </si>
+  <si>
+    <t>덫이 걸린 부위면 덫도 함께 발동</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>끝장을 보다</t>
+  </si>
+  <si>
+    <t>4(쓸 때마다 −1, 최소 1, 누적)</t>
+  </si>
+  <si>
+    <t>전투 시작시 / 적중 시</t>
+  </si>
+  <si>
+    <t>살수의 감 전부 소비 → 소비량 비례 마무리 피해 풀 (미정) → 적중마다 확정 추가 피해로 나눠 씀 (3굴림)</t>
+  </si>
+  <si>
+    <t>… (2굴림)</t>
+  </si>
+  <si>
+    <t>… (1굴림에 집중)</t>
+  </si>
+  <si>
+    <t>풀은 하나의 총량(소비 × 굴림 수로 불어나지 않음) · 남으면 소멸 · 기본위력 빛 2 기준 고정</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>은신 부여 결투 (가칭)</t>
+  </si>
+  <si>
+    <t>자기 부위에 다음 턴 은신 (미정) 누적 + 살수의 감 +(미정)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>은신 보상 결투 (가칭)</t>
+  </si>
+  <si>
+    <t>스킬 시작 시 사용 부위가 은신이면 확정 추가 피해 (미정)</t>
+  </si>
+  <si>
+    <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음</t>
+  </si>
+  <si>
+    <t>공용</t>
+  </si>
+  <si>
+    <t>방어도 +12</t>
+  </si>
+  <si>
+    <t>그 턴 모든 합 판정값 +1</t>
+  </si>
+  <si>
+    <t>노림수</t>
+  </si>
+  <si>
+    <t>그 턴 코인 앞면 확률 +10%p</t>
+  </si>
+  <si>
+    <t>선금 받기</t>
+  </si>
+  <si>
+    <t>그 턴 코인 뒷면 값 +2</t>
+  </si>
+  <si>
+    <t>환형(공격)</t>
+  </si>
+  <si>
+    <t>무기 교체(다음 턴) + 그 턴 위력 +2 (교체 전 무기 기준)</t>
+  </si>
+  <si>
+    <t>… +4</t>
+  </si>
+  <si>
+    <t>… +8</t>
+  </si>
+  <si>
+    <t>환형(수비)와 택1 장착</t>
+  </si>
+  <si>
+    <t>환형(수비)</t>
+  </si>
+  <si>
+    <t>무기 교체(다음 턴) + 그 턴 방어도 +30</t>
+  </si>
+  <si>
+    <t>환형(공격)과 택1 장착</t>
+  </si>
+  <si>
+    <t>기회를 엿보다</t>
   </si>
   <si>
     <t>살수의 감 +1</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>숨통을 끊다</t>
-  </si>
-  <si>
-    <t>대상이 흐트러짐 상태면 위력 +(미정)</t>
-  </si>
-  <si>
-    <t>대상이 봉인 상태면 위력 +(미정)</t>
-  </si>
-  <si>
-    <t>대상 부위 체력이 처형 구간 이하면 위력 +(미정)</t>
-  </si>
-  <si>
-    <t>역할을 이미 성공시킨 대상에게 위력 증가</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>소문을 내다</t>
-  </si>
-  <si>
-    <t>이 타격으로 대상 부위를 약화 또는 파괴하면 그 대상에게 표식 (미정) 대량 부여</t>
-  </si>
-  <si>
-    <t>한 타격에 약화·파괴가 같이 일어나도 1회</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>약점을 캐내다</t>
-  </si>
-  <si>
-    <t>상대 쇠약(다음 턴)</t>
-  </si>
-  <si>
-    <t>상대 골절(다음 턴)</t>
-  </si>
-  <si>
-    <t>상대 균열(다음 턴)</t>
-  </si>
-  <si>
-    <t>무기별 분기 첫 사례</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>퇴로 차단</t>
-  </si>
-  <si>
-    <t>승리시(짓누름일 때)</t>
-  </si>
-  <si>
-    <t>짓누름 상태면 상대 다음 턴 빛 최대치 −1 (1턴) + 자기 표식 10 소모 → 빛 +1</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>빌려 쓰다</t>
-  </si>
-  <si>
-    <t>안 든 무기 2개 중 하나를 골라 이번 결투의 코인 수 · 크리값 · 앞면 확률 · 처형 권한을 그 무기로</t>
-  </si>
-  <si>
-    <t>환형 UI 재사용</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>덫을 놓다</t>
-  </si>
-  <si>
-    <t>조준 부위에 덫 설치(지속) → 표식 44 발화 순간 함께 터져 확정 피해 +20(발동 후 소멸)</t>
-  </si>
-  <si>
-    <t>미구현(근사 필요) · 09-15 확정</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>시한을 정하다</t>
-  </si>
-  <si>
-    <t>대상에게 시한 2턴. 시한 중 표식 발화 시 다른 적들에게 표식 (미정) 전염, 발화하면 연쇄</t>
-  </si>
-  <si>
-    <t>한 번의 연쇄 처리에서 각 대상은 전염을 1회만 일으킨다</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>모두를 노리다</t>
-  </si>
-  <si>
-    <t>모든 적에게 「지정」(3턴)</t>
-  </si>
-  <si>
-    <t>미구현(전체 적 대상 처리 필요) · 09-15 신설, 목표 지정(C)의 전체 대상 버전</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>마침표를 찍다</t>
-  </si>
-  <si>
-    <t>이 타격으로 적을 처치했다면 → 살수의 감 +2</t>
-  </si>
-  <si>
-    <t>처형(크리로 파괴)이었다면 → 살수의 감 +2</t>
-  </si>
-  <si>
-    <t>미구현(무기별 조건 분기 필요) · 09-15 신설, 낙일 전용 처형 시너지 첫 카드 · 낙일=보스전/백우·적설=다수전 특화</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>때를 앞당기다</t>
-  </si>
-  <si>
-    <t>살수의 감 4 소모 → 조준 부위 표식 즉시 44까지 채워 발화(무기별 효과 즉시 발동)</t>
-  </si>
-  <si>
-    <t>미구현(표식 강제 발화 처리 신설 필요) · 09-16 신설, K·L과 달리 발화 자체를 직접 일으킴</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>끝장을 보다</t>
-  </si>
-  <si>
-    <t>4(쓸 때마다 −1, 최소 1, 누적)</t>
-  </si>
-  <si>
-    <t>살수의 감 전부 소모 → 이 스킬 위력 +2(소모한 살수의 감 1당)</t>
-  </si>
-  <si>
-    <t>기본위력은 빛 2 기준 고정(09-17) · 09-16 신설, 닥치는 대로(올라프)와 같은 비용 감소 구조</t>
-  </si>
-  <si>
-    <t>공용</t>
-  </si>
-  <si>
-    <t>방어도 +12</t>
-  </si>
-  <si>
-    <t>그 턴 모든 합 판정값 +1</t>
-  </si>
-  <si>
-    <t>노림수</t>
-  </si>
-  <si>
-    <t>그 턴 코인 앞면 확률 +10%p</t>
-  </si>
-  <si>
-    <t>선금 받기</t>
-  </si>
-  <si>
-    <t>그 턴 코인 뒷면 값 +2</t>
-  </si>
-  <si>
-    <t>환형(공격)</t>
-  </si>
-  <si>
-    <t>무기 교체(다음 턴) + 그 턴 위력 +2 (교체 전 무기 기준)</t>
-  </si>
-  <si>
-    <t>… +4</t>
-  </si>
-  <si>
-    <t>… +8</t>
-  </si>
-  <si>
-    <t>환형(수비)와 택1 장착</t>
-  </si>
-  <si>
-    <t>환형(수비)</t>
-  </si>
-  <si>
-    <t>무기 교체(다음 턴) + 그 턴 방어도 +30</t>
-  </si>
-  <si>
-    <t>환형(공격)과 택1 장착</t>
-  </si>
-  <si>
-    <t>기회를 엿보다</t>
-  </si>
-  <si>
-    <t>09-15 신설, 도사림 최초의 살수의 감 획득 카드</t>
-  </si>
-  <si>
     <t>숨을 죽이다</t>
   </si>
   <si>
-    <t>표식 10 소모 → 방어도 +20</t>
-  </si>
-  <si>
-    <t>미구현(표식 소모 전환 코드 신설 필요) · 09-15 신설</t>
+    <t>살수의 감 (미정) 소비 시도 → 방어도 +(미정)</t>
+  </si>
+  <si>
+    <t>구 「표식 소모」 폐기 — 도사림은 상대를 조준하지 않는다</t>
   </si>
   <si>
     <t>칼을 갈다</t>
   </si>
   <si>
-    <t>표식 10 소모 → 다음 턴 신속 1</t>
-  </si>
-  <si>
-    <t>미구현(표식 소모 전환 코드 신설 필요) · 09-15 신설, 힘→신속 정정(캐릭터별 크기형 배정)</t>
-  </si>
-  <si>
-    <t>은신</t>
-  </si>
-  <si>
-    <t>은신 부여 평타</t>
-  </si>
-  <si>
-    <t>자기 부위에 은신 (미정) 부여</t>
-  </si>
-  <si>
-    <t>행동 완료마다 −1 · 재부여는 덮어쓰기</t>
-  </si>
-  <si>
-    <t>은신 부여 결투</t>
-  </si>
-  <si>
-    <t>자기 부위에 은신 (미정) 부여 + 살수의 감 획득</t>
-  </si>
-  <si>
-    <t>은신 페이오프 평타</t>
-  </si>
-  <si>
-    <t>자기 은신 부위 하나를 골라 은신 전량 제거 → 큰 표식 획득 (미정)</t>
-  </si>
-  <si>
-    <t>이 카드를 쓰는 슬롯 부위가 은신일 필요 없음</t>
-  </si>
-  <si>
-    <t>은신 페이오프 결투</t>
-  </si>
-  <si>
-    <t>자기 은신 부위 하나를 골라 은신 전량 제거 → 큰 공격 보너스 (미정)</t>
+    <t>살수의 감 (미정) 소비 시도 → 다음 턴 신속 (미정)</t>
+  </si>
+  <si>
+    <t>손질하다</t>
+  </si>
+  <si>
+    <t>지금 든 무기를 손질 상태로 → 다음 턴 그 무기로 이긴 굴림의 낙점 +(미정) (3굴림)</t>
+  </si>
+  <si>
+    <t>… (1굴림)</t>
+  </si>
+  <si>
+    <t>다음 턴 종료 시 소멸 · 환형으로 바뀌면 원래 무기에만 귀속</t>
   </si>
   <si>
     <t>밑작업 착수</t>
@@ -1590,13 +1599,13 @@
     <t>내가 결정하고, 내가 끝낸다</t>
   </si>
   <si>
-    <t>표식을 부여하는 공격. 공격 전 대상에게 표식이 있으면 위력 증가, 없으면 감소</t>
-  </si>
-  <si>
-    <t>자신이 방금 부여한 표식은 조건을 채우지 않음</t>
-  </si>
-  <si>
-    <t>집행 2~4</t>
+    <t>결투. 스킬 시작 시 대상에 기존 표식이 없으면 기본 · 있으면 강화 상태. 각 굴림 승리시 고유 표식 +(미정) · 낙점 별도</t>
+  </si>
+  <si>
+    <t>스킬을 쓰기 전에 있던 표식이어야 함 · 지정을 부여하지 않음</t>
+  </si>
+  <si>
+    <t>집행 2</t>
   </si>
   <si>
     <t>집행 축</t>
@@ -1605,25 +1614,79 @@
     <t>표식 발화</t>
   </si>
   <si>
-    <t>기존 표식 위력 보너스 강화 → 표식 부여량 증가 → 이 스킬이 44 발화를 일으키면 무기 발화 효과 2배</t>
-  </si>
-  <si>
-    <t>표식 44 발화마다 성장 +1</t>
-  </si>
-  <si>
-    <t>판단 2~4</t>
+    <t>이 스킬의 표식이 직접 44 발화를 일으키면 발화 뒤 그 부위에 표식 +(미정) 재부여</t>
+  </si>
+  <si>
+    <t>진행 = 표식 44 발화 1회당 +1 · 앞 단계 효과 유지</t>
+  </si>
+  <si>
+    <t>집행 3</t>
+  </si>
+  <si>
+    <t>직접 발화 시 44를 넘친 표식을 보존 + 2단계 재부여</t>
+  </si>
+  <si>
+    <t>18.2 「초과분 이월 없음」의 예외</t>
+  </si>
+  <si>
+    <t>집행 4</t>
+  </si>
+  <si>
+    <t>이 스킬의 표식이 직접 44 발화를 일으키면 현재 무기의 원래 발화 효과 2배</t>
+  </si>
+  <si>
+    <t>그 턴에 발화가 있었다는 것만으로는 안 됨</t>
+  </si>
+  <si>
+    <t>판단 2</t>
   </si>
   <si>
     <t>판단 축</t>
   </si>
   <si>
-    <t>살수의 감 소비</t>
-  </si>
-  <si>
-    <t>환형 직후 공통 강화 → 무기별 역할 강화 → 역할 성공 시 살수의 감 획득</t>
-  </si>
-  <si>
-    <t>소비한 살수의 감 1스택마다 성장 +1</t>
+    <t>강화 상태 — 추가 흐트러짐 피해 +(미정)</t>
+  </si>
+  <si>
+    <t>강화 상태 — 대상에게 골절 (미정)</t>
+  </si>
+  <si>
+    <t>강화 상태 — 부위 피해 +(미정)</t>
+  </si>
+  <si>
+    <t>진행 = 살수의 감 실제 소비량 1당 +1</t>
+  </si>
+  <si>
+    <t>판단 3</t>
+  </si>
+  <si>
+    <t>적중 / 사용시</t>
+  </si>
+  <si>
+    <t>이 스킬의 흐트러짐 피해가 남은 흐트러짐을 넘으면 넘친 만큼 체력 피해로 전환 (비율 미정)</t>
+  </si>
+  <si>
+    <t>봉인된 부위 대상이면 각 굴림 사용시 골절 (미정)</t>
+  </si>
+  <si>
+    <t>강화 상태 적중 시 고정 부위 피해 +(미정)</t>
+  </si>
+  <si>
+    <t>낙일 — 원래 공격은 정상 내성, 그 위에 따로 더함(내성 무시 아님)</t>
+  </si>
+  <si>
+    <t>판단 4</t>
+  </si>
+  <si>
+    <t>역할 성공</t>
+  </si>
+  <si>
+    <t>이 스킬로 창을 직접 열면 살수의 감 +(미정) (이미 열린 대상 제외)</t>
+  </si>
+  <si>
+    <t>상대 디버프 2개 이상 + 이 결투에서 체력 · 흐트러짐 피해 0이면 살수의 감 +(미정)</t>
+  </si>
+  <si>
+    <t>이 스킬로 부위를 직접 파괴(처형 포함)하면 살수의 감 +(미정)</t>
   </si>
   <si>
     <t>무기</t>
@@ -3458,7 +3521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C09261C-EA70-475B-8875-41375E3A1503}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3906B2B1-305A-4129-B4E7-53BE1311A8C2}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3652,7 +3715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE675F75-22F2-4E82-84D3-1E6A6704FB1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C670D1-5BF1-465A-BE54-D655D8303358}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7208,15 +7271,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{AE675F75-22F2-4E82-84D3-1E6A6704FB1C}"/>
+  <autoFilter ref="A1:T57" xr:uid="{31C670D1-5BF1-465A-BE54-D655D8303358}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8187ED4B-7B17-490B-BA9F-8F5CD64F1CEE}">
-  <dimension ref="A1:M52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBCC0E78-1C69-4DAB-9646-0E638CDF183B}">
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
@@ -7313,7 +7376,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>52</v>
       </c>
@@ -7395,30 +7458,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>347</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>349</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>336</v>
@@ -7430,21 +7493,21 @@
         <v>1</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>351</v>
+        <v>53</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>1</v>
@@ -7459,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>336</v>
@@ -7471,215 +7534,215 @@
         <v>1</v>
       </c>
       <c r="L6" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="M7" s="8" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="54" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="B9" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="9" t="s">
+      <c r="J10" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="M10" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10" t="s">
+      <c r="B11" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="K8" s="9" t="s">
+      <c r="J11" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>368</v>
+      <c r="M11" s="10" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -7690,10 +7753,10 @@
         <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>1</v>
@@ -7702,10 +7765,10 @@
         <v>88</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>336</v>
@@ -7720,10 +7783,10 @@
         <v>51</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>83</v>
       </c>
@@ -7731,37 +7794,37 @@
         <v>49</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>74</v>
+        <v>375</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>374</v>
+        <v>336</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>376</v>
+        <v>1</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>377</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7772,7 +7835,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>86</v>
@@ -7781,31 +7844,31 @@
         <v>1</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>336</v>
-      </c>
       <c r="J14" s="8" t="s">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>1</v>
+        <v>381</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>83</v>
       </c>
@@ -7813,40 +7876,40 @@
         <v>49</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="K15" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>1</v>
-      </c>
       <c r="L15" s="7" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>83</v>
       </c>
@@ -7854,7 +7917,7 @@
         <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>86</v>
@@ -7866,25 +7929,25 @@
         <v>109</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>130</v>
+        <v>375</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>386</v>
+        <v>336</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>387</v>
+        <v>336</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>376</v>
+        <v>1</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7895,7 +7958,7 @@
         <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>98</v>
@@ -7904,206 +7967,206 @@
         <v>1</v>
       </c>
       <c r="F17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="G18" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="I19" s="10" t="s">
+      <c r="H20" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J20" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="K19" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="I20" s="10" t="s">
+      <c r="K20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J21" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="K20" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G21" s="9" t="s">
+      <c r="K21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>1</v>
@@ -8112,25 +8175,25 @@
         <v>109</v>
       </c>
       <c r="G22" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>336</v>
-      </c>
       <c r="K22" s="9" t="s">
-        <v>1</v>
+        <v>381</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>1</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8138,10 +8201,10 @@
         <v>176</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>417</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>86</v>
@@ -8153,25 +8216,25 @@
         <v>109</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>130</v>
+        <v>375</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M23" s="10" t="s">
         <v>418</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8179,13 +8242,13 @@
         <v>176</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>1</v>
@@ -8194,10 +8257,10 @@
         <v>109</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>74</v>
+        <v>421</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>336</v>
@@ -8212,21 +8275,21 @@
         <v>257</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>1</v>
@@ -8235,25 +8298,25 @@
         <v>109</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>74</v>
+        <v>426</v>
       </c>
       <c r="H25" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="M25" s="10" t="s">
         <v>428</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8261,10 +8324,10 @@
         <v>176</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>86</v>
@@ -8276,10 +8339,10 @@
         <v>109</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>336</v>
@@ -8291,21 +8354,21 @@
         <v>1</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>86</v>
@@ -8314,39 +8377,39 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>130</v>
+        <v>435</v>
       </c>
       <c r="H27" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="J27" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="I27" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>336</v>
-      </c>
       <c r="K27" s="9" t="s">
-        <v>1</v>
+        <v>439</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>86</v>
@@ -8355,13 +8418,13 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>336</v>
@@ -8376,21 +8439,21 @@
         <v>51</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>1</v>
@@ -8399,10 +8462,10 @@
         <v>109</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>74</v>
+        <v>375</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>336</v>
@@ -8417,7 +8480,7 @@
         <v>257</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>447</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8437,10 +8500,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>130</v>
+        <v>375</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>450</v>
@@ -8455,13 +8518,13 @@
         <v>1</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>176</v>
       </c>
@@ -8481,36 +8544,36 @@
         <v>109</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>74</v>
+        <v>426</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>454</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>336</v>
+        <v>455</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>86</v>
@@ -8522,10 +8585,10 @@
         <v>108</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>130</v>
+        <v>392</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>336</v>
@@ -8537,10 +8600,10 @@
         <v>1</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -8548,10 +8611,10 @@
         <v>176</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>86</v>
@@ -8560,110 +8623,110 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>130</v>
+        <v>465</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I33" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="I34" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J34" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="K33" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="I34" s="8" t="s">
+      <c r="K34" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="J35" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>1</v>
+      <c r="K35" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -8671,25 +8734,25 @@
         <v>262</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>272</v>
+        <v>477</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>469</v>
+        <v>263</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>130</v>
+        <v>265</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>336</v>
@@ -8712,25 +8775,25 @@
         <v>262</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>272</v>
+        <v>477</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>471</v>
+        <v>268</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>109</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>130</v>
+        <v>265</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>336</v>
@@ -8756,7 +8819,7 @@
         <v>272</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>1</v>
@@ -8768,16 +8831,16 @@
         <v>109</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>475</v>
+        <v>336</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>476</v>
+        <v>336</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>1</v>
@@ -8786,7 +8849,7 @@
         <v>51</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>477</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -8797,7 +8860,7 @@
         <v>272</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>1</v>
@@ -8809,10 +8872,10 @@
         <v>109</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>336</v>
@@ -8827,10 +8890,10 @@
         <v>51</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>262</v>
       </c>
@@ -8838,7 +8901,7 @@
         <v>272</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1</v>
@@ -8847,19 +8910,19 @@
         <v>272</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>130</v>
+        <v>354</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>415</v>
+        <v>485</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>336</v>
+        <v>486</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>336</v>
+        <v>487</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>1</v>
@@ -8868,10 +8931,10 @@
         <v>51</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>262</v>
       </c>
@@ -8879,7 +8942,7 @@
         <v>272</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>1</v>
@@ -8888,13 +8951,13 @@
         <v>272</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>130</v>
+        <v>354</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>336</v>
@@ -8909,10 +8972,10 @@
         <v>51</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>262</v>
       </c>
@@ -8920,7 +8983,7 @@
         <v>272</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>1</v>
@@ -8932,10 +8995,10 @@
         <v>88</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>130</v>
+        <v>265</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>336</v>
@@ -8950,279 +9013,279 @@
         <v>51</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="I43" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="I43" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="J43" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="K43" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L43" s="9" t="s">
+      <c r="K43" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L43" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="M43" s="10" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="I44" s="10" t="s">
+      <c r="M43" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="I44" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="J44" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="K44" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L44" s="9" t="s">
+      <c r="K44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L44" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="M44" s="10" t="s">
-        <v>492</v>
+      <c r="M44" s="8" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A45" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L45" s="9" t="s">
+      <c r="A45" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L45" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="M45" s="10" t="s">
-        <v>497</v>
+      <c r="M45" s="8" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>489</v>
+        <v>293</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>130</v>
+        <v>297</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="I46" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="I47" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J47" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="K46" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="M46" s="10" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
+      <c r="K47" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="7" t="s">
+      <c r="B48" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="H47" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L47" s="7" t="s">
+      <c r="H48" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M47" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M48" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="M48" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>303</v>
+        <v>512</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>297</v>
+        <v>375</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>336</v>
@@ -9234,144 +9297,267 @@
         <v>1</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>1</v>
+        <v>515</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="I50" s="10" t="s">
+      <c r="B50" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="I50" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="J50" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="K50" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L50" s="9" t="s">
+      <c r="K50" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L50" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="M50" s="10" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A51" s="9" t="s">
+      <c r="M50" s="8" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="I51" s="10" t="s">
+      <c r="B51" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="I51" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J51" s="10" t="s">
+      <c r="J51" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="K51" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L51" s="9" t="s">
+      <c r="K51" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L51" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="M51" s="10" t="s">
+      <c r="M51" s="8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
+      <c r="D52" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L52" s="9" t="s">
+      <c r="B53" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="L53" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="M52" s="10" t="s">
-        <v>522</v>
+      <c r="M53" s="8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M52" xr:uid="{8187ED4B-7B17-490B-BA9F-8F5CD64F1CEE}"/>
+  <autoFilter ref="A1:M55" xr:uid="{DBCC0E78-1C69-4DAB-9646-0E638CDF183B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE2A5DF-CC10-4D1C-AAC2-BCA27BD69341}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8078C1B3-7D64-41BB-8B06-DE86189CAD46}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9389,201 +9575,201 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>136</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>108</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>109</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>192</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{6DE2A5DF-CC10-4D1C-AAC2-BCA27BD69341}"/>
+  <autoFilter ref="A1:O4" xr:uid="{8078C1B3-7D64-41BB-8B06-DE86189CAD46}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526E5AF2-16DD-4FC9-AD9F-29FDDFB937B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{384CA777-8E7D-418E-B7DC-48645DB39F42}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9674,10 +9860,10 @@
         <v>46</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -9716,7 +9902,7 @@
         <v>49</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>1</v>
@@ -9733,10 +9919,10 @@
         <v>67</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -9778,7 +9964,7 @@
         <v>49</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>1</v>
@@ -9798,7 +9984,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
@@ -9837,10 +10023,10 @@
         <v>1</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>1</v>
@@ -9849,7 +10035,7 @@
         <v>51</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9857,10 +10043,10 @@
         <v>52</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>1</v>
@@ -9899,10 +10085,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="R5" s="13" t="s">
         <v>1</v>
@@ -9911,7 +10097,7 @@
         <v>51</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -9922,7 +10108,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1</v>
@@ -9961,10 +10147,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="R6" s="13" t="s">
         <v>1</v>
@@ -9981,10 +10167,10 @@
         <v>67</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>1</v>
@@ -10023,10 +10209,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="R7" s="11" t="s">
         <v>1</v>
@@ -10035,7 +10221,7 @@
         <v>51</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10043,10 +10229,10 @@
         <v>67</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>1</v>
@@ -10085,10 +10271,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="R8" s="11" t="s">
         <v>1</v>
@@ -10097,7 +10283,7 @@
         <v>51</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -10108,7 +10294,7 @@
         <v>68</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>1</v>
@@ -10150,7 +10336,7 @@
         <v>74</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="R9" s="11" t="s">
         <v>1</v>
@@ -10167,19 +10353,19 @@
         <v>176</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>92</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>135</v>
@@ -10191,37 +10377,37 @@
         <v>99</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="S10" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10229,19 +10415,19 @@
         <v>176</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>92</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>108</v>
@@ -10250,13 +10436,13 @@
         <v>109</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="L11" s="14" t="s">
         <v>1</v>
@@ -10268,22 +10454,22 @@
         <v>1</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10291,10 +10477,10 @@
         <v>176</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>1</v>
@@ -10303,7 +10489,7 @@
         <v>92</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>123</v>
@@ -10315,28 +10501,28 @@
         <v>158</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>130</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="R12" s="13" t="s">
         <v>1</v>
@@ -10345,7 +10531,7 @@
         <v>257</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10353,10 +10539,10 @@
         <v>176</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>1</v>
@@ -10365,13 +10551,13 @@
         <v>92</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>108</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>92</v>
@@ -10398,7 +10584,7 @@
         <v>210</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="R13" s="13" t="s">
         <v>1</v>
@@ -10407,7 +10593,7 @@
         <v>257</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
@@ -10415,10 +10601,10 @@
         <v>176</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -10427,7 +10613,7 @@
         <v>92</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>87</v>
@@ -10457,10 +10643,10 @@
         <v>92</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -10477,10 +10663,10 @@
         <v>176</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -10519,10 +10705,10 @@
         <v>92</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -10531,7 +10717,7 @@
         <v>257</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10539,10 +10725,10 @@
         <v>176</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -10554,13 +10740,13 @@
         <v>307</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>1</v>
@@ -10578,22 +10764,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="P16" s="13" t="s">
         <v>210</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="S16" s="13" t="s">
         <v>257</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10601,10 +10787,10 @@
         <v>176</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>633</v>
+        <v>654</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -10613,7 +10799,7 @@
         <v>98</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>87</v>
@@ -10643,19 +10829,19 @@
         <v>92</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>257</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -10663,10 +10849,10 @@
         <v>176</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>1</v>
@@ -10708,7 +10894,7 @@
         <v>188</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="R18" s="13" t="s">
         <v>1</v>
@@ -10725,10 +10911,10 @@
         <v>176</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>1</v>
@@ -10770,7 +10956,7 @@
         <v>130</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="R19" s="13" t="s">
         <v>1</v>
@@ -10787,10 +10973,10 @@
         <v>176</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>1</v>
@@ -10799,7 +10985,7 @@
         <v>86</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>87</v>
@@ -10832,7 +11018,7 @@
         <v>188</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="R20" s="13" t="s">
         <v>1</v>
@@ -10849,10 +11035,10 @@
         <v>83</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
@@ -10861,7 +11047,7 @@
         <v>92</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>108</v>
@@ -10870,13 +11056,13 @@
         <v>88</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="L21" s="12" t="s">
         <v>1</v>
@@ -10888,22 +11074,22 @@
         <v>1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>140</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="S21" s="11" t="s">
         <v>257</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>648</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10911,10 +11097,10 @@
         <v>83</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>1</v>
@@ -10935,13 +11121,13 @@
         <v>110</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>1</v>
@@ -10950,13 +11136,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>653</v>
+        <v>674</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>1</v>
@@ -10973,10 +11159,10 @@
         <v>83</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>655</v>
+        <v>676</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>1</v>
@@ -11018,7 +11204,7 @@
         <v>130</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="R23" s="11" t="s">
         <v>1</v>
@@ -11027,7 +11213,7 @@
         <v>257</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>658</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -11035,10 +11221,10 @@
         <v>83</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>1</v>
@@ -11047,7 +11233,7 @@
         <v>92</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>87</v>
@@ -11080,10 +11266,10 @@
         <v>140</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>257</v>
@@ -11097,10 +11283,10 @@
         <v>83</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>1</v>
@@ -11109,7 +11295,7 @@
         <v>92</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>108</v>
@@ -11142,10 +11328,10 @@
         <v>210</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>257</v>
@@ -11159,10 +11345,10 @@
         <v>83</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>1</v>
@@ -11171,7 +11357,7 @@
         <v>92</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>108</v>
@@ -11204,10 +11390,10 @@
         <v>130</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>257</v>
@@ -11221,10 +11407,10 @@
         <v>83</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>1</v>
@@ -11266,7 +11452,7 @@
         <v>130</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="R27" s="11" t="s">
         <v>1</v>
@@ -11283,10 +11469,10 @@
         <v>83</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>671</v>
+        <v>692</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>1</v>
@@ -11295,7 +11481,7 @@
         <v>92</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>87</v>
@@ -11328,7 +11514,7 @@
         <v>130</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>1</v>
@@ -11345,10 +11531,10 @@
         <v>83</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>1</v>
@@ -11390,7 +11576,7 @@
         <v>74</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="R29" s="11" t="s">
         <v>1</v>
@@ -11407,10 +11593,10 @@
         <v>83</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>677</v>
+        <v>698</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>1</v>
@@ -11449,10 +11635,10 @@
         <v>92</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="R30" s="11" t="s">
         <v>1</v>
@@ -11469,10 +11655,10 @@
         <v>83</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>1</v>
@@ -11511,10 +11697,10 @@
         <v>92</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="R31" s="11" t="s">
         <v>1</v>
@@ -11523,7 +11709,7 @@
         <v>257</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>684</v>
+        <v>705</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -11531,7 +11717,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>263</v>
@@ -11576,7 +11762,7 @@
         <v>130</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="R32" s="13" t="s">
         <v>1</v>
@@ -11593,7 +11779,7 @@
         <v>262</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>268</v>
@@ -11638,7 +11824,7 @@
         <v>130</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="R33" s="13" t="s">
         <v>1</v>
@@ -11655,10 +11841,10 @@
         <v>262</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -11700,7 +11886,7 @@
         <v>130</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="R34" s="13" t="s">
         <v>1</v>
@@ -11709,7 +11895,7 @@
         <v>257</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>687</v>
+        <v>708</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
@@ -11717,10 +11903,10 @@
         <v>262</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>1</v>
@@ -11762,7 +11948,7 @@
         <v>130</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>689</v>
+        <v>710</v>
       </c>
       <c r="R35" s="13" t="s">
         <v>1</v>
@@ -11771,7 +11957,7 @@
         <v>257</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
@@ -11779,10 +11965,10 @@
         <v>262</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>1</v>
@@ -11824,7 +12010,7 @@
         <v>130</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="R36" s="13" t="s">
         <v>1</v>
@@ -11841,10 +12027,10 @@
         <v>262</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>1</v>
@@ -11886,7 +12072,7 @@
         <v>130</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="R37" s="13" t="s">
         <v>1</v>
@@ -11895,7 +12081,7 @@
         <v>257</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>696</v>
+        <v>717</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
@@ -11903,10 +12089,10 @@
         <v>262</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -11948,7 +12134,7 @@
         <v>130</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>698</v>
+        <v>719</v>
       </c>
       <c r="R38" s="13" t="s">
         <v>1</v>
@@ -11968,7 +12154,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>1</v>
@@ -12010,7 +12196,7 @@
         <v>130</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="R39" s="13" t="s">
         <v>1</v>
@@ -12027,10 +12213,10 @@
         <v>262</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>1</v>
@@ -12072,7 +12258,7 @@
         <v>130</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="R40" s="13" t="s">
         <v>1</v>
@@ -12089,10 +12275,10 @@
         <v>262</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -12134,7 +12320,7 @@
         <v>130</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="R41" s="13" t="s">
         <v>1</v>
@@ -12154,7 +12340,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -12196,7 +12382,7 @@
         <v>130</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="R42" s="13" t="s">
         <v>1</v>
@@ -12216,7 +12402,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>1</v>
@@ -12258,7 +12444,7 @@
         <v>130</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="R43" s="13" t="s">
         <v>1</v>
@@ -12278,7 +12464,7 @@
         <v>294</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>709</v>
+        <v>730</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>1</v>
@@ -12287,7 +12473,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>1</v>
@@ -12320,7 +12506,7 @@
         <v>297</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>710</v>
+        <v>731</v>
       </c>
       <c r="R44" s="11" t="s">
         <v>1</v>
@@ -12340,7 +12526,7 @@
         <v>299</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>1</v>
@@ -12349,7 +12535,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>1</v>
@@ -12382,7 +12568,7 @@
         <v>297</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>712</v>
+        <v>733</v>
       </c>
       <c r="R45" s="11" t="s">
         <v>1</v>
@@ -12402,7 +12588,7 @@
         <v>303</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>1</v>
@@ -12444,7 +12630,7 @@
         <v>297</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>1</v>
@@ -12457,14 +12643,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{526E5AF2-16DD-4FC9-AD9F-29FDDFB937B9}"/>
+  <autoFilter ref="A1:T46" xr:uid="{384CA777-8E7D-418E-B7DC-48645DB39F42}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AB93E2-D30D-4C9A-9E27-62315E76A06F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C1CC09-2ABD-4C21-880B-393A94C331A9}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12479,7 +12665,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>716</v>
+        <v>737</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>28</v>
@@ -12488,13 +12674,13 @@
         <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -12502,278 +12688,278 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>722</v>
-      </c>
       <c r="D8" s="10" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>747</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>725</v>
-      </c>
       <c r="G9" s="10" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>756</v>
+        <v>777</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>758</v>
+        <v>779</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -12784,19 +12970,19 @@
         <v>65</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>764</v>
+        <v>785</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>765</v>
+        <v>786</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -12807,76 +12993,76 @@
         <v>343</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>768</v>
+        <v>789</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>774</v>
+        <v>795</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17" xr:uid="{11AB93E2-D30D-4C9A-9E27-62315E76A06F}"/>
+  <autoFilter ref="A1:G17" xr:uid="{39C1CC09-2ABD-4C21-880B-393A94C331A9}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1607A0E6-F927-4990-82B2-DCF8B6295B0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3B2D9A-6240-4E2C-A773-313A4E56CE94}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12890,19 +13076,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>42</v>
@@ -12913,22 +13099,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>756</v>
+        <v>777</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>51</v>
@@ -12936,22 +13122,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>51</v>
@@ -12959,22 +13145,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>794</v>
+        <v>815</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>51</v>
@@ -12982,22 +13168,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
@@ -13005,22 +13191,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>51</v>
@@ -13028,22 +13214,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>51</v>
@@ -13051,22 +13237,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>51</v>
@@ -13074,22 +13260,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>804</v>
+        <v>825</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>51</v>
@@ -13097,22 +13283,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>805</v>
+        <v>826</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>51</v>
@@ -13120,22 +13306,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>109</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>51</v>
@@ -13143,22 +13329,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>109</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>51</v>
@@ -13166,22 +13352,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>109</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>814</v>
+        <v>835</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>815</v>
+        <v>836</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>51</v>
@@ -13189,22 +13375,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>51</v>
@@ -13212,22 +13398,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>819</v>
+        <v>840</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>51</v>
@@ -13235,22 +13421,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>820</v>
+        <v>841</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>821</v>
+        <v>842</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>51</v>
@@ -13258,45 +13444,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>822</v>
+        <v>843</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>823</v>
+        <v>844</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>824</v>
+        <v>845</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>825</v>
+        <v>846</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>51</v>
@@ -13304,22 +13490,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>51</v>
@@ -13327,22 +13513,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>832</v>
+        <v>853</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>51</v>
@@ -13350,22 +13536,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>834</v>
+        <v>855</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>51</v>
@@ -13373,22 +13559,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>835</v>
+        <v>856</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>836</v>
+        <v>857</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>51</v>
@@ -13396,22 +13582,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>51</v>
@@ -13419,22 +13605,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>839</v>
+        <v>860</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>51</v>
@@ -13442,22 +13628,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>51</v>
@@ -13465,22 +13651,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>51</v>
@@ -13488,22 +13674,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>51</v>
@@ -13511,183 +13697,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>109</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>109</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>109</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>858</v>
+        <v>879</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>859</v>
+        <v>880</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>51</v>
@@ -13695,68 +13881,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>867</v>
+        <v>888</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>869</v>
+        <v>890</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>870</v>
+        <v>891</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>871</v>
+        <v>892</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>872</v>
+        <v>893</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>51</v>
@@ -13764,22 +13950,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>877</v>
+        <v>898</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>51</v>
@@ -13787,22 +13973,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>51</v>
@@ -13810,22 +13996,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>882</v>
+        <v>903</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>51</v>
@@ -13833,22 +14019,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>51</v>
@@ -13856,22 +14042,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>51</v>
@@ -13879,45 +14065,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>51</v>
@@ -13925,22 +14111,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>51</v>
@@ -13948,10 +14134,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>293</v>
@@ -13960,10 +14146,10 @@
         <v>109</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>896</v>
+        <v>917</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>51</v>
@@ -13971,10 +14157,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>293</v>
@@ -13983,10 +14169,10 @@
         <v>109</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>51</v>
@@ -13994,10 +14180,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>293</v>
@@ -14006,10 +14192,10 @@
         <v>109</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>51</v>
@@ -14017,10 +14203,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>293</v>
@@ -14029,10 +14215,10 @@
         <v>108</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>51</v>
@@ -14040,10 +14226,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>293</v>
@@ -14052,10 +14238,10 @@
         <v>108</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>902</v>
+        <v>923</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>903</v>
+        <v>924</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>51</v>
@@ -14063,10 +14249,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>293</v>
@@ -14075,10 +14261,10 @@
         <v>108</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>51</v>
@@ -14086,10 +14272,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>293</v>
@@ -14098,10 +14284,10 @@
         <v>87</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>906</v>
+        <v>927</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>51</v>
@@ -14109,10 +14295,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>293</v>
@@ -14121,10 +14307,10 @@
         <v>87</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>907</v>
+        <v>928</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>51</v>
@@ -14132,10 +14318,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>293</v>
@@ -14144,10 +14330,10 @@
         <v>87</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>51</v>
@@ -14155,68 +14341,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>914</v>
+        <v>935</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>916</v>
+        <v>937</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>914</v>
+        <v>935</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>917</v>
+        <v>938</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>918</v>
+        <v>939</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>51</v>
@@ -14224,22 +14410,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>919</v>
+        <v>940</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>51</v>
@@ -14247,22 +14433,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>921</v>
+        <v>942</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>51</v>
@@ -14270,22 +14456,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>924</v>
+        <v>945</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>51</v>
@@ -14293,22 +14479,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>925</v>
+        <v>946</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>926</v>
+        <v>947</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>51</v>
@@ -14316,22 +14502,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>927</v>
+        <v>948</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>928</v>
+        <v>949</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>51</v>
@@ -14339,36 +14525,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>929</v>
+        <v>950</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>930</v>
+        <v>951</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{1607A0E6-F927-4990-82B2-DCF8B6295B0C}"/>
+  <autoFilter ref="A1:G64" xr:uid="{6F3B2D9A-6240-4E2C-A773-313A4E56CE94}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98477FE3-8F42-435F-9816-82B5E674842B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3791FFB9-7D8B-4FFF-B845-BCD6F9279FA0}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14382,10 +14568,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>931</v>
+        <v>952</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>932</v>
+        <v>953</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>32</v>
@@ -14397,7 +14583,7 @@
         <v>176</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -14405,10 +14591,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>934</v>
+        <v>955</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>935</v>
+        <v>956</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>87</v>
@@ -14417,21 +14603,21 @@
         <v>89</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>936</v>
+        <v>957</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>937</v>
+        <v>958</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
@@ -14440,21 +14626,21 @@
         <v>110</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>942</v>
+        <v>963</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>945</v>
+        <v>966</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>49</v>
@@ -14466,18 +14652,18 @@
         <v>49</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>947</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>949</v>
+        <v>970</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>49</v>
@@ -14489,18 +14675,18 @@
         <v>49</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>951</v>
+        <v>972</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>952</v>
+        <v>973</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>953</v>
+        <v>974</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>87</v>
@@ -14509,21 +14695,21 @@
         <v>158</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>952</v>
+        <v>973</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>108</v>
@@ -14532,21 +14718,21 @@
         <v>110</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>958</v>
+        <v>979</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>952</v>
+        <v>973</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>49</v>
@@ -14558,14 +14744,14 @@
         <v>49</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>960</v>
+        <v>981</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{98477FE3-8F42-435F-9816-82B5E674842B}"/>
+  <autoFilter ref="A1:G8" xr:uid="{3791FFB9-7D8B-4FFF-B845-BCD6F9279FA0}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\yj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-Onedrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F04ED2C4-43E2-494B-A9BE-7F4DA6C998D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{316815E2-27F6-4AA3-A642-B1D9722447A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{22344033-CCBA-419E-8156-8B9E3B59CE79}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{C6B7F077-5047-4A62-AE28-8A5B08F99E0C}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -1164,10 +1164,10 @@
     <t>처형</t>
   </si>
   <si>
-    <t>앞면(크리) 타격의 피해가 부위의 남은 체력을 0 이하로 만들 수 있으면 한 타격 안에서 정상 → 약화 → 파괴</t>
-  </si>
-  <si>
-    <t>미리 약화될 필요 없음</t>
+    <t>모든 낙일 타격(앞면 · 뒷면 무관)의 피해가 부위의 남은 체력을 0 이하로 만들 수 있으면 한 타격 안에서 정상 → 약화 → 파괴</t>
+  </si>
+  <si>
+    <t>무기 기본 효과 · 미리 약화될 필요 없음</t>
   </si>
   <si>
     <t>뒷조사</t>
@@ -3521,7 +3521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3906B2B1-305A-4129-B4E7-53BE1311A8C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA682E6-AB1B-488D-BA6A-164CDC96D6FB}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3715,7 +3715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C670D1-5BF1-465A-BE54-D655D8303358}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0060C8D5-7ECB-46FF-8FDD-341534EDFC62}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7271,14 +7271,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{31C670D1-5BF1-465A-BE54-D655D8303358}"/>
+  <autoFilter ref="A1:T57" xr:uid="{0060C8D5-7ECB-46FF-8FDD-341534EDFC62}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBCC0E78-1C69-4DAB-9646-0E638CDF183B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7202AF-A717-48BC-86F7-F2C633FE86C4}">
   <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9550,14 +9550,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{DBCC0E78-1C69-4DAB-9646-0E638CDF183B}"/>
+  <autoFilter ref="A1:M55" xr:uid="{DD7202AF-A717-48BC-86F7-F2C633FE86C4}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8078C1B3-7D64-41BB-8B06-DE86189CAD46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D9AE0D-9715-46A0-822E-BF09943268FF}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9762,14 +9762,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{8078C1B3-7D64-41BB-8B06-DE86189CAD46}"/>
+  <autoFilter ref="A1:O4" xr:uid="{88D9AE0D-9715-46A0-822E-BF09943268FF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{384CA777-8E7D-418E-B7DC-48645DB39F42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26047717-DF63-46F4-BE00-8DAE8137D19B}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12643,14 +12643,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{384CA777-8E7D-418E-B7DC-48645DB39F42}"/>
+  <autoFilter ref="A1:T46" xr:uid="{26047717-DF63-46F4-BE00-8DAE8137D19B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C1CC09-2ABD-4C21-880B-393A94C331A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5737A798-B4DF-4491-9E0E-C444FEB63439}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13055,14 +13055,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17" xr:uid="{39C1CC09-2ABD-4C21-880B-393A94C331A9}"/>
+  <autoFilter ref="A1:G17" xr:uid="{5737A798-B4DF-4491-9E0E-C444FEB63439}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3B2D9A-6240-4E2C-A773-313A4E56CE94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C58C528B-B2FA-47E6-87B3-C62F9E42028D}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14547,14 +14547,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{6F3B2D9A-6240-4E2C-A773-313A4E56CE94}"/>
+  <autoFilter ref="A1:G64" xr:uid="{C58C528B-B2FA-47E6-87B3-C62F9E42028D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3791FFB9-7D8B-4FFF-B845-BCD6F9279FA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9319BE63-053B-4980-8BF5-EAC4BFDBF7B2}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14751,7 +14751,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{3791FFB9-7D8B-4FFF-B845-BCD6F9279FA0}"/>
+  <autoFilter ref="A1:G8" xr:uid="{9319BE63-053B-4980-8BF5-EAC4BFDBF7B2}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-Onedrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-Onedrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\yj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D7F1501-708D-4CC1-8817-DC8978CE8457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{986C1017-41D2-4665-A498-7EC9639E83C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{9F62C7BB-3CDA-4376-BE0D-D710944C06D6}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{38FEBCBC-461C-4494-888D-1E110B1C7DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'감정 증강'!$A$1:$G$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">공용!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">올라프!$A$1:$T$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">유진!$A$1:$M$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">유진!$A$1:$M$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'유진 무기'!$A$1:$O$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">적!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">히후미!$A$1:$T$46</definedName>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3488" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3501" uniqueCount="994">
   <si>
     <t>Project Abyss — 전투 콘텐츠 명세 (2026-09-25)</t>
   </si>
@@ -1122,10 +1122,10 @@
     <t>재부여 처리 (미정)</t>
   </si>
   <si>
-    <t>덫 (폭발 덫 · 공명 덫)</t>
-  </si>
-  <si>
-    <t>부위 스택. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발 = 스택 비례 확정 피해 (미정) / 공명 = 현재 무기의 발화 효과 강화 (미정)</t>
+    <t>덫 (폭발 덫 · 공명 덫 · 전염 덫)</t>
+  </si>
+  <si>
+    <t>부위 단위. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발 = 스택 비례 확정 피해 (미정) / 공명 = 발화 자체를 강화 발화로 (미정) / 전염(2턴) = 다른 적 무작위 최대 2명에게 표식 (미정), 그 발화도 전염을 잇고 재감염 허용</t>
   </si>
   <si>
     <t>덫은 표식을 주지 않음 · 승리 → 덫 설치 → 낙점 → 발화 → 방금 단 덫도 발동</t>
@@ -1326,10 +1326,10 @@
     <t>잔혹한 마무리</t>
   </si>
   <si>
-    <t>살수의 감 1 소비 시도 → 성공하면 무저항 추가타 (상한 강화 표)</t>
-  </si>
-  <si>
-    <t>추가타는 승리시를 다시 일으키지 않고 추가타를 다시 만들지 않음</t>
+    <t>추가타 판정 코인 — 앞면이면 무저항 추가타(상한 강화 표), 뒷면이면 살수의 감 1 소비해 다시 던짐 · 감이 없으면 추가타 없음</t>
+  </si>
+  <si>
+    <t>추가타는 승리시 · 피해 처리 후 효과를 만들지 않고 추가타를 다시 만들지 않음</t>
   </si>
   <si>
     <t>C</t>
@@ -1380,10 +1380,10 @@
     <t>퇴로 차단</t>
   </si>
   <si>
-    <t>승리시(굴림 위치별)</t>
-  </si>
-  <si>
-    <t>짓누름이면 1굴림: 상대 다음 턴 빛 최대치 −(미정) · 2굴림: 표식 (미정) 소비 → 빛 +(미정) · 3굴림: 기세 바 +(미정)</t>
+    <t>승리시(굴림 위치별) · 사용 조건: 지난 턴 짓누름(+70)</t>
+  </si>
+  <si>
+    <t>1굴림: 상대 다음 턴 빛 최대치 −(미정) · 2굴림: 현재 대상 부위 표식 (미정) 소비 → 빛 +(미정) · 3굴림: 기세 바 +(미정)</t>
   </si>
   <si>
     <t>… 1~2굴림 효과만</t>
@@ -1431,6 +1431,18 @@
     <t>카드명은 작명 단계에서 바뀔 수 있음 · 구 「시한」 상태 폐기</t>
   </si>
   <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>전염 덫 (가칭)</t>
+  </si>
+  <si>
+    <t>대상 부위에 전염 덫(2턴) — 그 부위 표식 발화 시 다른 적 무작위 최대 2명에게 표식 (미정), 연쇄 · 재감염 허용</t>
+  </si>
+  <si>
+    <t>다부위 적에게 전염될 때 표식 부위 (미정)</t>
+  </si>
+  <si>
     <t>J</t>
   </si>
   <si>
@@ -1470,114 +1482,117 @@
     <t>4(쓸 때마다 −1, 최소 1, 누적)</t>
   </si>
   <si>
-    <t>전투 시작시 / 적중 시</t>
-  </si>
-  <si>
-    <t>살수의 감 전부 소비 → 소비량 비례 마무리 피해 풀 (미정) → 적중마다 확정 추가 피해로 나눠 씀 (3굴림)</t>
+    <t>전투 시작시 / 이긴 굴림</t>
+  </si>
+  <si>
+    <t>살수의 감 전부 소비 → 풀 P (미정) → 총 굴림 수로 미리 분할(P/3) · 이긴 굴림만 받고 진 몫은 소멸</t>
+  </si>
+  <si>
+    <t>… (P/2)</t>
+  </si>
+  <si>
+    <t>… (P)</t>
+  </si>
+  <si>
+    <t>풀은 하나의 총량(소비 × 굴림 수로 불어나지 않음) · 남으면 소멸 · 기본위력 빛 2 기준 고정</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>은신 부여 결투 (가칭)</t>
+  </si>
+  <si>
+    <t>쓰는 부위가 은신이 아니면 다음 턴 은신 (미정) 예약 · 이미 은신이면 대신 살수의 감 +(미정)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>은신 보상 결투 (가칭)</t>
+  </si>
+  <si>
+    <t>스킬 시작 시 사용 부위가 은신이면 확정 추가 피해 (미정)</t>
+  </si>
+  <si>
+    <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음</t>
+  </si>
+  <si>
+    <t>공용</t>
+  </si>
+  <si>
+    <t>방어도 +12</t>
+  </si>
+  <si>
+    <t>그 턴 모든 합 판정값 +1</t>
+  </si>
+  <si>
+    <t>노림수</t>
+  </si>
+  <si>
+    <t>그 턴 코인 앞면 확률 +10%p</t>
+  </si>
+  <si>
+    <t>선금 받기</t>
+  </si>
+  <si>
+    <t>그 턴 코인 뒷면 값 +2</t>
+  </si>
+  <si>
+    <t>환형(공격)</t>
+  </si>
+  <si>
+    <t>무기 교체(다음 턴) + 그 턴 위력 +2 (교체 전 무기 기준)</t>
+  </si>
+  <si>
+    <t>… +4</t>
+  </si>
+  <si>
+    <t>… +8</t>
+  </si>
+  <si>
+    <t>환형(수비)와 택1 장착</t>
+  </si>
+  <si>
+    <t>환형(수비)</t>
+  </si>
+  <si>
+    <t>무기 교체(다음 턴) + 그 턴 방어도 +30</t>
+  </si>
+  <si>
+    <t>환형(공격)과 택1 장착</t>
+  </si>
+  <si>
+    <t>기회를 엿보다</t>
+  </si>
+  <si>
+    <t>살수의 감 +1</t>
+  </si>
+  <si>
+    <t>숨을 죽이다</t>
+  </si>
+  <si>
+    <t>살수의 감 (미정) 소비 시도 → 방어도 +(미정)</t>
+  </si>
+  <si>
+    <t>구 「표식 소모」 폐기 — 도사림은 상대를 조준하지 않는다</t>
+  </si>
+  <si>
+    <t>칼을 갈다</t>
+  </si>
+  <si>
+    <t>살수의 감 (미정) 소비 시도 → 다음 턴 신속 (미정)</t>
+  </si>
+  <si>
+    <t>손질하다</t>
+  </si>
+  <si>
+    <t>지금 든 무기를 손질 상태로 → 다음 턴 그 무기로 이긴 굴림의 낙점 +(미정) (3굴림)</t>
   </si>
   <si>
     <t>… (2굴림)</t>
   </si>
   <si>
-    <t>… (1굴림에 집중)</t>
-  </si>
-  <si>
-    <t>풀은 하나의 총량(소비 × 굴림 수로 불어나지 않음) · 남으면 소멸 · 기본위력 빛 2 기준 고정</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>은신 부여 결투 (가칭)</t>
-  </si>
-  <si>
-    <t>자기 부위에 다음 턴 은신 (미정) 누적 + 살수의 감 +(미정)</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>은신 보상 결투 (가칭)</t>
-  </si>
-  <si>
-    <t>스킬 시작 시 사용 부위가 은신이면 확정 추가 피해 (미정)</t>
-  </si>
-  <si>
-    <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음</t>
-  </si>
-  <si>
-    <t>공용</t>
-  </si>
-  <si>
-    <t>방어도 +12</t>
-  </si>
-  <si>
-    <t>그 턴 모든 합 판정값 +1</t>
-  </si>
-  <si>
-    <t>노림수</t>
-  </si>
-  <si>
-    <t>그 턴 코인 앞면 확률 +10%p</t>
-  </si>
-  <si>
-    <t>선금 받기</t>
-  </si>
-  <si>
-    <t>그 턴 코인 뒷면 값 +2</t>
-  </si>
-  <si>
-    <t>환형(공격)</t>
-  </si>
-  <si>
-    <t>무기 교체(다음 턴) + 그 턴 위력 +2 (교체 전 무기 기준)</t>
-  </si>
-  <si>
-    <t>… +4</t>
-  </si>
-  <si>
-    <t>… +8</t>
-  </si>
-  <si>
-    <t>환형(수비)와 택1 장착</t>
-  </si>
-  <si>
-    <t>환형(수비)</t>
-  </si>
-  <si>
-    <t>무기 교체(다음 턴) + 그 턴 방어도 +30</t>
-  </si>
-  <si>
-    <t>환형(공격)과 택1 장착</t>
-  </si>
-  <si>
-    <t>기회를 엿보다</t>
-  </si>
-  <si>
-    <t>살수의 감 +1</t>
-  </si>
-  <si>
-    <t>숨을 죽이다</t>
-  </si>
-  <si>
-    <t>살수의 감 (미정) 소비 시도 → 방어도 +(미정)</t>
-  </si>
-  <si>
-    <t>구 「표식 소모」 폐기 — 도사림은 상대를 조준하지 않는다</t>
-  </si>
-  <si>
-    <t>칼을 갈다</t>
-  </si>
-  <si>
-    <t>살수의 감 (미정) 소비 시도 → 다음 턴 신속 (미정)</t>
-  </si>
-  <si>
-    <t>손질하다</t>
-  </si>
-  <si>
-    <t>지금 든 무기를 손질 상태로 → 다음 턴 그 무기로 이긴 굴림의 낙점 +(미정) (3굴림)</t>
-  </si>
-  <si>
     <t>… (1굴림)</t>
   </si>
   <si>
@@ -1650,7 +1665,7 @@
     <t>집행 4</t>
   </si>
   <si>
-    <t>이 스킬의 표식이 직접 44 발화를 일으키면 현재 무기의 원래 발화 효과 2배</t>
+    <t>이 스킬의 표식이 직접 44 발화를 일으키면 그 발화 결과를 한 번 더 반복(공명 덫으로 강화된 발화면 강화 발화 반복)</t>
   </si>
   <si>
     <t>그 턴에 발화가 있었다는 것만으로는 안 됨</t>
@@ -3539,7 +3554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B88A98-0015-4874-9AD7-EE414194D85D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E44A681-0E89-45F9-94DA-22524FEA4DB2}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3733,7 +3748,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0652A123-0323-41B5-B9F6-D7486214FC9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA9EEF0C-863E-4131-B0D4-42D8983C9831}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7289,15 +7304,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{0652A123-0323-41B5-B9F6-D7486214FC9C}"/>
+  <autoFilter ref="A1:T57" xr:uid="{BA9EEF0C-863E-4131-B0D4-42D8983C9831}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22281FC6-C817-4477-B5B4-ADB23937FF79}">
-  <dimension ref="A1:M55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED9C3D5-5796-40D4-92CF-B834BDCB6ECD}">
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
@@ -7517,7 +7532,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>52</v>
       </c>
@@ -8102,7 +8117,7 @@
         <v>411</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>262</v>
+        <v>99</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>1</v>
@@ -8143,7 +8158,7 @@
         <v>413</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>1</v>
@@ -8214,7 +8229,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>178</v>
       </c>
@@ -8553,34 +8568,34 @@
         <v>459</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>1</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>460</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>461</v>
+        <v>342</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>462</v>
+        <v>342</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>387</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9" t="s">
         <v>106</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8588,10 +8603,10 @@
         <v>178</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>86</v>
@@ -8600,22 +8615,22 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="H32" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="J32" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>342</v>
-      </c>
       <c r="K32" s="9" t="s">
-        <v>1</v>
+        <v>387</v>
       </c>
       <c r="L32" s="9" t="s">
         <v>106</v>
@@ -8624,7 +8639,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>178</v>
       </c>
@@ -8641,19 +8656,19 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="G33" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>472</v>
-      </c>
       <c r="I33" s="10" t="s">
-        <v>473</v>
+        <v>342</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>474</v>
+        <v>342</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>1</v>
@@ -8662,39 +8677,39 @@
         <v>106</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>178</v>
       </c>
       <c r="B34" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="H34" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="I34" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="H34" s="10" t="s">
+      <c r="J34" s="10" t="s">
         <v>478</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>342</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>1</v>
@@ -8703,7 +8718,7 @@
         <v>106</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>1</v>
+        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8711,13 +8726,13 @@
         <v>178</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>262</v>
+        <v>99</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>1</v>
@@ -8729,7 +8744,7 @@
         <v>398</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>342</v>
@@ -8744,48 +8759,48 @@
         <v>106</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="B36" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="H36" s="8" t="s">
+      <c r="C36" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="D36" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="J36" s="8" t="s">
+      <c r="J36" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="K36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>1</v>
+      <c r="K36" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -8793,10 +8808,10 @@
         <v>268</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>1</v>
@@ -8805,13 +8820,13 @@
         <v>270</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>271</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>342</v>
@@ -8834,16 +8849,16 @@
         <v>268</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>278</v>
+        <v>487</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>486</v>
+        <v>274</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>111</v>
@@ -8852,7 +8867,7 @@
         <v>271</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>342</v>
@@ -8878,7 +8893,7 @@
         <v>278</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>1</v>
@@ -8893,7 +8908,7 @@
         <v>271</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>342</v>
@@ -8919,7 +8934,7 @@
         <v>278</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1</v>
@@ -8931,16 +8946,16 @@
         <v>111</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>360</v>
+        <v>271</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>492</v>
+        <v>342</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>493</v>
+        <v>342</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>1</v>
@@ -8949,7 +8964,7 @@
         <v>51</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>494</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -8960,7 +8975,7 @@
         <v>278</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>1</v>
@@ -8975,13 +8990,13 @@
         <v>360</v>
       </c>
       <c r="H41" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="I41" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="I41" s="8" t="s">
-        <v>342</v>
-      </c>
       <c r="J41" s="8" t="s">
-        <v>342</v>
+        <v>497</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>1</v>
@@ -8990,7 +9005,7 @@
         <v>51</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -9001,7 +9016,7 @@
         <v>278</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>1</v>
@@ -9010,13 +9025,13 @@
         <v>278</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>271</v>
+        <v>360</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>342</v>
@@ -9031,10 +9046,10 @@
         <v>51</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>268</v>
       </c>
@@ -9042,7 +9057,7 @@
         <v>278</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>1</v>
@@ -9057,7 +9072,7 @@
         <v>271</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>342</v>
@@ -9069,10 +9084,10 @@
         <v>1</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>502</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -9083,7 +9098,7 @@
         <v>278</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>1</v>
@@ -9098,7 +9113,7 @@
         <v>271</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>342</v>
@@ -9113,7 +9128,7 @@
         <v>106</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -9124,7 +9139,7 @@
         <v>278</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>1</v>
@@ -9133,19 +9148,19 @@
         <v>278</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>262</v>
+        <v>88</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>271</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>473</v>
+        <v>342</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>507</v>
+        <v>342</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>1</v>
@@ -9154,48 +9169,48 @@
         <v>106</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="C46" s="9" t="s">
+      <c r="A46" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="9" t="s">
+      <c r="D46" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="H46" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="F46" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="H46" s="10" t="s">
+      <c r="I46" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="J46" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="K46" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M46" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M46" s="10" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -9203,7 +9218,7 @@
         <v>299</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>514</v>
@@ -9212,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>1</v>
@@ -9221,13 +9236,13 @@
         <v>303</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>342</v>
+        <v>517</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>342</v>
+        <v>518</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>1</v>
@@ -9244,16 +9259,16 @@
         <v>299</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>1</v>
@@ -9262,7 +9277,7 @@
         <v>303</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>342</v>
@@ -9280,59 +9295,59 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="I49" s="8" t="s">
+    <row r="49" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="I49" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="J49" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="K49" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="K49" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>313</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>1</v>
@@ -9341,7 +9356,7 @@
         <v>262</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>524</v>
+        <v>381</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>525</v>
@@ -9362,7 +9377,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>313</v>
       </c>
@@ -9370,10 +9385,10 @@
         <v>527</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>1</v>
@@ -9382,10 +9397,10 @@
         <v>262</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>342</v>
@@ -9400,21 +9415,21 @@
         <v>106</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>313</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>1</v>
@@ -9423,10 +9438,10 @@
         <v>262</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>342</v>
@@ -9441,21 +9456,21 @@
         <v>106</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>313</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>1</v>
@@ -9464,39 +9479,39 @@
         <v>262</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>381</v>
+        <v>529</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>536</v>
+        <v>342</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>537</v>
+        <v>342</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>387</v>
+        <v>1</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>106</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>313</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>534</v>
-      </c>
       <c r="D54" s="7" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>1</v>
@@ -9505,16 +9520,16 @@
         <v>262</v>
       </c>
       <c r="G54" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="H54" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="J54" s="8" t="s">
         <v>542</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>543</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>387</v>
@@ -9523,7 +9538,7 @@
         <v>106</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -9531,13 +9546,13 @@
         <v>313</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>1</v>
@@ -9546,16 +9561,16 @@
         <v>262</v>
       </c>
       <c r="G55" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="H55" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="I55" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="J55" s="8" t="s">
         <v>548</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>549</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>387</v>
@@ -9564,18 +9579,59 @@
         <v>106</v>
       </c>
       <c r="M55" s="8" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M56" s="8" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{22281FC6-C817-4477-B5B4-ADB23937FF79}"/>
+  <autoFilter ref="A1:M56" xr:uid="{CED9C3D5-5796-40D4-92CF-B834BDCB6ECD}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA19418A-BD54-45C4-8354-41F7A372DB91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE593C69-6934-4F9C-B82B-6F444B0C6718}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9593,201 +9649,201 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>138</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>110</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>127</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>111</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{CA19418A-BD54-45C4-8354-41F7A372DB91}"/>
+  <autoFilter ref="A1:O4" xr:uid="{DE593C69-6934-4F9C-B82B-6F444B0C6718}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68DC3E6-3636-4AF8-82E7-4F7ADBA32FD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A454DC6-538E-44FA-AA15-B5A02C582321}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9878,10 +9934,10 @@
         <v>46</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -9920,7 +9976,7 @@
         <v>49</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>1</v>
@@ -9937,10 +9993,10 @@
         <v>67</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -9982,7 +10038,7 @@
         <v>49</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>1</v>
@@ -10002,7 +10058,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
@@ -10041,10 +10097,10 @@
         <v>1</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>1</v>
@@ -10053,7 +10109,7 @@
         <v>51</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10061,10 +10117,10 @@
         <v>52</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>1</v>
@@ -10103,10 +10159,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="R5" s="13" t="s">
         <v>1</v>
@@ -10115,7 +10171,7 @@
         <v>51</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -10126,7 +10182,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1</v>
@@ -10165,10 +10221,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="R6" s="13" t="s">
         <v>1</v>
@@ -10185,10 +10241,10 @@
         <v>67</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>1</v>
@@ -10227,10 +10283,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="R7" s="11" t="s">
         <v>1</v>
@@ -10239,7 +10295,7 @@
         <v>51</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10247,10 +10303,10 @@
         <v>67</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>1</v>
@@ -10289,10 +10345,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="R8" s="11" t="s">
         <v>1</v>
@@ -10301,7 +10357,7 @@
         <v>51</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -10312,7 +10368,7 @@
         <v>68</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>1</v>
@@ -10354,7 +10410,7 @@
         <v>74</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="R9" s="11" t="s">
         <v>1</v>
@@ -10374,16 +10430,16 @@
         <v>416</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>92</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>137</v>
@@ -10395,37 +10451,37 @@
         <v>100</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="S10" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10436,16 +10492,16 @@
         <v>421</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>92</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>110</v>
@@ -10454,40 +10510,40 @@
         <v>111</v>
       </c>
       <c r="I11" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="P11" s="13" t="s">
         <v>632</v>
       </c>
-      <c r="J11" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>634</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>627</v>
-      </c>
       <c r="Q11" s="14" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10498,7 +10554,7 @@
         <v>425</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>1</v>
@@ -10507,7 +10563,7 @@
         <v>92</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>126</v>
@@ -10519,28 +10575,28 @@
         <v>159</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>132</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="R12" s="13" t="s">
         <v>1</v>
@@ -10549,7 +10605,7 @@
         <v>106</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10560,7 +10616,7 @@
         <v>435</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>1</v>
@@ -10569,13 +10625,13 @@
         <v>92</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>110</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>92</v>
@@ -10602,7 +10658,7 @@
         <v>213</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="R13" s="13" t="s">
         <v>1</v>
@@ -10611,7 +10667,7 @@
         <v>106</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
@@ -10622,7 +10678,7 @@
         <v>447</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -10631,7 +10687,7 @@
         <v>92</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>87</v>
@@ -10661,10 +10717,10 @@
         <v>92</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -10684,7 +10740,7 @@
         <v>451</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -10723,10 +10779,10 @@
         <v>92</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -10735,7 +10791,7 @@
         <v>106</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10746,7 +10802,7 @@
         <v>454</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -10758,13 +10814,13 @@
         <v>313</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>1</v>
@@ -10782,22 +10838,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="P16" s="13" t="s">
         <v>213</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="S16" s="13" t="s">
         <v>106</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -10805,10 +10861,10 @@
         <v>178</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -10817,7 +10873,7 @@
         <v>99</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>87</v>
@@ -10847,19 +10903,19 @@
         <v>92</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>106</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -10867,10 +10923,10 @@
         <v>178</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>1</v>
@@ -10912,7 +10968,7 @@
         <v>190</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="R18" s="13" t="s">
         <v>1</v>
@@ -10929,10 +10985,10 @@
         <v>178</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>1</v>
@@ -10974,7 +11030,7 @@
         <v>132</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R19" s="13" t="s">
         <v>1</v>
@@ -10991,10 +11047,10 @@
         <v>178</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>1</v>
@@ -11003,7 +11059,7 @@
         <v>86</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>87</v>
@@ -11036,7 +11092,7 @@
         <v>190</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="R20" s="13" t="s">
         <v>1</v>
@@ -11053,10 +11109,10 @@
         <v>83</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
@@ -11065,7 +11121,7 @@
         <v>92</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>110</v>
@@ -11074,13 +11130,13 @@
         <v>88</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="L21" s="12" t="s">
         <v>1</v>
@@ -11092,22 +11148,22 @@
         <v>1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>142</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="S21" s="11" t="s">
         <v>106</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -11115,10 +11171,10 @@
         <v>83</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>1</v>
@@ -11139,13 +11195,13 @@
         <v>112</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>1</v>
@@ -11154,13 +11210,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>1</v>
@@ -11177,10 +11233,10 @@
         <v>83</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>1</v>
@@ -11222,7 +11278,7 @@
         <v>132</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="R23" s="11" t="s">
         <v>1</v>
@@ -11231,7 +11287,7 @@
         <v>106</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -11239,10 +11295,10 @@
         <v>83</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>1</v>
@@ -11251,7 +11307,7 @@
         <v>92</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>87</v>
@@ -11284,10 +11340,10 @@
         <v>142</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>106</v>
@@ -11301,10 +11357,10 @@
         <v>83</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>1</v>
@@ -11313,7 +11369,7 @@
         <v>92</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>110</v>
@@ -11346,10 +11402,10 @@
         <v>213</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>106</v>
@@ -11363,10 +11419,10 @@
         <v>83</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>1</v>
@@ -11375,7 +11431,7 @@
         <v>92</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>110</v>
@@ -11408,10 +11464,10 @@
         <v>132</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>106</v>
@@ -11425,10 +11481,10 @@
         <v>83</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>1</v>
@@ -11470,7 +11526,7 @@
         <v>132</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="R27" s="11" t="s">
         <v>1</v>
@@ -11487,10 +11543,10 @@
         <v>83</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>1</v>
@@ -11499,7 +11555,7 @@
         <v>92</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>87</v>
@@ -11532,7 +11588,7 @@
         <v>132</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>1</v>
@@ -11549,10 +11605,10 @@
         <v>83</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>1</v>
@@ -11594,7 +11650,7 @@
         <v>74</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="R29" s="11" t="s">
         <v>1</v>
@@ -11611,10 +11667,10 @@
         <v>83</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>1</v>
@@ -11653,10 +11709,10 @@
         <v>92</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="R30" s="11" t="s">
         <v>1</v>
@@ -11673,10 +11729,10 @@
         <v>83</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>1</v>
@@ -11715,10 +11771,10 @@
         <v>92</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="R31" s="11" t="s">
         <v>1</v>
@@ -11727,7 +11783,7 @@
         <v>106</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -11735,7 +11791,7 @@
         <v>268</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>269</v>
@@ -11780,7 +11836,7 @@
         <v>132</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="R32" s="13" t="s">
         <v>1</v>
@@ -11797,7 +11853,7 @@
         <v>268</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>274</v>
@@ -11842,7 +11898,7 @@
         <v>132</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="R33" s="13" t="s">
         <v>1</v>
@@ -11862,7 +11918,7 @@
         <v>416</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -11904,7 +11960,7 @@
         <v>132</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="R34" s="13" t="s">
         <v>1</v>
@@ -11913,7 +11969,7 @@
         <v>106</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
@@ -11924,7 +11980,7 @@
         <v>421</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>1</v>
@@ -11966,7 +12022,7 @@
         <v>132</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="R35" s="13" t="s">
         <v>1</v>
@@ -11975,7 +12031,7 @@
         <v>106</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
@@ -11986,7 +12042,7 @@
         <v>425</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>1</v>
@@ -12028,7 +12084,7 @@
         <v>132</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="R36" s="13" t="s">
         <v>1</v>
@@ -12045,10 +12101,10 @@
         <v>268</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>1</v>
@@ -12090,7 +12146,7 @@
         <v>132</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="R37" s="13" t="s">
         <v>1</v>
@@ -12099,7 +12155,7 @@
         <v>106</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
@@ -12110,7 +12166,7 @@
         <v>430</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -12152,7 +12208,7 @@
         <v>132</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="R38" s="13" t="s">
         <v>1</v>
@@ -12172,7 +12228,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>1</v>
@@ -12214,7 +12270,7 @@
         <v>132</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="R39" s="13" t="s">
         <v>1</v>
@@ -12234,7 +12290,7 @@
         <v>435</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>1</v>
@@ -12276,7 +12332,7 @@
         <v>132</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="R40" s="13" t="s">
         <v>1</v>
@@ -12296,7 +12352,7 @@
         <v>439</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -12338,7 +12394,7 @@
         <v>132</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="R41" s="13" t="s">
         <v>1</v>
@@ -12358,7 +12414,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -12400,7 +12456,7 @@
         <v>132</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="R42" s="13" t="s">
         <v>1</v>
@@ -12420,7 +12476,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>1</v>
@@ -12462,7 +12518,7 @@
         <v>132</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="R43" s="13" t="s">
         <v>1</v>
@@ -12482,7 +12538,7 @@
         <v>300</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>1</v>
@@ -12491,7 +12547,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>1</v>
@@ -12524,7 +12580,7 @@
         <v>303</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="R44" s="11" t="s">
         <v>1</v>
@@ -12544,7 +12600,7 @@
         <v>305</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>1</v>
@@ -12553,7 +12609,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>1</v>
@@ -12586,7 +12642,7 @@
         <v>303</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="R45" s="11" t="s">
         <v>1</v>
@@ -12606,7 +12662,7 @@
         <v>309</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>1</v>
@@ -12648,7 +12704,7 @@
         <v>303</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>1</v>
@@ -12661,14 +12717,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{D68DC3E6-3636-4AF8-82E7-4F7ADBA32FD3}"/>
+  <autoFilter ref="A1:T46" xr:uid="{9A454DC6-538E-44FA-AA15-B5A02C582321}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B15D1E-1C04-4E63-8A35-A2CB73B320C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE6AB55-9456-4293-8942-2A7060C48F73}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12683,7 +12739,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>28</v>
@@ -12692,13 +12748,13 @@
         <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -12706,278 +12762,278 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>749</v>
-      </c>
       <c r="D3" s="10" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>758</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>752</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -12988,19 +13044,19 @@
         <v>65</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -13011,76 +13067,76 @@
         <v>349</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>374</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17" xr:uid="{D3B15D1E-1C04-4E63-8A35-A2CB73B320C1}"/>
+  <autoFilter ref="A1:G17" xr:uid="{1FE6AB55-9456-4293-8942-2A7060C48F73}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5E5BA9-9CC2-4F7C-8594-3D0283D98BE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE13597B-C99E-4385-8BE2-E7B30AF3A5C1}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13094,19 +13150,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>42</v>
@@ -13117,22 +13173,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>51</v>
@@ -13140,22 +13196,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>51</v>
@@ -13163,22 +13219,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>51</v>
@@ -13186,22 +13242,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
@@ -13209,22 +13265,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>51</v>
@@ -13232,22 +13288,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>51</v>
@@ -13255,22 +13311,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>51</v>
@@ -13278,22 +13334,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>51</v>
@@ -13301,22 +13357,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>51</v>
@@ -13324,22 +13380,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>51</v>
@@ -13347,22 +13403,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>51</v>
@@ -13370,22 +13426,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>51</v>
@@ -13393,22 +13449,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>51</v>
@@ -13416,22 +13472,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>51</v>
@@ -13439,22 +13495,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>51</v>
@@ -13462,45 +13518,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>51</v>
@@ -13508,22 +13564,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>51</v>
@@ -13531,22 +13587,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>51</v>
@@ -13554,22 +13610,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>51</v>
@@ -13577,22 +13633,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>51</v>
@@ -13600,22 +13656,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>51</v>
@@ -13623,22 +13679,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>51</v>
@@ -13646,22 +13702,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>51</v>
@@ -13669,22 +13725,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>51</v>
@@ -13692,22 +13748,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>51</v>
@@ -13715,183 +13771,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E32" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>886</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>887</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>51</v>
@@ -13899,68 +13955,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>51</v>
@@ -13968,22 +14024,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>51</v>
@@ -13991,22 +14047,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>51</v>
@@ -14014,22 +14070,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>51</v>
@@ -14037,22 +14093,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>51</v>
@@ -14060,22 +14116,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>51</v>
@@ -14083,45 +14139,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>51</v>
@@ -14129,22 +14185,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>51</v>
@@ -14152,10 +14208,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>299</v>
@@ -14164,10 +14220,10 @@
         <v>111</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>51</v>
@@ -14175,10 +14231,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>299</v>
@@ -14187,10 +14243,10 @@
         <v>111</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>51</v>
@@ -14198,10 +14254,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>299</v>
@@ -14210,10 +14266,10 @@
         <v>111</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>51</v>
@@ -14221,10 +14277,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>299</v>
@@ -14233,10 +14289,10 @@
         <v>110</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>51</v>
@@ -14244,10 +14300,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>299</v>
@@ -14256,10 +14312,10 @@
         <v>110</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>51</v>
@@ -14267,10 +14323,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>299</v>
@@ -14279,10 +14335,10 @@
         <v>110</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>51</v>
@@ -14290,10 +14346,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>299</v>
@@ -14302,10 +14358,10 @@
         <v>87</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>51</v>
@@ -14313,10 +14369,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>299</v>
@@ -14325,10 +14381,10 @@
         <v>87</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>51</v>
@@ -14336,10 +14392,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>299</v>
@@ -14348,10 +14404,10 @@
         <v>87</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>51</v>
@@ -14359,68 +14415,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>51</v>
@@ -14428,22 +14484,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>51</v>
@@ -14451,22 +14507,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>51</v>
@@ -14474,22 +14530,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>51</v>
@@ -14497,22 +14553,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>51</v>
@@ -14520,22 +14576,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>51</v>
@@ -14543,36 +14599,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{EE5E5BA9-9CC2-4F7C-8594-3D0283D98BE8}"/>
+  <autoFilter ref="A1:G64" xr:uid="{FE13597B-C99E-4385-8BE2-E7B30AF3A5C1}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA04409-6403-4F87-8E37-6BD3C29B7527}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB58B4F-40CD-48DB-9632-8329A6F50138}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14586,10 +14642,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>32</v>
@@ -14601,7 +14657,7 @@
         <v>178</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -14609,10 +14665,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>87</v>
@@ -14621,21 +14677,21 @@
         <v>89</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
@@ -14644,21 +14700,21 @@
         <v>112</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>49</v>
@@ -14670,18 +14726,18 @@
         <v>49</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>49</v>
@@ -14693,18 +14749,18 @@
         <v>49</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>87</v>
@@ -14713,21 +14769,21 @@
         <v>159</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>110</v>
@@ -14736,21 +14792,21 @@
         <v>112</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>49</v>
@@ -14762,14 +14818,14 @@
         <v>49</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{4FA04409-6403-4F87-8E37-6BD3C29B7527}"/>
+  <autoFilter ref="A1:G8" xr:uid="{FFB58B4F-40CD-48DB-9632-8329A6F50138}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E32DCC7-5FCD-4376-AD3E-CB46D6A089E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F19E1933-3F7D-4AA7-B14C-D3BAFA21222F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{A32AD390-71C0-48EC-9204-342C5596A2BC}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{8C20D798-809A-45D9-AD38-3D86B6FCA999}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="1267">
   <si>
     <t>Project Abyss — 전투 콘텐츠 명세 (2026-09-25)</t>
   </si>
@@ -270,7 +270,7 @@
     <t>공포</t>
   </si>
   <si>
-    <t>공포 N / T — 대상 굴림 위력 −N. 부여마다 독립 항목, 살아 있는 N 합산</t>
+    <t>공포 T — 크기 없음, 대상 굴림 위력 −1(상수). 재부여 = 남은 턴 max</t>
   </si>
   <si>
     <t>구조 확정(09-28) · 수치 재계산 대기</t>
@@ -915,7 +915,7 @@
     <t>강한</t>
   </si>
   <si>
-    <t>자기 최저 체력 부위 약화 + 광기 2 + 적에게 공포 1 / 3</t>
+    <t>자기 최저 체력 부위 약화 + 광기 2 + 적에게 공포 3턴</t>
   </si>
   <si>
     <t>피의 서약</t>
@@ -960,7 +960,7 @@
     <t>하드 게이트 / 도사림 발동시</t>
   </si>
   <si>
-    <t>지난 턴 짓눌림 종료일 때만 사용 가능. 발동하면 이번 턴 자기 공격 슬롯 속도 계열 강화</t>
+    <t>지난 턴 짓눌림 종료일 때만 사용 가능. 속도 굴림 뒤, 이번 턴 자기 모든 공격 슬롯의 현재 속도를 보정 적용 후 속도 최댓값으로 덮어쓴다(골절 · 신속 반영, 디버프 무시 아님)</t>
   </si>
   <si>
     <t>하드 게이트</t>
@@ -1059,7 +1059,7 @@
     <t>4굴림 사용시</t>
   </si>
   <si>
-    <t>광기 N + 자기 출혈 N 획득. 증가 후 만개면 추가 보상·해당 굴림 위력 강화</t>
+    <t>4번째 사용시 광기 확인 — 만개가 아니면 광기 N + 자기 출혈 N / 이미 만개면 현재 자기 출혈만큼 상대 추가 출혈(자기 출혈 유지)</t>
   </si>
   <si>
     <t>구 전투 시작시 대량 획득·초과분 힘 전환 폐기</t>
@@ -1959,6 +1959,9 @@
     <t>肉斬</t>
   </si>
   <si>
+    <t>육참골단 · 반격</t>
+  </si>
+  <si>
     <t>13~18 · 대박 30</t>
   </si>
   <si>
@@ -1980,6 +1983,9 @@
     <t>骨斷</t>
   </si>
   <si>
+    <t>육참골단 · 반격 · 파괴형</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
@@ -1989,7 +1995,7 @@
     <t>절단 2</t>
   </si>
   <si>
-    <t>(반격). 본체 위력 20 − 실제 뼈 구간 × 4. 만개면 반격 굴림 ×2 + 회복 350 + 조건부 파괴 + 바 +25. 반격 시 뼈 전량 소모</t>
+    <t>(반격) · 파괴형(약화된 부위를 끊는다). 본체 위력 20 − 실제 뼈 구간 × 4. 만개면 모든 반격 타격이 처형 권한 + 반격 굴림 ×2 + 회복 350 + 바 +25</t>
   </si>
   <si>
     <t>반격 · 파괴 권한(만개)</t>
@@ -2028,18 +2034,21 @@
     <t>곱절을 노리다</t>
   </si>
   <si>
+    <t>무난 · 파괴형</t>
+  </si>
+  <si>
+    <t>각 굴림 직전</t>
+  </si>
+  <si>
+    <t>뼈 K를 걸어 승리시 3K 획득, 패배시 K 소실. K 미만이면 배팅 없이 정상 판정</t>
+  </si>
+  <si>
+    <t>운명을 흔들다</t>
+  </si>
+  <si>
     <t>무난</t>
   </si>
   <si>
-    <t>각 굴림 직전</t>
-  </si>
-  <si>
-    <t>뼈 K를 걸어 승리시 3K 획득, 패배시 K 소실. K 미만이면 배팅 없이 정상 판정</t>
-  </si>
-  <si>
-    <t>운명을 흔들다</t>
-  </si>
-  <si>
     <t>목·꽝 정상 / 시고로 자동 승리 / 아라시 자동 승리 + 다음 적 굴림 무효 / 대실패는 위력 0 정상 비교</t>
   </si>
   <si>
@@ -2049,6 +2058,9 @@
     <t>몸에 새기다</t>
   </si>
   <si>
+    <t>육참골단 · 성장 · 4단계 파괴형</t>
+  </si>
+  <si>
     <t>1 → 4</t>
   </si>
   <si>
@@ -2070,6 +2082,9 @@
     <t>굴림 도감</t>
   </si>
   <si>
+    <t>무난 · 반격</t>
+  </si>
+  <si>
     <t>트리거 재정의 대기</t>
   </si>
   <si>
@@ -2082,6 +2097,9 @@
     <t>도발형</t>
   </si>
   <si>
+    <t>육참골단</t>
+  </si>
+  <si>
     <t>다음 턴 자기 부위 도발 예약 · 승리시 다음 턴 견고 + 핏값</t>
   </si>
   <si>
@@ -2094,6 +2112,9 @@
     <t>판을 엎다</t>
   </si>
   <si>
+    <t>과부화 · 파괴형</t>
+  </si>
+  <si>
     <t>양수 기세를 전량 소모. 소모량 비례 1굴림 위력·2굴림 뼈, 3굴림 승리시 골절. 침체 대가는 뼈 비용으로 면제</t>
   </si>
   <si>
@@ -2130,7 +2151,7 @@
     <t>사용시 / 합 종료시</t>
   </si>
   <si>
-    <t>뼈 비용 지불(가불 우선), 실패 처리 미정 · 다음 턴 속도 −1 · 완전 차단이면 가불 획득</t>
+    <t>뼈 비용 지불 시도(가불 우선) — 성공하면 속도 페널티 없음 / 실패하면 다음 턴 속도 −1. 합 종료시 완전 차단이면 지불 여부와 무관하게 가불 획득</t>
   </si>
   <si>
     <t>③</t>
@@ -2196,7 +2217,7 @@
     <t>골절 부여형</t>
   </si>
   <si>
-    <t>다음 턴 상대에게 골절 부여. 굴림별/카드당 1회 여부 미정</t>
+    <t>각 굴림 승리시 다음 턴 상대에게 골절 N / 1 — 굴림마다 독립(2승이면 합 2N)</t>
   </si>
   <si>
     <t>⑩</t>
@@ -2214,10 +2235,10 @@
     <t>빚지기</t>
   </si>
   <si>
-    <t>사용시 / 다음 턴 시작</t>
-  </si>
-  <si>
-    <t>빛 +1 즉시. 다음 턴 뼈 비용 미납 시 그 턴 최대 빛 −1</t>
+    <t>사용시 / 이번 턴 종료 시</t>
+  </si>
+  <si>
+    <t>빛 +1 즉시. 이번 턴 종료 시 실제 뼈 N 상환(가불 불가) — 실패하면 다음 턴 최대 빛 −1</t>
   </si>
   <si>
     <t>가불은 턴 종료에 사라져 다음 턴 비용에 못 씀</t>
@@ -2286,7 +2307,7 @@
     <t>상호 쇠약형</t>
   </si>
   <si>
-    <t>자신과 상대에게 같은 쇠약 부여</t>
+    <t>자신과 상대(개체 전체)에게 같은 쇠약 N / T. 쇠약은 부위 상태가 아니다. 도사림 자기 효과 원칙의 명시적 예외 — 자기 쇠약만 정화해 상대에게 남기는 연계</t>
   </si>
   <si>
     <t>기세 바 태우기형</t>
@@ -2472,16 +2493,19 @@
     <t>고통</t>
   </si>
   <si>
-    <t>걸려 있는 동안 회복량과 흐트러짐 회복량 절반(버림 · 최소 1, 거듭하지 않음). N의 효과 (미정)</t>
-  </si>
-  <si>
-    <t>부여마다 독립 항목</t>
-  </si>
-  <si>
-    <t>대상 굴림 위력 −N</t>
-  </si>
-  <si>
-    <t>올라프. 부여마다 독립 항목, N 합산</t>
+    <t>T만(크기 없음)</t>
+  </si>
+  <si>
+    <t>걸려 있는 동안 체력 · 흐트러짐 회복량 절반(버림 · 최소 1). 재부여 = 남은 턴 max</t>
+  </si>
+  <si>
+    <t>크기 중첩 없음</t>
+  </si>
+  <si>
+    <t>대상 굴림 위력 −1(상수). 재부여 = 남은 턴 max</t>
+  </si>
+  <si>
+    <t>올라프. 크기 중첩 없음</t>
   </si>
   <si>
     <t>표식이 실제로 쌓일 때마다 추가 표식 +N</t>
@@ -4361,7 +4385,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B888A2-F743-436D-90CA-5E7BB82CB861}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651E81E6-8561-47B1-88EC-A56BA6CAC177}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4555,7 +4579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33EE02D8-E793-49C4-86A1-C802B687DE85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0635ACD-2DD3-4842-8C4B-859D881DA394}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4565,93 +4589,93 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10" xr:uid="{33EE02D8-E793-49C4-86A1-C802B687DE85}"/>
+  <autoFilter ref="A1:B10" xr:uid="{F0635ACD-2DD3-4842-8C4B-859D881DA394}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC006EAF-5047-4EAD-B04C-D24E927D189A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94380A0F-5B12-46AF-9C4F-A9B967BB9662}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4661,19 +4685,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -4681,56 +4705,56 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -4741,93 +4765,93 @@
     </row>
     <row r="5" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{CC006EAF-5047-4EAD-B04C-D24E927D189A}"/>
+  <autoFilter ref="A1:F8" xr:uid="{94380A0F-5B12-46AF-9C4F-A9B967BB9662}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFEDAC3E-4A7A-411F-AB12-298AAF7958D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04522843-D6D1-4C27-B7F5-3840D133A5B8}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4837,16 +4861,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>45</v>
@@ -4854,16 +4878,16 @@
     </row>
     <row r="2" spans="1:5" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -4871,81 +4895,81 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6" xr:uid="{EFEDAC3E-4A7A-411F-AB12-298AAF7958D9}"/>
+  <autoFilter ref="A1:E6" xr:uid="{04522843-D6D1-4C27-B7F5-3840D133A5B8}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6CE0538-4F36-4494-A132-21D6BC3EBA51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD625983-B8A8-4524-BE59-D1CE2D8A66DA}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4955,10 +4979,10 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -4969,7 +4993,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -4983,27 +5007,27 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>1</v>
@@ -5011,13 +5035,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5025,13 +5049,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1</v>
@@ -5039,13 +5063,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>1</v>
@@ -5053,13 +5077,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>1</v>
@@ -5067,7 +5091,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>1</v>
@@ -5081,13 +5105,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1</v>
@@ -5095,13 +5119,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>1</v>
@@ -5109,13 +5133,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>1</v>
@@ -5123,7 +5147,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1</v>
@@ -5137,41 +5161,41 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>1</v>
@@ -5179,13 +5203,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>1</v>
@@ -5193,13 +5217,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>1</v>
@@ -5207,13 +5231,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>1</v>
@@ -5221,13 +5245,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>1</v>
@@ -5235,7 +5259,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>1</v>
@@ -5249,13 +5273,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>1</v>
@@ -5263,13 +5287,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>1</v>
@@ -5277,13 +5301,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1</v>
@@ -5291,7 +5315,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>1</v>
@@ -5305,13 +5329,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1</v>
@@ -5319,27 +5343,27 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1</v>
@@ -5347,13 +5371,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1</v>
@@ -5361,13 +5385,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1</v>
@@ -5375,13 +5399,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1</v>
@@ -5389,13 +5413,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1</v>
@@ -5403,7 +5427,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>1</v>
@@ -5417,13 +5441,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1</v>
@@ -5431,27 +5455,27 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35" xr:uid="{E6CE0538-4F36-4494-A132-21D6BC3EBA51}"/>
+  <autoFilter ref="A1:D35" xr:uid="{FD625983-B8A8-4524-BE59-D1CE2D8A66DA}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9175ED3D-B083-4D8D-9E15-2BFE78359E35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC79B0D-6A09-4E73-B11C-1E35D8B69931}">
   <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5464,7 +5488,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -5475,7 +5499,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -5489,13 +5513,13 @@
     </row>
     <row r="3" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1</v>
@@ -5503,27 +5527,27 @@
     </row>
     <row r="4" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5531,97 +5555,97 @@
     </row>
     <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>1</v>
@@ -5629,13 +5653,13 @@
     </row>
     <row r="13" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1</v>
@@ -5643,21 +5667,21 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>1</v>
@@ -5671,49 +5695,49 @@
     </row>
     <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>1</v>
@@ -5727,7 +5751,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1</v>
@@ -5741,7 +5765,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>1</v>
@@ -5755,7 +5779,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>1</v>
@@ -5769,7 +5793,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>1</v>
@@ -5783,7 +5807,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>1</v>
@@ -5797,7 +5821,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>1</v>
@@ -5811,7 +5835,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>1</v>
@@ -5825,7 +5849,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>1</v>
@@ -5839,7 +5863,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>1</v>
@@ -5853,7 +5877,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>1</v>
@@ -5867,7 +5891,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>1</v>
@@ -5881,7 +5905,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>1</v>
@@ -5895,7 +5919,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>1</v>
@@ -5909,7 +5933,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>1</v>
@@ -5923,7 +5947,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>1</v>
@@ -5937,7 +5961,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>1</v>
@@ -5951,7 +5975,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>1</v>
@@ -5965,7 +5989,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>1</v>
@@ -5979,7 +6003,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>1</v>
@@ -5993,7 +6017,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>1</v>
@@ -6007,7 +6031,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>1</v>
@@ -6021,7 +6045,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>1</v>
@@ -6035,7 +6059,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>1</v>
@@ -6049,7 +6073,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>1</v>
@@ -6063,7 +6087,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>1</v>
@@ -6077,7 +6101,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>1</v>
@@ -6091,7 +6115,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>1</v>
@@ -6105,7 +6129,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>1</v>
@@ -6119,7 +6143,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>1</v>
@@ -6133,7 +6157,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>1</v>
@@ -6147,7 +6171,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>1</v>
@@ -6161,7 +6185,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>1</v>
@@ -6175,7 +6199,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>1</v>
@@ -6189,7 +6213,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>1</v>
@@ -6203,7 +6227,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>1</v>
@@ -6217,7 +6241,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>1</v>
@@ -6231,55 +6255,55 @@
     </row>
     <row r="56" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>1</v>
@@ -6287,105 +6311,105 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>1</v>
@@ -6399,13 +6423,13 @@
     </row>
     <row r="68" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>1</v>
@@ -6413,13 +6437,13 @@
     </row>
     <row r="69" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>1</v>
@@ -6427,13 +6451,13 @@
     </row>
     <row r="70" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>1</v>
@@ -6441,7 +6465,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>1</v>
@@ -6455,7 +6479,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>1</v>
@@ -6469,7 +6493,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>1</v>
@@ -6483,7 +6507,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>1</v>
@@ -6497,7 +6521,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>1</v>
@@ -6511,7 +6535,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>1</v>
@@ -6525,7 +6549,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>1</v>
@@ -6539,7 +6563,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>1</v>
@@ -6553,13 +6577,13 @@
     </row>
     <row r="79" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>1</v>
@@ -6567,7 +6591,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>1</v>
@@ -6581,7 +6605,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>1</v>
@@ -6595,7 +6619,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>1</v>
@@ -6609,7 +6633,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>1</v>
@@ -6623,7 +6647,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>1</v>
@@ -6637,7 +6661,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>1</v>
@@ -6651,7 +6675,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>1</v>
@@ -6665,7 +6689,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>1</v>
@@ -6679,7 +6703,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>1</v>
@@ -6692,14 +6716,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D88" xr:uid="{9175ED3D-B083-4D8D-9E15-2BFE78359E35}"/>
+  <autoFilter ref="A1:D88" xr:uid="{1EC79B0D-6A09-4E73-B11C-1E35D8B69931}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386A7E17-D583-4906-B4D2-20F21E7116F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2CF04E-13F7-4B51-9DC9-7D1B021409CA}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9510,7 +9534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>271</v>
       </c>
@@ -10255,14 +10279,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{386A7E17-D583-4906-B4D2-20F21E7116F6}"/>
+  <autoFilter ref="A1:T57" xr:uid="{3E2CF04E-13F7-4B51-9DC9-7D1B021409CA}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F258DA-8634-4D16-93A8-5538FB3DC362}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685FEAA4-17E6-4B56-9D91-AD0C60D538DB}">
   <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12534,14 +12558,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{87F258DA-8634-4D16-93A8-5538FB3DC362}"/>
+  <autoFilter ref="A1:M55" xr:uid="{685FEAA4-17E6-4B56-9D91-AD0C60D538DB}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFB27F1-DC13-4BAD-9C19-DD5471BB405A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58420B8B-909B-4B37-90AE-7038F54253D4}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12746,14 +12770,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{5BFB27F1-DC13-4BAD-9C19-DD5471BB405A}"/>
+  <autoFilter ref="A1:O4" xr:uid="{58420B8B-909B-4B37-90AE-7038F54253D4}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B8D5A2C-787F-4102-9E2F-77B15D8615FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA90B2A-03AB-4DCC-B79F-178F168417BE}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12847,7 +12871,7 @@
         <v>599</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -13346,10 +13370,10 @@
         <v>629</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>139</v>
@@ -13361,28 +13385,28 @@
         <v>102</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="R10" s="13" t="s">
         <v>616</v>
@@ -13391,7 +13415,7 @@
         <v>51</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13402,16 +13426,16 @@
         <v>424</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>112</v>
@@ -13420,13 +13444,13 @@
         <v>113</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L11" s="14" t="s">
         <v>1</v>
@@ -13438,22 +13462,22 @@
         <v>1</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13464,16 +13488,16 @@
         <v>428</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>128</v>
@@ -13485,28 +13509,28 @@
         <v>161</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>134</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R12" s="13" t="s">
         <v>1</v>
@@ -13515,7 +13539,7 @@
         <v>108</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13526,22 +13550,22 @@
         <v>438</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>112</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>94</v>
@@ -13568,7 +13592,7 @@
         <v>215</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="R13" s="13" t="s">
         <v>1</v>
@@ -13577,7 +13601,7 @@
         <v>108</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
@@ -13585,19 +13609,19 @@
         <v>180</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>89</v>
@@ -13627,10 +13651,10 @@
         <v>94</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -13650,16 +13674,16 @@
         <v>450</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1</v>
+        <v>659</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>112</v>
@@ -13692,7 +13716,7 @@
         <v>623</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -13701,7 +13725,7 @@
         <v>108</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13712,25 +13736,25 @@
         <v>453</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>316</v>
+        <v>663</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>1</v>
@@ -13754,16 +13778,16 @@
         <v>215</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="S16" s="13" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13774,7 +13798,7 @@
         <v>462</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -13783,7 +13807,7 @@
         <v>101</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>616</v>
+        <v>671</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>89</v>
@@ -13813,10 +13837,10 @@
         <v>94</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="R17" s="13" t="s">
         <v>616</v>
@@ -13825,7 +13849,7 @@
         <v>108</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -13836,7 +13860,7 @@
         <v>472</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>1</v>
@@ -13845,7 +13869,7 @@
         <v>101</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>1</v>
+        <v>676</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>112</v>
@@ -13878,7 +13902,7 @@
         <v>192</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="R18" s="13" t="s">
         <v>1</v>
@@ -13898,16 +13922,16 @@
         <v>480</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>1</v>
+        <v>645</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>94</v>
@@ -13940,7 +13964,7 @@
         <v>134</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="R19" s="13" t="s">
         <v>1</v>
@@ -13960,7 +13984,7 @@
         <v>468</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>1</v>
@@ -13969,7 +13993,7 @@
         <v>88</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>643</v>
+        <v>681</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>89</v>
@@ -14002,7 +14026,7 @@
         <v>192</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="R20" s="13" t="s">
         <v>1</v>
@@ -14019,16 +14043,16 @@
         <v>85</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>616</v>
@@ -14040,13 +14064,13 @@
         <v>90</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L21" s="12" t="s">
         <v>1</v>
@@ -14058,13 +14082,13 @@
         <v>1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>144</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="R21" s="11" t="s">
         <v>616</v>
@@ -14073,7 +14097,7 @@
         <v>108</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -14081,16 +14105,16 @@
         <v>85</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>1</v>
@@ -14105,13 +14129,13 @@
         <v>114</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>1</v>
@@ -14120,13 +14144,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>1</v>
@@ -14143,16 +14167,16 @@
         <v>85</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>1</v>
@@ -14188,7 +14212,7 @@
         <v>134</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="R23" s="11" t="s">
         <v>1</v>
@@ -14197,7 +14221,7 @@
         <v>108</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -14205,16 +14229,16 @@
         <v>85</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>616</v>
@@ -14250,7 +14274,7 @@
         <v>144</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="R24" s="11" t="s">
         <v>616</v>
@@ -14267,16 +14291,16 @@
         <v>85</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>616</v>
@@ -14312,7 +14336,7 @@
         <v>215</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="R25" s="11" t="s">
         <v>616</v>
@@ -14329,16 +14353,16 @@
         <v>85</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>616</v>
@@ -14374,7 +14398,7 @@
         <v>134</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="R26" s="11" t="s">
         <v>616</v>
@@ -14391,16 +14415,16 @@
         <v>85</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>1</v>
@@ -14436,7 +14460,7 @@
         <v>134</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="R27" s="11" t="s">
         <v>1</v>
@@ -14453,19 +14477,19 @@
         <v>85</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>89</v>
@@ -14498,7 +14522,7 @@
         <v>134</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>1</v>
@@ -14515,16 +14539,16 @@
         <v>85</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>1</v>
@@ -14560,7 +14584,7 @@
         <v>76</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="R29" s="11" t="s">
         <v>1</v>
@@ -14577,16 +14601,16 @@
         <v>85</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>1</v>
@@ -14622,7 +14646,7 @@
         <v>623</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="R30" s="11" t="s">
         <v>1</v>
@@ -14639,16 +14663,16 @@
         <v>85</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>1</v>
@@ -14681,10 +14705,10 @@
         <v>94</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="R31" s="11" t="s">
         <v>1</v>
@@ -14693,7 +14717,7 @@
         <v>108</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -14828,7 +14852,7 @@
         <v>419</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -14870,7 +14894,7 @@
         <v>134</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="R34" s="13" t="s">
         <v>1</v>
@@ -14879,7 +14903,7 @@
         <v>108</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
@@ -14890,7 +14914,7 @@
         <v>424</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>1</v>
@@ -14932,7 +14956,7 @@
         <v>134</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="R35" s="13" t="s">
         <v>1</v>
@@ -14941,7 +14965,7 @@
         <v>108</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
@@ -14952,7 +14976,7 @@
         <v>428</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>1</v>
@@ -14994,7 +15018,7 @@
         <v>134</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="R36" s="13" t="s">
         <v>1</v>
@@ -15011,10 +15035,10 @@
         <v>271</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>1</v>
@@ -15056,7 +15080,7 @@
         <v>134</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="R37" s="13" t="s">
         <v>1</v>
@@ -15065,7 +15089,7 @@
         <v>108</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
@@ -15076,7 +15100,7 @@
         <v>433</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -15118,7 +15142,7 @@
         <v>134</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="R38" s="13" t="s">
         <v>1</v>
@@ -15138,7 +15162,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>1</v>
@@ -15180,7 +15204,7 @@
         <v>134</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="R39" s="13" t="s">
         <v>1</v>
@@ -15200,7 +15224,7 @@
         <v>438</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>1</v>
@@ -15242,7 +15266,7 @@
         <v>134</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="R40" s="13" t="s">
         <v>1</v>
@@ -15262,7 +15286,7 @@
         <v>442</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -15304,7 +15328,7 @@
         <v>134</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="R41" s="13" t="s">
         <v>1</v>
@@ -15316,7 +15340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>271</v>
       </c>
@@ -15324,7 +15348,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -15363,10 +15387,10 @@
         <v>1</v>
       </c>
       <c r="P42" s="13" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="R42" s="13" t="s">
         <v>1</v>
@@ -15386,7 +15410,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>1</v>
@@ -15428,7 +15452,7 @@
         <v>134</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="R43" s="13" t="s">
         <v>1</v>
@@ -15448,7 +15472,7 @@
         <v>303</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>1</v>
@@ -15490,7 +15514,7 @@
         <v>306</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="R44" s="11" t="s">
         <v>1</v>
@@ -15510,7 +15534,7 @@
         <v>308</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>1</v>
@@ -15552,7 +15576,7 @@
         <v>306</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="R45" s="11" t="s">
         <v>1</v>
@@ -15572,7 +15596,7 @@
         <v>312</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>1</v>
@@ -15614,7 +15638,7 @@
         <v>306</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>1</v>
@@ -15627,14 +15651,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{2B8D5A2C-787F-4102-9E2F-77B15D8615FC}"/>
+  <autoFilter ref="A1:T46" xr:uid="{6AA90B2A-03AB-4DCC-B79F-178F168417BE}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B31B9B-35CD-4867-8911-5CF33BD98E77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34419D5-C91B-48A1-BE76-F54402D77F9B}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15649,7 +15673,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>28</v>
@@ -15658,13 +15682,13 @@
         <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -15672,301 +15696,301 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>764</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>757</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>792</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>793</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>768</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>794</v>
+      <c r="A13" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>795</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>768</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>796</v>
+      <c r="C14" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -15977,148 +16001,148 @@
         <v>352</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>377</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>80</v>
@@ -16127,18 +16151,18 @@
         <v>49</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21" xr:uid="{B1B31B9B-35CD-4867-8911-5CF33BD98E77}"/>
+  <autoFilter ref="A1:G21" xr:uid="{E34419D5-C91B-48A1-BE76-F54402D77F9B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9B1CBB-01AC-43DB-A50A-52EBA2BD83AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3041902F-B9FB-4086-B4A4-4CAA7D51550C}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16152,19 +16176,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>42</v>
@@ -16175,22 +16199,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>51</v>
@@ -16198,22 +16222,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>51</v>
@@ -16221,22 +16245,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>51</v>
@@ -16244,22 +16268,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
@@ -16267,22 +16291,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>51</v>
@@ -16290,22 +16314,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>51</v>
@@ -16313,22 +16337,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>51</v>
@@ -16336,22 +16360,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>51</v>
@@ -16359,22 +16383,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>51</v>
@@ -16382,22 +16406,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>51</v>
@@ -16405,22 +16429,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>51</v>
@@ -16428,22 +16452,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>51</v>
@@ -16451,22 +16475,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>51</v>
@@ -16474,22 +16498,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>51</v>
@@ -16497,22 +16521,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>51</v>
@@ -16520,45 +16544,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>51</v>
@@ -16566,22 +16590,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>51</v>
@@ -16589,22 +16613,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>51</v>
@@ -16612,22 +16636,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>51</v>
@@ -16635,22 +16659,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>51</v>
@@ -16658,22 +16682,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>51</v>
@@ -16681,22 +16705,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>51</v>
@@ -16704,22 +16728,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>51</v>
@@ -16727,22 +16751,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>51</v>
@@ -16750,22 +16774,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>51</v>
@@ -16773,183 +16797,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="F33" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>912</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>51</v>
@@ -16957,68 +16981,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>51</v>
@@ -17026,22 +17050,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>51</v>
@@ -17049,22 +17073,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>51</v>
@@ -17072,22 +17096,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>51</v>
@@ -17095,22 +17119,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>51</v>
@@ -17118,22 +17142,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>51</v>
@@ -17141,45 +17165,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>51</v>
@@ -17187,22 +17211,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>51</v>
@@ -17210,10 +17234,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>302</v>
@@ -17222,10 +17246,10 @@
         <v>113</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>51</v>
@@ -17233,10 +17257,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>302</v>
@@ -17245,10 +17269,10 @@
         <v>113</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>51</v>
@@ -17256,10 +17280,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>302</v>
@@ -17268,10 +17292,10 @@
         <v>113</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>51</v>
@@ -17279,10 +17303,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>302</v>
@@ -17291,10 +17315,10 @@
         <v>112</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>51</v>
@@ -17302,10 +17326,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>302</v>
@@ -17314,10 +17338,10 @@
         <v>112</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>51</v>
@@ -17325,10 +17349,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>302</v>
@@ -17337,10 +17361,10 @@
         <v>112</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>51</v>
@@ -17348,10 +17372,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>302</v>
@@ -17360,10 +17384,10 @@
         <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>51</v>
@@ -17371,10 +17395,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>302</v>
@@ -17383,10 +17407,10 @@
         <v>89</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>51</v>
@@ -17394,10 +17418,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>302</v>
@@ -17406,10 +17430,10 @@
         <v>89</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>51</v>
@@ -17417,68 +17441,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>51</v>
@@ -17486,22 +17510,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>51</v>
@@ -17509,22 +17533,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>51</v>
@@ -17532,22 +17556,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>51</v>
@@ -17555,22 +17579,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>51</v>
@@ -17578,22 +17602,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>51</v>
@@ -17601,36 +17625,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{AA9B1CBB-01AC-43DB-A50A-52EBA2BD83AA}"/>
+  <autoFilter ref="A1:G64" xr:uid="{3041902F-B9FB-4086-B4A4-4CAA7D51550C}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3951F689-9769-4B79-917E-103AE7BAD644}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEEF81A9-AC88-4C3A-80A6-6CB7867DA6B0}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17644,10 +17668,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>32</v>
@@ -17659,7 +17683,7 @@
         <v>180</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -17667,10 +17691,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>89</v>
@@ -17679,21 +17703,21 @@
         <v>91</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
@@ -17702,21 +17726,21 @@
         <v>114</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>49</v>
@@ -17728,18 +17752,18 @@
         <v>49</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>49</v>
@@ -17751,18 +17775,18 @@
         <v>49</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>89</v>
@@ -17771,21 +17795,21 @@
         <v>161</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>112</v>
@@ -17794,21 +17818,21 @@
         <v>114</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>49</v>
@@ -17820,21 +17844,21 @@
         <v>49</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{3951F689-9769-4B79-917E-103AE7BAD644}"/>
+  <autoFilter ref="A1:G8" xr:uid="{CEEF81A9-AC88-4C3A-80A6-6CB7867DA6B0}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5CE218-9EA1-4424-91CB-78396D439BED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF92E6A-7109-4B29-9ABE-2ED5B1A20D1F}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17844,19 +17868,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -17864,66 +17888,66 @@
     </row>
     <row r="2" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{AC5CE218-9EA1-4424-91CB-78396D439BED}"/>
+  <autoFilter ref="A1:F4" xr:uid="{CAF92E6A-7109-4B29-9ABE-2ED5B1A20D1F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-Onedrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42B065A3-1971-4072-9D6E-7F648C565022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6CB2DE6-2C40-444D-B6F9-FBF560A2573C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{7C6754F7-B4DA-4BF8-8C21-C1879D816020}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{4FD8DE85-2159-414B-9B9D-5F75F99ECF06}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="1262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="1274">
   <si>
     <t>Project Abyss — 전투 콘텐츠 명세 (2026-09-25)</t>
   </si>
@@ -531,117 +531,117 @@
     <t>틈을 파고들다</t>
   </si>
   <si>
+    <t>피해 처리 뒤</t>
+  </si>
+  <si>
+    <t>다수전 연쇄형 — 대상을 약화 · 파괴 · 흐트러짐으로 만들면 이번 스킬로 아직 안 친 다른 무작위 생존 적에게 추가타 1회, 조건을 만족하면 다시 이어짐(같은 적 재공격 없음 · 단일 적이면 연쇄 없음)</t>
+  </si>
+  <si>
+    <t>재굴림 아님 · 추가타 위력 처리 (미정) · 구 균열 / 흐트러짐 증폭 / 3굴림 폐기 · 기존 ID OL-B12</t>
+  </si>
+  <si>
+    <t>활성 9</t>
+  </si>
+  <si>
+    <t>선수치기</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>18~23</t>
+  </si>
+  <si>
+    <t>다음 턴 이 슬롯 속도 굴림값을 최댓값으로 고정. 2굴림 별도 고유 효과 없음</t>
+  </si>
+  <si>
+    <t>기존 ID OL-B13</t>
+  </si>
+  <si>
+    <t>활성 10</t>
+  </si>
+  <si>
+    <t>약점을 노리다</t>
+  </si>
+  <si>
+    <t>11~16</t>
+  </si>
+  <si>
+    <t>17~24</t>
+  </si>
+  <si>
+    <t>승리시 / 3굴림 사용시</t>
+  </si>
+  <si>
+    <t>1굴림 승리시 다음 턴 쇠약 1만큼 3턴 · 2굴림 승리시 현재 출혈 5 이상이면 다음 턴 균열 1 · 3굴림 사용시 상대 부정적 상태 1종당 해당 굴림 위력 +1</t>
+  </si>
+  <si>
+    <t>앞 굴림이 붙인 상태 포함 · 기존 ID OL-B14</t>
+  </si>
+  <si>
+    <t>활성 11</t>
+  </si>
+  <si>
+    <t>저며내기</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>16~19</t>
+  </si>
+  <si>
+    <t>20~32</t>
+  </si>
+  <si>
+    <t>2굴림 승리시</t>
+  </si>
+  <si>
+    <t>2굴림 승리시 상대 출혈 2 + 자신에게 자기 출혈 1</t>
+  </si>
+  <si>
+    <t>기존 ID OL-B17</t>
+  </si>
+  <si>
+    <t>결투</t>
+  </si>
+  <si>
+    <t>표준</t>
+  </si>
+  <si>
+    <t>블로드외른 · blóðörn</t>
+  </si>
+  <si>
+    <t>파괴형</t>
+  </si>
+  <si>
+    <t>14~21</t>
+  </si>
+  <si>
+    <t>15~20</t>
+  </si>
+  <si>
+    <t>각 굴림 승리시 대상 출혈 폭발</t>
+  </si>
+  <si>
+    <t>파괴 권한 · 폭발</t>
+  </si>
+  <si>
+    <t>기존 ID OL-D01</t>
+  </si>
+  <si>
+    <t>끈질기게</t>
+  </si>
+  <si>
+    <t>홀름강 · hólmganga</t>
+  </si>
+  <si>
+    <t>유틸형</t>
+  </si>
+  <si>
     <t>15~22</t>
   </si>
   <si>
-    <t>17~29</t>
-  </si>
-  <si>
-    <t>1·2굴림 승리시 상대 균열 (미정). 3굴림 승리시 피해 적용 직전 상대 흐트러짐이 기준 (미정) 이하라면 그 굴림 흐트러짐 피해 증폭</t>
-  </si>
-  <si>
-    <t>소급 판정 없음 · 기존 ID OL-B12</t>
-  </si>
-  <si>
-    <t>활성 9</t>
-  </si>
-  <si>
-    <t>선수치기</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>18~23</t>
-  </si>
-  <si>
-    <t>다음 턴 이 슬롯 속도 굴림값을 최댓값으로 고정. 2굴림 별도 고유 효과 없음</t>
-  </si>
-  <si>
-    <t>기존 ID OL-B13</t>
-  </si>
-  <si>
-    <t>활성 10</t>
-  </si>
-  <si>
-    <t>약점을 노리다</t>
-  </si>
-  <si>
-    <t>11~16</t>
-  </si>
-  <si>
-    <t>17~24</t>
-  </si>
-  <si>
-    <t>승리시 / 3굴림 사용시</t>
-  </si>
-  <si>
-    <t>1굴림 승리시 다음 턴 쇠약 1만큼 3턴 · 2굴림 승리시 현재 출혈 5 이상이면 다음 턴 균열 1 · 3굴림 사용시 상대 부정적 상태 1종당 해당 굴림 위력 +1</t>
-  </si>
-  <si>
-    <t>앞 굴림이 붙인 상태 포함 · 기존 ID OL-B14</t>
-  </si>
-  <si>
-    <t>활성 11</t>
-  </si>
-  <si>
-    <t>저며내기</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>16~19</t>
-  </si>
-  <si>
-    <t>20~32</t>
-  </si>
-  <si>
-    <t>2굴림 승리시</t>
-  </si>
-  <si>
-    <t>2굴림 승리시 상대 출혈 2 + 자신에게 자기 출혈 1</t>
-  </si>
-  <si>
-    <t>기존 ID OL-B17</t>
-  </si>
-  <si>
-    <t>결투</t>
-  </si>
-  <si>
-    <t>표준</t>
-  </si>
-  <si>
-    <t>블로드외른 · blóðörn</t>
-  </si>
-  <si>
-    <t>파괴형</t>
-  </si>
-  <si>
-    <t>14~21</t>
-  </si>
-  <si>
-    <t>15~20</t>
-  </si>
-  <si>
-    <t>각 굴림 승리시 대상 출혈 폭발</t>
-  </si>
-  <si>
-    <t>파괴 권한 · 폭발</t>
-  </si>
-  <si>
-    <t>기존 ID OL-D01</t>
-  </si>
-  <si>
-    <t>끈질기게</t>
-  </si>
-  <si>
-    <t>홀름강 · hólmganga</t>
-  </si>
-  <si>
-    <t>유틸형</t>
-  </si>
-  <si>
     <t>16~21</t>
   </si>
   <si>
@@ -1113,7 +1113,7 @@
     <t>표식 (낙점)</t>
   </si>
   <si>
-    <t>낙점 = 실제 교환에서 이긴 굴림마다 적립(일방 공격 제외) · 상한 44에서 소비하고 발화: 바 푸시 50</t>
+    <t>낙점 = 실제 교환에서 이긴 굴림마다 적립(일방 공격 제외) · 상한 44에서 소비하고 발화: 흐트러짐 피해 (미정)</t>
   </si>
   <si>
     <t>… 발화: 봉인 1턴 (두 곳 동시 가능)</t>
@@ -1146,7 +1146,7 @@
     <t>덫 (폭발 덫 · 공명 덫 · 전염 덫)</t>
   </si>
   <si>
-    <t>부위 단위. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발(RED) = 스택 비례 확정 피해 (미정) / 공명(BLUE) = 발화 자체를 강화 발화로 (미정) / 전염(RED) = 원본 덫 2턴 · 발화 시 전염을 일으킨 적을 뺀 다른 적들의 생존 부위 중 표식 상위 2개(같은 적 두 부위 허용 · 동률 무작위)에 표식 (미정) + 전염 덫 1 · 전염으로 생긴 덫은 그 턴만 · 연쇄 · 재감염 허용</t>
+    <t>부위 단위. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발(RED) = 스택 비례 확정 피해 (미정) / 공명(BLUE) = 발화 자체를 강화 발화로 — 백우 흐트러짐 피해 증가 (미정) · 적설 봉인 1턴 그대로 + 쇠약 (미정)/1 · 낙일 확정 체력 피해 증가 (미정) / 전염(RED) = 원본 덫 2턴 · 발화 시 전염을 일으킨 적을 뺀 다른 적들의 생존 부위 중 표식 상위 2개(같은 적 두 부위 허용 · 동률 무작위)에 표식 (미정) + 전염 덫 1 · 전염으로 생긴 덫은 그 턴만 · 연쇄 · 재감염 허용</t>
   </si>
   <si>
     <t>덫은 표식을 주지 않음 · 승리 → 덫 설치 → 낙점 → 발화 → 방금 단 덫도 발동</t>
@@ -1272,48 +1272,60 @@
     <t>손에 익히다</t>
   </si>
   <si>
+    <t>전투 시작시 + 승리시(각 굴림)</t>
+  </si>
+  <si>
+    <t>지난 턴 환형 완료(새 무기 첫 턴)여야 사용 가능 · 전투 시작시 살수의 감 +(미정)(스킬 전체 1회) · 굴림 승리시 추가 흐트러짐 피해 +(미정)</t>
+  </si>
+  <si>
+    <t>… · 굴림 승리시 대상 표식 +(미정)</t>
+  </si>
+  <si>
+    <t>… · 굴림 승리시 확정 추가 체력 피해 +(미정)</t>
+  </si>
+  <si>
+    <t>무기별 분기(공통 살수의 감은 굴림 수만큼 반복하지 않음)</t>
+  </si>
+  <si>
+    <t>하드 게이트가 지난 턴 확정 사실이라 허용</t>
+  </si>
+  <si>
+    <t>믿는 구석</t>
+  </si>
+  <si>
+    <t>살수의 감 (미정) 소비 시도 → 성공하면 이 스킬의 모든 굴림을 앞면(크리) 취급</t>
+  </si>
+  <si>
+    <t>확정 크리는 자동 승리가 아님 · 실패해도 스킬은 정상 진행</t>
+  </si>
+  <si>
+    <t>현상수배</t>
+  </si>
+  <si>
+    <t>굴림 1 · 2 · 3에 서로 다른 효과 (미정)</t>
+  </si>
+  <si>
+    <t>굴림 1 · 2에 서로 다른 효과 (미정)</t>
+  </si>
+  <si>
+    <t>강한 1굴림 효과 (미정)</t>
+  </si>
+  <si>
+    <t>무기별 분기 — 같은 효과를 모든 굴림에 반복하지 않음 · 무기별 패키지 가치를 맞춤</t>
+  </si>
+  <si>
+    <t>재설계 대기 · 효과 미정</t>
+  </si>
+  <si>
+    <t>구 「각 굴림 승리시 다음 턴 모든 적에게 같은 효과」 폐기</t>
+  </si>
+  <si>
+    <t>은신 부여 평타 (가칭)</t>
+  </si>
+  <si>
     <t>사용시(각 굴림)</t>
   </si>
   <si>
-    <t>지난 턴 환형 완료(새 무기 첫 턴)여야 사용 가능 · 살수의 감 +(미정) (최대 3회)</t>
-  </si>
-  <si>
-    <t>… (최대 2회)</t>
-  </si>
-  <si>
-    <t>… (최대 1회)</t>
-  </si>
-  <si>
-    <t>하드 게이트가 지난 턴 확정 사실이라 허용</t>
-  </si>
-  <si>
-    <t>믿는 구석</t>
-  </si>
-  <si>
-    <t>살수의 감 (미정) 소비 시도 → 성공하면 이 스킬의 모든 굴림을 앞면(크리) 취급</t>
-  </si>
-  <si>
-    <t>확정 크리는 자동 승리가 아님 · 실패해도 스킬은 정상 진행</t>
-  </si>
-  <si>
-    <t>현상수배</t>
-  </si>
-  <si>
-    <t>다음 턴 모든 적에게 쇠약 (미정)</t>
-  </si>
-  <si>
-    <t>… 쇠약 (미정)</t>
-  </si>
-  <si>
-    <t>… 균열 (미정)</t>
-  </si>
-  <si>
-    <t>굴림마다 반복 발동</t>
-  </si>
-  <si>
-    <t>은신 부여 평타 (가칭)</t>
-  </si>
-  <si>
     <t>이 카드를 쓰는 자기 부위에 다음 턴 은신 (미정) — 굴림마다 인스턴스 하나</t>
   </si>
   <si>
@@ -1377,10 +1389,13 @@
     <t>피해 처리 후(각 굴림)</t>
   </si>
   <si>
-    <t>그 굴림이 대상 부위를 약화 · 파괴하면 그 대상에게 표식 +(미정)</t>
-  </si>
-  <si>
-    <t>한 타격의 약화+파괴는 1회 · 처형 포함 · 일방 공격 포함</t>
+    <t>그 굴림이 대상 부위를 약화 · 파괴하면 그 부위의 표식 전부를 다른 생존 부위 중 표식 최소 부위로 전이(동률 무작위 · 맞은 부위 제외 · 다른 생존 부위가 없으면 전이 없음 · 정상 44 발화)</t>
+  </si>
+  <si>
+    <t>구조 확정</t>
+  </si>
+  <si>
+    <t>추가 표식 없음 · 한 타격의 약화+파괴는 1회 · 처형 포함 · 일방 공격 포함 · 일반 몹은 처치 = 파괴(죽은 몹의 표식을 다른 생존 몹으로)</t>
   </si>
   <si>
     <t>E</t>
@@ -1389,10 +1404,10 @@
     <t>소문을 내다</t>
   </si>
   <si>
-    <t>그 굴림이 대상 부위를 약화 · 파괴하면 모든 적에게 표식 +(미정)</t>
-  </si>
-  <si>
-    <t>숨통을 끊다의 전역판</t>
+    <t>그 굴림이 대상 부위를 약화 · 파괴하면 다른 모든 생존 적에게 표식 +(미정), 그중 현재 표식 최고 대상 하나에 표식 +(미정) 추가</t>
+  </si>
+  <si>
+    <t>다부위 적의 표식 부위 (미정) · 전체 확산 + 한 대상 발화 압축</t>
   </si>
   <si>
     <t>F</t>
@@ -1461,13 +1476,13 @@
     <t>마침표를 찍다</t>
   </si>
   <si>
-    <t>그 굴림으로 적을 처치하면 살수의 감 +(미정)</t>
-  </si>
-  <si>
-    <t>그 굴림으로 적을 흐트러뜨리면 살수의 감 +(미정)</t>
-  </si>
-  <si>
-    <t>그 굴림으로 처형에 성공하면 살수의 감 +(미정)</t>
+    <t>그 굴림으로 적을 처치하면 살수의 감 +(미정) · 빛 +(미정)</t>
+  </si>
+  <si>
+    <t>그 굴림으로 적을 흐트러뜨리면 살수의 감 +(미정) · 빛 +(미정)</t>
+  </si>
+  <si>
+    <t>그 굴림으로 처형에 성공하면 살수의 감 +(미정) · 빛 +(미정)</t>
   </si>
   <si>
     <t>한 굴림의 중복 조건은 1회</t>
@@ -1515,9 +1530,15 @@
     <t>은신 부여 결투 (가칭)</t>
   </si>
   <si>
+    <t>전투 시작시(스킬 전체 1회)</t>
+  </si>
+  <si>
     <t>쓰는 부위가 은신이 아니면 다음 턴 은신 (미정) 예약 · 이미 은신이면 대신 살수의 감 +(미정)</t>
   </si>
   <si>
+    <t>굴림 수만큼 반복하지 않음</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
@@ -1527,6 +1548,12 @@
     <t>스킬 시작 시 사용 부위가 은신이면 확정 추가 피해 (미정)</t>
   </si>
   <si>
+    <t>… (미정)</t>
+  </si>
+  <si>
+    <t>무기별 값을 따로 둔다</t>
+  </si>
+  <si>
     <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음</t>
   </si>
   <si>
@@ -1542,7 +1569,13 @@
     <t>노림수</t>
   </si>
   <si>
-    <t>그 턴 코인 앞면 확률 +10%p</t>
+    <t>그 턴 코인 앞면 확률 +(미정)%p</t>
+  </si>
+  <si>
+    <t>+(미정)%p</t>
+  </si>
+  <si>
+    <t>앞면 확률 보정치는 무기별</t>
   </si>
   <si>
     <t>선금 받기</t>
@@ -1551,6 +1584,9 @@
     <t>그 턴 코인 뒷면 값 +2</t>
   </si>
   <si>
+    <t>세 무기 공통</t>
+  </si>
+  <si>
     <t>환형(공격)</t>
   </si>
   <si>
@@ -1794,13 +1830,13 @@
     <t>없음</t>
   </si>
   <si>
-    <t>바 푸시 50</t>
+    <t>흐트러짐 피해 (미정)</t>
   </si>
   <si>
     <t>6 / 12</t>
   </si>
   <si>
-    <t>20 (백우 전용 - 체력 피해 아님, 창을 여는 통로)</t>
+    <t>적중마다(교환 승리 · 일방) 기세 바 +(미정) · 흐트러짐 +(미정) (백우 전용 - 체력 피해 아님, 창을 여는 통로)</t>
   </si>
   <si>
     <t>추가타 굴림당 1</t>
@@ -2070,7 +2106,7 @@
     <t xml:space="preserve">15(1굴림 예외) </t>
   </si>
   <si>
-    <t>런 전체 영구 성장. 먼저 임계에 닿은 승리/패배 축으로 고정되어 2→3→4굴림 성장</t>
+    <t>런 전체 영구 성장. 먼저 임계에 닿은 승리/패배 축으로 고정되어 2→3→4굴림 성장 · 패배 축 4굴림 1패 = 이번 합 동안 핏값 (미정)</t>
   </si>
   <si>
     <t>반격(단계별 변동)</t>
@@ -2100,7 +2136,7 @@
     <t>육참골단</t>
   </si>
   <si>
-    <t>다음 턴 자기 부위 도발 예약 · 승리시 다음 턴 (미정 — 구 견고 폐기) + 핏값</t>
+    <t>고른 자기 부위에 다음 턴 도발 (미정)/1 예약 · 각 굴림 승리시 다음 턴 보호 (미정)/1 + 핏값 (미정)/1</t>
   </si>
   <si>
     <t>전체 정화형</t>
@@ -3060,13 +3096,13 @@
     <t>기본 슬롯</t>
   </si>
   <si>
-    <t>아니오</t>
-  </si>
-  <si>
-    <t>개체 체력 135 (3마리) / 101 (4마리) · 흐트러짐 100 · 부위 없음</t>
-  </si>
-  <si>
-    <t>소스 균등 1~8 · 발악 없음 · 파괴 스킬은 일부 잡몹만</t>
+    <t>종마다</t>
+  </si>
+  <si>
+    <t>개체 체력 역할별 (미정) — 인원수 · 플레이어 캐릭터와 무관 · 흐트러짐 100 · 부위 없음</t>
+  </si>
+  <si>
+    <t>소스 균등 1~8 · 발악 없음 · 1층 12종(개발용 가명)은 규칙서 12.3 · 1층 파괴 권한은 파쇄병만 · 각 몹이 자기 행동 로직으로 공격 · 결투 · 지원 결정</t>
   </si>
   <si>
     <t>적 공통</t>
@@ -4370,7 +4406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0611E9-FC01-4DC1-8140-4594E205E917}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C2A501-8756-4310-B2BB-43B5BF6A31BA}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4564,7 +4600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B698DBFE-7891-47CB-A965-8C335EB5AF39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41FAE56-FC38-4A96-9EC9-D0D03ED9ACF2}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4574,93 +4610,93 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10" xr:uid="{B698DBFE-7891-47CB-A965-8C335EB5AF39}"/>
+  <autoFilter ref="A1:B10" xr:uid="{A41FAE56-FC38-4A96-9EC9-D0D03ED9ACF2}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B37C829C-C4DB-4885-B38A-D1647456903D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA50BC1-9C08-4A9F-98F7-F2ABE54EF6FF}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4670,19 +4706,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -4690,56 +4726,56 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -4750,93 +4786,93 @@
     </row>
     <row r="5" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{B37C829C-C4DB-4885-B38A-D1647456903D}"/>
+  <autoFilter ref="A1:F8" xr:uid="{7CA50BC1-9C08-4A9F-98F7-F2ABE54EF6FF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E129DB1-5E56-480D-8999-D4D9139EA776}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E371EB-B0CC-4EE3-A9AE-0B29751DB7AB}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4846,16 +4882,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>45</v>
@@ -4863,16 +4899,16 @@
     </row>
     <row r="2" spans="1:5" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -4880,81 +4916,81 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6" xr:uid="{2E129DB1-5E56-480D-8999-D4D9139EA776}"/>
+  <autoFilter ref="A1:E6" xr:uid="{F9E371EB-B0CC-4EE3-A9AE-0B29751DB7AB}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF4D5D6-B182-467E-A63A-33286395836F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2DDC98-140F-430E-8906-A1AC2BF26C5A}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4964,10 +5000,10 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -4978,7 +5014,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -4992,27 +5028,27 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>1</v>
@@ -5020,13 +5056,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5034,13 +5070,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1118</v>
+        <v>1130</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1</v>
@@ -5048,13 +5084,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1120</v>
+        <v>1132</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>1</v>
@@ -5062,13 +5098,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1122</v>
+        <v>1134</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>1</v>
@@ -5076,7 +5112,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>1</v>
@@ -5090,13 +5126,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1124</v>
+        <v>1136</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1125</v>
+        <v>1137</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1</v>
@@ -5104,13 +5140,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1126</v>
+        <v>1138</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>1</v>
@@ -5118,13 +5154,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1128</v>
+        <v>1140</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>1</v>
@@ -5132,7 +5168,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>1129</v>
+        <v>1141</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1</v>
@@ -5146,41 +5182,41 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1132</v>
+        <v>1144</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1133</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1134</v>
+        <v>1146</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1135</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1136</v>
+        <v>1148</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>1</v>
@@ -5188,13 +5224,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>1</v>
@@ -5202,13 +5238,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1138</v>
+        <v>1150</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>1</v>
@@ -5216,13 +5252,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>1</v>
@@ -5230,13 +5266,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>1</v>
@@ -5244,7 +5280,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>1141</v>
+        <v>1153</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>1</v>
@@ -5258,13 +5294,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1124</v>
+        <v>1136</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1142</v>
+        <v>1154</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>1</v>
@@ -5272,13 +5308,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1143</v>
+        <v>1155</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>1</v>
@@ -5286,13 +5322,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1</v>
@@ -5300,7 +5336,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>1</v>
@@ -5314,13 +5350,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1</v>
@@ -5328,27 +5364,27 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1150</v>
+        <v>1162</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1</v>
@@ -5356,13 +5392,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1151</v>
+        <v>1163</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1</v>
@@ -5370,13 +5406,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1152</v>
+        <v>1164</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1</v>
@@ -5384,13 +5420,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1</v>
@@ -5398,13 +5434,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1</v>
@@ -5412,7 +5448,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>1</v>
@@ -5426,13 +5462,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1</v>
@@ -5440,27 +5476,27 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1157</v>
+        <v>1169</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35" xr:uid="{6CF4D5D6-B182-467E-A63A-33286395836F}"/>
+  <autoFilter ref="A1:D35" xr:uid="{1D2DDC98-140F-430E-8906-A1AC2BF26C5A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885B9E4C-BA7A-40DB-B6D9-2437E5ECEAD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240FD444-DAC9-4B25-AE74-68F09E2F2627}">
   <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5473,7 +5509,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1158</v>
+        <v>1170</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -5484,7 +5520,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -5498,13 +5534,13 @@
     </row>
     <row r="3" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1160</v>
+        <v>1172</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1161</v>
+        <v>1173</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1</v>
@@ -5512,27 +5548,27 @@
     </row>
     <row r="4" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1162</v>
+        <v>1174</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1163</v>
+        <v>1175</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1166</v>
+        <v>1178</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5540,97 +5576,97 @@
     </row>
     <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1169</v>
+        <v>1181</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1172</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1175</v>
+        <v>1187</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1183</v>
+        <v>1195</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1184</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1185</v>
+        <v>1197</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1186</v>
+        <v>1198</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1189</v>
+        <v>1201</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1190</v>
+        <v>1202</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1191</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>1192</v>
+        <v>1204</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1193</v>
+        <v>1205</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1194</v>
+        <v>1206</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>1</v>
@@ -5638,13 +5674,13 @@
     </row>
     <row r="13" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1195</v>
+        <v>1207</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1196</v>
+        <v>1208</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1</v>
@@ -5652,21 +5688,21 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1198</v>
+        <v>1210</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1200</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1201</v>
+        <v>1213</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>1</v>
@@ -5680,49 +5716,49 @@
     </row>
     <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1207</v>
+        <v>1219</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1208</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>1209</v>
+        <v>1221</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1213</v>
+        <v>1225</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>1</v>
@@ -5736,7 +5772,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1</v>
@@ -5750,7 +5786,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>1</v>
@@ -5764,7 +5800,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>1</v>
@@ -5778,7 +5814,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>1</v>
@@ -5792,7 +5828,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>1</v>
@@ -5806,7 +5842,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>1</v>
@@ -5820,7 +5856,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>1</v>
@@ -5834,7 +5870,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>1</v>
@@ -5848,7 +5884,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>1</v>
@@ -5862,7 +5898,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>1</v>
@@ -5876,7 +5912,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>1</v>
@@ -5890,7 +5926,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>1</v>
@@ -5904,7 +5940,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>1</v>
@@ -5918,7 +5954,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>1</v>
@@ -5932,7 +5968,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>1</v>
@@ -5946,7 +5982,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>1</v>
@@ -5960,7 +5996,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>1</v>
@@ -5974,7 +6010,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>1</v>
@@ -5988,7 +6024,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>1</v>
@@ -6002,7 +6038,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>1</v>
@@ -6016,7 +6052,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>1</v>
@@ -6030,7 +6066,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>1</v>
@@ -6044,7 +6080,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>1</v>
@@ -6058,7 +6094,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>1</v>
@@ -6072,7 +6108,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>1</v>
@@ -6086,7 +6122,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>1</v>
@@ -6100,7 +6136,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>1</v>
@@ -6114,7 +6150,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>1</v>
@@ -6128,7 +6164,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>1</v>
@@ -6142,7 +6178,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>1</v>
@@ -6156,7 +6192,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>1</v>
@@ -6170,7 +6206,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>1</v>
@@ -6184,7 +6220,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>1219</v>
+        <v>1231</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>1</v>
@@ -6198,7 +6234,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>1</v>
@@ -6212,7 +6248,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>1</v>
@@ -6226,7 +6262,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>1</v>
@@ -6240,55 +6276,55 @@
     </row>
     <row r="56" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>1231</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1232</v>
+        <v>1244</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>1</v>
@@ -6296,105 +6332,105 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1235</v>
+        <v>1247</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1237</v>
+        <v>1249</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>1238</v>
+        <v>1250</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>1239</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1240</v>
+        <v>1252</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>1241</v>
+        <v>1253</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>1245</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1246</v>
+        <v>1258</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>1248</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>1250</v>
+        <v>1262</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>1251</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>1</v>
@@ -6408,13 +6444,13 @@
     </row>
     <row r="68" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>1</v>
@@ -6422,13 +6458,13 @@
     </row>
     <row r="69" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1258</v>
+        <v>1270</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>1</v>
@@ -6436,13 +6472,13 @@
     </row>
     <row r="70" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1259</v>
+        <v>1271</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>1</v>
@@ -6450,7 +6486,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>1</v>
@@ -6464,7 +6500,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>1</v>
@@ -6478,7 +6514,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>1</v>
@@ -6492,7 +6528,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>1</v>
@@ -6506,7 +6542,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>1</v>
@@ -6520,7 +6556,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>1</v>
@@ -6534,7 +6570,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>1</v>
@@ -6548,7 +6584,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>1260</v>
+        <v>1272</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>1</v>
@@ -6562,13 +6598,13 @@
     </row>
     <row r="79" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>1</v>
@@ -6576,7 +6612,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>1</v>
@@ -6590,7 +6626,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>1</v>
@@ -6604,7 +6640,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>1</v>
@@ -6618,7 +6654,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>1</v>
@@ -6632,7 +6668,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>1</v>
@@ -6646,7 +6682,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>1</v>
@@ -6660,7 +6696,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>1</v>
@@ -6674,7 +6710,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>1</v>
@@ -6688,7 +6724,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>1</v>
@@ -6701,14 +6737,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D88" xr:uid="{885B9E4C-BA7A-40DB-B6D9-2437E5ECEAD9}"/>
+  <autoFilter ref="A1:D88" xr:uid="{240FD444-DAC9-4B25-AE74-68F09E2F2627}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E02075-7C62-4EA9-B9EE-8E84EE25BD5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A3A3A5-DB13-433C-AFC5-F80D4537D016}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7721,7 +7757,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>85</v>
       </c>
@@ -7741,22 +7777,22 @@
         <v>1</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>1</v>
@@ -7768,10 +7804,10 @@
         <v>94</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R17" s="7" t="s">
         <v>1</v>
@@ -7780,7 +7816,7 @@
         <v>108</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -7788,10 +7824,10 @@
         <v>85</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>1</v>
@@ -7809,10 +7845,10 @@
         <v>90</v>
       </c>
       <c r="I18" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>160</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>161</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>121</v>
@@ -7833,7 +7869,7 @@
         <v>106</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R18" s="7" t="s">
         <v>1</v>
@@ -7842,7 +7878,7 @@
         <v>96</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -7850,10 +7886,10 @@
         <v>85</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>1</v>
@@ -7874,10 +7910,10 @@
         <v>102</v>
       </c>
       <c r="J19" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>141</v>
@@ -7892,10 +7928,10 @@
         <v>94</v>
       </c>
       <c r="P19" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q19" s="8" t="s">
         <v>168</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>169</v>
       </c>
       <c r="R19" s="7" t="s">
         <v>1</v>
@@ -7904,7 +7940,7 @@
         <v>96</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -7912,10 +7948,10 @@
         <v>85</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>1</v>
@@ -7933,13 +7969,13 @@
         <v>113</v>
       </c>
       <c r="I20" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="K20" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>175</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>1</v>
@@ -7954,10 +7990,10 @@
         <v>94</v>
       </c>
       <c r="P20" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>176</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>177</v>
       </c>
       <c r="R20" s="7" t="s">
         <v>1</v>
@@ -7966,27 +8002,27 @@
         <v>96</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>112</v>
@@ -7995,13 +8031,13 @@
         <v>112</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J21" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>1</v>
@@ -8019,36 +8055,36 @@
         <v>76</v>
       </c>
       <c r="Q21" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="R21" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="S21" s="9" t="s">
         <v>58</v>
       </c>
       <c r="T21" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>98</v>
       </c>
       <c r="C22" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>101</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>89</v>
@@ -8060,13 +8096,13 @@
         <v>114</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>191</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="M22" s="9" t="s">
         <v>1</v>
@@ -8095,7 +8131,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>110</v>
@@ -8110,7 +8146,7 @@
         <v>88</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>113</v>
@@ -8119,7 +8155,7 @@
         <v>113</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>196</v>
@@ -8146,7 +8182,7 @@
         <v>197</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S23" s="9" t="s">
         <v>58</v>
@@ -8157,7 +8193,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>119</v>
@@ -8172,7 +8208,7 @@
         <v>101</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>89</v>
@@ -8219,7 +8255,7 @@
     </row>
     <row r="25" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>125</v>
@@ -8234,7 +8270,7 @@
         <v>88</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>112</v>
@@ -8281,7 +8317,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>136</v>
@@ -8296,7 +8332,7 @@
         <v>101</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>89</v>
@@ -8308,7 +8344,7 @@
         <v>209</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>122</v>
@@ -8343,7 +8379,7 @@
     </row>
     <row r="27" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>146</v>
@@ -8358,7 +8394,7 @@
         <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>112</v>
@@ -8370,10 +8406,10 @@
         <v>215</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>1</v>
@@ -8405,7 +8441,7 @@
     </row>
     <row r="28" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>152</v>
@@ -8420,7 +8456,7 @@
         <v>88</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>112</v>
@@ -8467,10 +8503,10 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>226</v>
@@ -8482,7 +8518,7 @@
         <v>88</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>112</v>
@@ -8494,7 +8530,7 @@
         <v>114</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>191</v>
@@ -8529,10 +8565,10 @@
     </row>
     <row r="30" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>229</v>
@@ -8544,7 +8580,7 @@
         <v>101</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>89</v>
@@ -8591,10 +8627,10 @@
     </row>
     <row r="31" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>232</v>
@@ -8606,7 +8642,7 @@
         <v>101</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>112</v>
@@ -8653,7 +8689,7 @@
     </row>
     <row r="32" spans="1:20" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>237</v>
@@ -8715,7 +8751,7 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>243</v>
@@ -8730,7 +8766,7 @@
         <v>88</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>127</v>
@@ -8777,7 +8813,7 @@
     </row>
     <row r="34" spans="1:20" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>248</v>
@@ -8792,7 +8828,7 @@
         <v>88</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>113</v>
@@ -8839,7 +8875,7 @@
     </row>
     <row r="35" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>255</v>
@@ -8854,7 +8890,7 @@
         <v>88</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>89</v>
@@ -8869,7 +8905,7 @@
         <v>258</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>258</v>
@@ -8901,7 +8937,7 @@
     </row>
     <row r="36" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>263</v>
@@ -8963,7 +8999,7 @@
     </row>
     <row r="37" spans="1:20" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>267</v>
@@ -9524,7 +9560,7 @@
         <v>271</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>295</v>
@@ -9586,7 +9622,7 @@
         <v>271</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>299</v>
@@ -9876,7 +9912,7 @@
         <v>94</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="8" t="s">
         <v>319</v>
@@ -10264,14 +10300,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{30E02075-7C62-4EA9-B9EE-8E84EE25BD5A}"/>
+  <autoFilter ref="A1:T57" xr:uid="{46A3A3A5-DB13-433C-AFC5-F80D4537D016}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D93E4DF-44F8-434F-96C0-053B5F46E8C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3049D6D4-FC52-4EBC-8031-5D9EE1692144}">
   <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10492,7 +10528,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="121.5" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>52</v>
       </c>
@@ -10943,7 +10979,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>85</v>
       </c>
@@ -10975,13 +11011,13 @@
         <v>404</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>108</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -10992,7 +11028,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>88</v>
@@ -11007,7 +11043,7 @@
         <v>251</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>345</v>
@@ -11022,10 +11058,10 @@
         <v>108</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>85</v>
       </c>
@@ -11033,7 +11069,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>101</v>
@@ -11045,25 +11081,25 @@
         <v>113</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>384</v>
+        <v>265</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>108</v>
+        <v>415</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11074,7 +11110,7 @@
         <v>49</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>101</v>
@@ -11086,10 +11122,10 @@
         <v>265</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>345</v>
@@ -11115,7 +11151,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>88</v>
@@ -11127,10 +11163,10 @@
         <v>265</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>345</v>
@@ -11145,18 +11181,18 @@
         <v>108</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>88</v>
@@ -11168,16 +11204,16 @@
         <v>113</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>390</v>
@@ -11191,13 +11227,13 @@
     </row>
     <row r="23" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>88</v>
@@ -11212,7 +11248,7 @@
         <v>384</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>345</v>
@@ -11227,18 +11263,18 @@
         <v>51</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>101</v>
@@ -11250,10 +11286,10 @@
         <v>113</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>345</v>
@@ -11268,18 +11304,18 @@
         <v>108</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="54" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>88</v>
@@ -11291,10 +11327,10 @@
         <v>113</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>345</v>
@@ -11306,21 +11342,21 @@
         <v>1</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>108</v>
+        <v>441</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>88</v>
@@ -11332,10 +11368,10 @@
         <v>113</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>345</v>
@@ -11350,18 +11386,18 @@
         <v>108</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>88</v>
@@ -11373,36 +11409,36 @@
         <v>113</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>108</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>88</v>
@@ -11417,7 +11453,7 @@
         <v>384</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>345</v>
@@ -11437,13 +11473,13 @@
     </row>
     <row r="29" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>101</v>
@@ -11458,7 +11494,7 @@
         <v>384</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>345</v>
@@ -11473,18 +11509,18 @@
         <v>108</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="54" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>88</v>
@@ -11499,7 +11535,7 @@
         <v>384</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>345</v>
@@ -11511,21 +11547,21 @@
         <v>1</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>88</v>
@@ -11537,16 +11573,16 @@
         <v>113</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>390</v>
@@ -11555,18 +11591,18 @@
         <v>108</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>88</v>
@@ -11578,10 +11614,10 @@
         <v>112</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>345</v>
@@ -11596,18 +11632,18 @@
         <v>108</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>88</v>
@@ -11616,39 +11652,39 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>251</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>1</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>101</v>
@@ -11660,10 +11696,10 @@
         <v>265</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>401</v>
+        <v>487</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>345</v>
@@ -11678,18 +11714,18 @@
         <v>108</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>1</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>88</v>
@@ -11701,25 +11737,25 @@
         <v>265</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>345</v>
+        <v>493</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>345</v>
+        <v>493</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>108</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -11727,7 +11763,7 @@
         <v>271</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>272</v>
@@ -11745,7 +11781,7 @@
         <v>274</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>345</v>
@@ -11768,7 +11804,7 @@
         <v>271</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>277</v>
@@ -11786,7 +11822,7 @@
         <v>274</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>345</v>
@@ -11812,7 +11848,7 @@
         <v>281</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>1</v>
@@ -11827,22 +11863,22 @@
         <v>274</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>345</v>
+        <v>501</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>345</v>
+        <v>501</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>1</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>1</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -11853,7 +11889,7 @@
         <v>281</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>1</v>
@@ -11868,7 +11904,7 @@
         <v>274</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>345</v>
@@ -11883,7 +11919,7 @@
         <v>51</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>1</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -11894,7 +11930,7 @@
         <v>281</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1</v>
@@ -11909,13 +11945,13 @@
         <v>363</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>1</v>
@@ -11924,7 +11960,7 @@
         <v>51</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -11935,7 +11971,7 @@
         <v>281</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>1</v>
@@ -11950,7 +11986,7 @@
         <v>363</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>345</v>
@@ -11965,7 +12001,7 @@
         <v>51</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -11976,7 +12012,7 @@
         <v>281</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>1</v>
@@ -11991,7 +12027,7 @@
         <v>274</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>345</v>
@@ -12017,7 +12053,7 @@
         <v>281</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>1</v>
@@ -12032,7 +12068,7 @@
         <v>274</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>345</v>
@@ -12047,7 +12083,7 @@
         <v>108</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12058,7 +12094,7 @@
         <v>281</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>1</v>
@@ -12073,7 +12109,7 @@
         <v>274</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>345</v>
@@ -12088,7 +12124,7 @@
         <v>108</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12099,7 +12135,7 @@
         <v>281</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>101</v>
@@ -12114,13 +12150,13 @@
         <v>274</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>1</v>
@@ -12129,7 +12165,7 @@
         <v>108</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12140,13 +12176,13 @@
         <v>303</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>1</v>
@@ -12155,13 +12191,13 @@
         <v>306</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>1</v>
@@ -12181,13 +12217,13 @@
         <v>308</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>1</v>
@@ -12196,7 +12232,7 @@
         <v>306</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>345</v>
@@ -12222,13 +12258,13 @@
         <v>312</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>1</v>
@@ -12237,7 +12273,7 @@
         <v>306</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>345</v>
@@ -12260,10 +12296,10 @@
         <v>316</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>88</v>
@@ -12278,7 +12314,7 @@
         <v>384</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>345</v>
@@ -12293,7 +12329,7 @@
         <v>108</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12301,10 +12337,10 @@
         <v>316</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>88</v>
@@ -12316,10 +12352,10 @@
         <v>265</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>345</v>
@@ -12334,7 +12370,7 @@
         <v>108</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -12342,10 +12378,10 @@
         <v>316</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>88</v>
@@ -12357,10 +12393,10 @@
         <v>265</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>345</v>
@@ -12375,7 +12411,7 @@
         <v>108</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -12383,10 +12419,10 @@
         <v>316</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>88</v>
@@ -12398,10 +12434,10 @@
         <v>265</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>345</v>
@@ -12416,7 +12452,7 @@
         <v>108</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
@@ -12424,10 +12460,10 @@
         <v>316</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>88</v>
@@ -12442,13 +12478,13 @@
         <v>384</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>390</v>
@@ -12457,7 +12493,7 @@
         <v>108</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12465,10 +12501,10 @@
         <v>316</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>88</v>
@@ -12480,16 +12516,16 @@
         <v>265</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>390</v>
@@ -12498,7 +12534,7 @@
         <v>108</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12506,10 +12542,10 @@
         <v>316</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>88</v>
@@ -12521,16 +12557,16 @@
         <v>265</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>390</v>
@@ -12543,14 +12579,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{1D93E4DF-44F8-434F-96C0-053B5F46E8C4}"/>
+  <autoFilter ref="A1:M55" xr:uid="{3049D6D4-FC52-4EBC-8031-5D9EE1692144}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04F35370-FCD3-4EDF-A969-828AD3C97586}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0CE46A-BDFC-4897-B0D6-7ABA82CAF3C0}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12568,201 +12604,201 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>128</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{04F35370-FCD3-4EDF-A969-828AD3C97586}"/>
+  <autoFilter ref="A1:O4" xr:uid="{1A0CE46A-BDFC-4897-B0D6-7ABA82CAF3C0}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D93171-BD4A-4107-88EE-F7B9C18D0E8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB0C742-3EB3-41A0-A93D-C3BCB7764D3F}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12853,10 +12889,10 @@
         <v>46</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -12895,7 +12931,7 @@
         <v>49</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>1</v>
@@ -12912,10 +12948,10 @@
         <v>69</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -12957,7 +12993,7 @@
         <v>49</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>1</v>
@@ -12977,7 +13013,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
@@ -13016,10 +13052,10 @@
         <v>1</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>1</v>
@@ -13028,7 +13064,7 @@
         <v>51</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13036,10 +13072,10 @@
         <v>52</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>1</v>
@@ -13078,10 +13114,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="R5" s="13" t="s">
         <v>1</v>
@@ -13090,7 +13126,7 @@
         <v>51</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -13101,7 +13137,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1</v>
@@ -13140,10 +13176,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="R6" s="13" t="s">
         <v>1</v>
@@ -13160,10 +13196,10 @@
         <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>1</v>
@@ -13202,10 +13238,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="R7" s="11" t="s">
         <v>1</v>
@@ -13214,7 +13250,7 @@
         <v>51</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13222,10 +13258,10 @@
         <v>69</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>1</v>
@@ -13264,10 +13300,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="R8" s="11" t="s">
         <v>1</v>
@@ -13276,7 +13312,7 @@
         <v>51</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -13287,7 +13323,7 @@
         <v>70</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>1</v>
@@ -13329,7 +13365,7 @@
         <v>76</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="R9" s="11" t="s">
         <v>1</v>
@@ -13343,22 +13379,22 @@
     </row>
     <row r="10" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>101</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>138</v>
@@ -13370,57 +13406,57 @@
         <v>102</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="S10" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>112</v>
@@ -13429,13 +13465,13 @@
         <v>113</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="L11" s="14" t="s">
         <v>1</v>
@@ -13447,33 +13483,33 @@
         <v>1</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>1</v>
@@ -13482,7 +13518,7 @@
         <v>88</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>127</v>
@@ -13491,31 +13527,31 @@
         <v>112</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>133</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="R12" s="13" t="s">
         <v>1</v>
@@ -13524,18 +13560,18 @@
         <v>108</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>1</v>
@@ -13544,13 +13580,13 @@
         <v>88</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>112</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>94</v>
@@ -13577,7 +13613,7 @@
         <v>216</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="R13" s="13" t="s">
         <v>1</v>
@@ -13586,18 +13622,18 @@
         <v>108</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -13606,7 +13642,7 @@
         <v>88</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>89</v>
@@ -13636,10 +13672,10 @@
         <v>94</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -13653,13 +13689,13 @@
     </row>
     <row r="15" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -13668,7 +13704,7 @@
         <v>88</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>112</v>
@@ -13698,10 +13734,10 @@
         <v>94</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -13710,18 +13746,18 @@
         <v>108</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -13730,16 +13766,16 @@
         <v>88</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>1</v>
@@ -13757,33 +13793,33 @@
         <v>1</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="P16" s="13" t="s">
         <v>216</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="S16" s="13" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -13792,7 +13828,7 @@
         <v>101</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>89</v>
@@ -13822,30 +13858,30 @@
         <v>94</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>108</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>1</v>
@@ -13854,7 +13890,7 @@
         <v>101</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>112</v>
@@ -13887,7 +13923,7 @@
         <v>192</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="R18" s="13" t="s">
         <v>1</v>
@@ -13901,13 +13937,13 @@
     </row>
     <row r="19" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>1</v>
@@ -13916,7 +13952,7 @@
         <v>101</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>94</v>
@@ -13949,7 +13985,7 @@
         <v>133</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="R19" s="13" t="s">
         <v>1</v>
@@ -13963,13 +13999,13 @@
     </row>
     <row r="20" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>1</v>
@@ -13978,7 +14014,7 @@
         <v>88</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>89</v>
@@ -14011,7 +14047,7 @@
         <v>192</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="R20" s="13" t="s">
         <v>1</v>
@@ -14028,10 +14064,10 @@
         <v>85</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
@@ -14040,7 +14076,7 @@
         <v>88</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>112</v>
@@ -14049,13 +14085,13 @@
         <v>90</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="L21" s="12" t="s">
         <v>1</v>
@@ -14067,22 +14103,22 @@
         <v>1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>143</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="S21" s="11" t="s">
         <v>108</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -14090,10 +14126,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>1</v>
@@ -14114,13 +14150,13 @@
         <v>114</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>1</v>
@@ -14129,13 +14165,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>1</v>
@@ -14152,10 +14188,10 @@
         <v>85</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>1</v>
@@ -14197,7 +14233,7 @@
         <v>133</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="R23" s="11" t="s">
         <v>1</v>
@@ -14206,7 +14242,7 @@
         <v>108</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -14214,10 +14250,10 @@
         <v>85</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>1</v>
@@ -14226,7 +14262,7 @@
         <v>101</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>89</v>
@@ -14259,10 +14295,10 @@
         <v>143</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>108</v>
@@ -14276,10 +14312,10 @@
         <v>85</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>1</v>
@@ -14288,7 +14324,7 @@
         <v>101</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>112</v>
@@ -14321,10 +14357,10 @@
         <v>216</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>108</v>
@@ -14338,10 +14374,10 @@
         <v>85</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>1</v>
@@ -14350,7 +14386,7 @@
         <v>88</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>112</v>
@@ -14383,10 +14419,10 @@
         <v>133</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>108</v>
@@ -14400,10 +14436,10 @@
         <v>85</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>1</v>
@@ -14445,7 +14481,7 @@
         <v>133</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="R27" s="11" t="s">
         <v>1</v>
@@ -14462,10 +14498,10 @@
         <v>85</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>1</v>
@@ -14474,7 +14510,7 @@
         <v>88</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>89</v>
@@ -14507,7 +14543,7 @@
         <v>133</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>1</v>
@@ -14524,10 +14560,10 @@
         <v>85</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>1</v>
@@ -14569,7 +14605,7 @@
         <v>76</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="R29" s="11" t="s">
         <v>1</v>
@@ -14586,10 +14622,10 @@
         <v>85</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>1</v>
@@ -14628,10 +14664,10 @@
         <v>94</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="R30" s="11" t="s">
         <v>1</v>
@@ -14648,10 +14684,10 @@
         <v>85</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>1</v>
@@ -14690,10 +14726,10 @@
         <v>94</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="R31" s="11" t="s">
         <v>1</v>
@@ -14702,7 +14738,7 @@
         <v>108</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -14710,7 +14746,7 @@
         <v>271</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>272</v>
@@ -14755,7 +14791,7 @@
         <v>133</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="R32" s="13" t="s">
         <v>1</v>
@@ -14772,7 +14808,7 @@
         <v>271</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>277</v>
@@ -14817,7 +14853,7 @@
         <v>133</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="R33" s="13" t="s">
         <v>1</v>
@@ -14834,10 +14870,10 @@
         <v>271</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -14879,7 +14915,7 @@
         <v>133</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="R34" s="13" t="s">
         <v>1</v>
@@ -14888,7 +14924,7 @@
         <v>108</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
@@ -14896,10 +14932,10 @@
         <v>271</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>1</v>
@@ -14941,7 +14977,7 @@
         <v>133</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="R35" s="13" t="s">
         <v>1</v>
@@ -14950,7 +14986,7 @@
         <v>108</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
@@ -14958,10 +14994,10 @@
         <v>271</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>1</v>
@@ -15003,7 +15039,7 @@
         <v>133</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="R36" s="13" t="s">
         <v>1</v>
@@ -15020,10 +15056,10 @@
         <v>271</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>1</v>
@@ -15065,7 +15101,7 @@
         <v>133</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="R37" s="13" t="s">
         <v>1</v>
@@ -15074,7 +15110,7 @@
         <v>108</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
@@ -15082,10 +15118,10 @@
         <v>271</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -15127,7 +15163,7 @@
         <v>133</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="R38" s="13" t="s">
         <v>1</v>
@@ -15147,7 +15183,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>1</v>
@@ -15189,7 +15225,7 @@
         <v>133</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="R39" s="13" t="s">
         <v>1</v>
@@ -15206,10 +15242,10 @@
         <v>271</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>1</v>
@@ -15251,7 +15287,7 @@
         <v>133</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="R40" s="13" t="s">
         <v>1</v>
@@ -15268,10 +15304,10 @@
         <v>271</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -15313,7 +15349,7 @@
         <v>133</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="R41" s="13" t="s">
         <v>1</v>
@@ -15333,7 +15369,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -15375,7 +15411,7 @@
         <v>274</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="R42" s="13" t="s">
         <v>1</v>
@@ -15395,7 +15431,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>1</v>
@@ -15437,7 +15473,7 @@
         <v>133</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="R43" s="13" t="s">
         <v>1</v>
@@ -15457,7 +15493,7 @@
         <v>303</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>1</v>
@@ -15466,7 +15502,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>1</v>
@@ -15499,7 +15535,7 @@
         <v>306</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="R44" s="11" t="s">
         <v>1</v>
@@ -15519,7 +15555,7 @@
         <v>308</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>1</v>
@@ -15528,7 +15564,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>1</v>
@@ -15561,7 +15597,7 @@
         <v>306</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="R45" s="11" t="s">
         <v>1</v>
@@ -15581,7 +15617,7 @@
         <v>312</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>1</v>
@@ -15623,7 +15659,7 @@
         <v>306</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>1</v>
@@ -15636,14 +15672,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{F2D93171-BD4A-4107-88EE-F7B9C18D0E8F}"/>
+  <autoFilter ref="A1:T46" xr:uid="{0CB0C742-3EB3-41A0-A93D-C3BCB7764D3F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9B9F60-F9F4-4C21-9B6F-73F6A10694A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEC861D-4BCB-4A23-B967-3EA761DA5B2B}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15658,7 +15694,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>28</v>
@@ -15667,13 +15703,13 @@
         <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -15681,232 +15717,232 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>762</v>
-      </c>
       <c r="D5" s="10" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -15917,19 +15953,19 @@
         <v>66</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -15940,148 +15976,148 @@
         <v>352</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>377</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -16090,18 +16126,18 @@
         <v>49</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19" xr:uid="{0F9B9F60-F9F4-4C21-9B6F-73F6A10694A6}"/>
+  <autoFilter ref="A1:G19" xr:uid="{DCEC861D-4BCB-4A23-B967-3EA761DA5B2B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C776BA-BBF0-4413-9373-4B5A1E450780}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A550CB5-5EB6-4379-8B91-81519F9A3647}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16115,19 +16151,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>42</v>
@@ -16138,22 +16174,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>51</v>
@@ -16161,22 +16197,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>51</v>
@@ -16184,22 +16220,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>51</v>
@@ -16207,22 +16243,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
@@ -16230,22 +16266,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>51</v>
@@ -16253,22 +16289,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>51</v>
@@ -16276,22 +16312,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>51</v>
@@ -16299,22 +16335,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>51</v>
@@ -16322,22 +16358,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>51</v>
@@ -16345,22 +16381,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>51</v>
@@ -16368,22 +16404,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>51</v>
@@ -16391,22 +16427,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>51</v>
@@ -16414,22 +16450,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>51</v>
@@ -16437,22 +16473,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>51</v>
@@ -16460,22 +16496,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>51</v>
@@ -16483,45 +16519,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>51</v>
@@ -16529,22 +16565,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>51</v>
@@ -16552,22 +16588,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>51</v>
@@ -16575,22 +16611,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>51</v>
@@ -16598,22 +16634,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>51</v>
@@ -16621,22 +16657,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>51</v>
@@ -16644,22 +16680,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>51</v>
@@ -16667,22 +16703,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>51</v>
@@ -16690,22 +16726,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>51</v>
@@ -16713,22 +16749,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>51</v>
@@ -16736,183 +16772,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>51</v>
@@ -16920,68 +16956,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>51</v>
@@ -16989,22 +17025,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>51</v>
@@ -17012,22 +17048,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>51</v>
@@ -17035,22 +17071,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>51</v>
@@ -17058,22 +17094,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>51</v>
@@ -17081,22 +17117,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>51</v>
@@ -17104,45 +17140,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>942</v>
+        <v>954</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>943</v>
+        <v>955</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>51</v>
@@ -17150,22 +17186,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>51</v>
@@ -17173,10 +17209,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>302</v>
@@ -17185,10 +17221,10 @@
         <v>113</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>51</v>
@@ -17196,10 +17232,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>302</v>
@@ -17208,10 +17244,10 @@
         <v>113</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>51</v>
@@ -17219,10 +17255,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>302</v>
@@ -17231,10 +17267,10 @@
         <v>113</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>51</v>
@@ -17242,10 +17278,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>302</v>
@@ -17254,10 +17290,10 @@
         <v>112</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>51</v>
@@ -17265,10 +17301,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>302</v>
@@ -17277,10 +17313,10 @@
         <v>112</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>51</v>
@@ -17288,10 +17324,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>302</v>
@@ -17300,10 +17336,10 @@
         <v>112</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>51</v>
@@ -17311,10 +17347,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>302</v>
@@ -17323,10 +17359,10 @@
         <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>51</v>
@@ -17334,10 +17370,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>302</v>
@@ -17346,10 +17382,10 @@
         <v>89</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>51</v>
@@ -17357,10 +17393,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>302</v>
@@ -17369,10 +17405,10 @@
         <v>89</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>51</v>
@@ -17380,68 +17416,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>51</v>
@@ -17449,22 +17485,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>51</v>
@@ -17472,22 +17508,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>51</v>
@@ -17495,22 +17531,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>51</v>
@@ -17518,22 +17554,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>51</v>
@@ -17541,22 +17577,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>51</v>
@@ -17564,36 +17600,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{F8C776BA-BBF0-4413-9373-4B5A1E450780}"/>
+  <autoFilter ref="A1:G64" xr:uid="{9A550CB5-5EB6-4379-8B91-81519F9A3647}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35EC1D6-FD2B-4E26-B735-B78F95FC26FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC1DE6A-FEDD-4017-8948-DCBEA77A4BBE}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17607,10 +17643,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>32</v>
@@ -17619,44 +17655,44 @@
         <v>34</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>89</v>
+        <v>1001</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>91</v>
+        <v>1001</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
@@ -17665,21 +17701,21 @@
         <v>114</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>49</v>
@@ -17691,18 +17727,18 @@
         <v>49</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>49</v>
@@ -17714,41 +17750,41 @@
         <v>49</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>112</v>
@@ -17757,21 +17793,21 @@
         <v>114</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>49</v>
@@ -17783,21 +17819,21 @@
         <v>49</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{B35EC1D6-FD2B-4E26-B735-B78F95FC26FB}"/>
+  <autoFilter ref="A1:G8" xr:uid="{4CC1DE6A-FEDD-4017-8948-DCBEA77A4BBE}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC9DA60-9404-446D-81E0-99F4BECCACAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E4F3EA-0A7C-4DF9-AB60-1703F49EF72F}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17807,19 +17843,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -17827,66 +17863,66 @@
     </row>
     <row r="2" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{3FC9DA60-9404-446D-81E0-99F4BECCACAC}"/>
+  <autoFilter ref="A1:F4" xr:uid="{77E4F3EA-0A7C-4DF9-AB60-1703F49EF72F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-Onedrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6CB2DE6-2C40-444D-B6F9-FBF560A2573C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31836643-5F51-419C-9251-E45EB88AED1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{4FD8DE85-2159-414B-9B9D-5F75F99ECF06}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{9632B8F0-0750-44F8-A501-4955FF517E26}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="1274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="1275">
   <si>
     <t>Project Abyss — 전투 콘텐츠 명세 (2026-09-25)</t>
   </si>
@@ -1302,22 +1302,22 @@
     <t>현상수배</t>
   </si>
   <si>
-    <t>굴림 1 · 2 · 3에 서로 다른 효과 (미정)</t>
-  </si>
-  <si>
-    <t>굴림 1 · 2에 서로 다른 효과 (미정)</t>
-  </si>
-  <si>
-    <t>강한 1굴림 효과 (미정)</t>
+    <t>승리시(굴림별로 다른 효과)</t>
+  </si>
+  <si>
+    <t>1굴림 다음 턴 모든 적 표식 +(미정) · 2굴림 다음 턴 모든 적 지정 (미정)/1 · 3굴림 자신 다음 턴 신속 (미정)/1</t>
+  </si>
+  <si>
+    <t>1굴림 다음 턴 모든 적 쇠약 (미정)/1 · 2굴림 다음 턴 모든 적 속박 (미정)/1</t>
+  </si>
+  <si>
+    <t>1굴림 다음 턴 모든 적 균열 (미정)/1</t>
   </si>
   <si>
     <t>무기별 분기 — 같은 효과를 모든 굴림에 반복하지 않음 · 무기별 패키지 가치를 맞춤</t>
   </si>
   <si>
-    <t>재설계 대기 · 효과 미정</t>
-  </si>
-  <si>
-    <t>구 「각 굴림 승리시 다음 턴 모든 적에게 같은 효과」 폐기</t>
+    <t>각 굴림은 자기 효과만 · 실제 교환 승리시만 · 다부위 적의 표식 · 지정 부위 = 그 적의 표식 최고 생존 부위(동률 무작위)</t>
   </si>
   <si>
     <t>은신 부여 평타 (가칭)</t>
@@ -1332,10 +1332,16 @@
     <t>은신 보상 평타 (가칭)</t>
   </si>
   <si>
-    <t>스킬 시작 시 사용 부위가 은신이면 대상에게 표식 +(미정)</t>
-  </si>
-  <si>
-    <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음(행동이 끝나면 −1)</t>
+    <t>스킬 시작 시 사용 부위가 은신이면 이 스킬 모든 굴림 위력 +(미정)</t>
+  </si>
+  <si>
+    <t>… +(미정)</t>
+  </si>
+  <si>
+    <t>무기별 값을 따로 둔다</t>
+  </si>
+  <si>
+    <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음(행동이 끝나면 공통 규칙대로 −1) · 구 「각 굴림 사용시 표식」 폐기</t>
   </si>
   <si>
     <t>A</t>
@@ -1549,9 +1555,6 @@
   </si>
   <si>
     <t>… (미정)</t>
-  </si>
-  <si>
-    <t>무기별 값을 따로 둔다</t>
   </si>
   <si>
     <t>은신 여부와 무관하게 사용 가능 · 은신을 따로 소비하지 않음</t>
@@ -4406,7 +4409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C2A501-8756-4310-B2BB-43B5BF6A31BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99604371-668C-4F2F-A06F-71A4FA92810C}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4600,7 +4603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41FAE56-FC38-4A96-9EC9-D0D03ED9ACF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67A3A5F-8CE1-45AD-80D1-812A884CF3DE}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4610,93 +4613,93 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10" xr:uid="{A41FAE56-FC38-4A96-9EC9-D0D03ED9ACF2}"/>
+  <autoFilter ref="A1:B10" xr:uid="{D67A3A5F-8CE1-45AD-80D1-812A884CF3DE}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA50BC1-9C08-4A9F-98F7-F2ABE54EF6FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCF2CA2F-2787-4110-9F87-F0F789F4DE1C}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4706,19 +4709,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -4726,56 +4729,56 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -4786,93 +4789,93 @@
     </row>
     <row r="5" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{7CA50BC1-9C08-4A9F-98F7-F2ABE54EF6FF}"/>
+  <autoFilter ref="A1:F8" xr:uid="{DCF2CA2F-2787-4110-9F87-F0F789F4DE1C}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E371EB-B0CC-4EE3-A9AE-0B29751DB7AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6765D0-CF53-4FFF-8FE8-E4306A191142}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4882,16 +4885,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>45</v>
@@ -4899,16 +4902,16 @@
     </row>
     <row r="2" spans="1:5" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -4916,81 +4919,81 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6" xr:uid="{F9E371EB-B0CC-4EE3-A9AE-0B29751DB7AB}"/>
+  <autoFilter ref="A1:E6" xr:uid="{FA6765D0-CF53-4FFF-8FE8-E4306A191142}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2DDC98-140F-430E-8906-A1AC2BF26C5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F2692F-6627-4838-AC04-7D00DBCACD61}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5000,10 +5003,10 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -5014,7 +5017,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -5028,27 +5031,27 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>1</v>
@@ -5056,13 +5059,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5070,13 +5073,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1</v>
@@ -5084,13 +5087,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>1</v>
@@ -5098,13 +5101,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>1</v>
@@ -5112,7 +5115,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>1</v>
@@ -5126,13 +5129,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1</v>
@@ -5140,13 +5143,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>1</v>
@@ -5154,13 +5157,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>1</v>
@@ -5168,7 +5171,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1</v>
@@ -5182,41 +5185,41 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>1</v>
@@ -5224,13 +5227,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>1</v>
@@ -5238,13 +5241,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>1</v>
@@ -5252,13 +5255,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>1</v>
@@ -5266,13 +5269,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>1</v>
@@ -5280,7 +5283,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>1</v>
@@ -5294,13 +5297,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>1</v>
@@ -5308,13 +5311,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>1</v>
@@ -5322,13 +5325,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1</v>
@@ -5336,7 +5339,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>1</v>
@@ -5350,13 +5353,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1</v>
@@ -5364,27 +5367,27 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1</v>
@@ -5392,13 +5395,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1</v>
@@ -5406,13 +5409,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1</v>
@@ -5420,13 +5423,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1</v>
@@ -5434,13 +5437,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1</v>
@@ -5448,7 +5451,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>1</v>
@@ -5462,13 +5465,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1</v>
@@ -5476,27 +5479,27 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35" xr:uid="{1D2DDC98-140F-430E-8906-A1AC2BF26C5A}"/>
+  <autoFilter ref="A1:D35" xr:uid="{03F2692F-6627-4838-AC04-7D00DBCACD61}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240FD444-DAC9-4B25-AE74-68F09E2F2627}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070C6150-43B0-4D6E-9890-80FB69DFC2EC}">
   <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5509,7 +5512,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -5520,7 +5523,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -5534,13 +5537,13 @@
     </row>
     <row r="3" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1</v>
@@ -5548,27 +5551,27 @@
     </row>
     <row r="4" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5576,97 +5579,97 @@
     </row>
     <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>1</v>
@@ -5674,13 +5677,13 @@
     </row>
     <row r="13" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1</v>
@@ -5688,21 +5691,21 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>1</v>
@@ -5716,49 +5719,49 @@
     </row>
     <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>1</v>
@@ -5772,7 +5775,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1</v>
@@ -5786,7 +5789,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>1</v>
@@ -5800,7 +5803,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>1</v>
@@ -5814,7 +5817,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>1</v>
@@ -5828,7 +5831,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>1</v>
@@ -5842,7 +5845,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>1</v>
@@ -5856,7 +5859,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>1</v>
@@ -5870,7 +5873,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>1</v>
@@ -5884,7 +5887,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>1</v>
@@ -5898,7 +5901,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>1</v>
@@ -5912,7 +5915,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>1</v>
@@ -5926,7 +5929,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>1</v>
@@ -5940,7 +5943,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>1</v>
@@ -5954,7 +5957,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>1</v>
@@ -5968,7 +5971,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>1</v>
@@ -5982,7 +5985,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>1</v>
@@ -5996,7 +5999,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>1</v>
@@ -6010,7 +6013,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>1</v>
@@ -6024,7 +6027,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>1</v>
@@ -6038,7 +6041,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>1</v>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>1</v>
@@ -6066,7 +6069,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>1</v>
@@ -6080,7 +6083,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>1</v>
@@ -6094,7 +6097,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>1</v>
@@ -6108,7 +6111,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>1</v>
@@ -6122,7 +6125,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>1</v>
@@ -6136,7 +6139,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>1</v>
@@ -6150,7 +6153,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>1</v>
@@ -6164,7 +6167,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>1</v>
@@ -6178,7 +6181,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>1</v>
@@ -6192,7 +6195,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>1</v>
@@ -6206,7 +6209,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>1</v>
@@ -6220,7 +6223,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>1</v>
@@ -6234,7 +6237,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>1</v>
@@ -6248,7 +6251,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>1</v>
@@ -6262,7 +6265,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>1</v>
@@ -6276,55 +6279,55 @@
     </row>
     <row r="56" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>1</v>
@@ -6332,105 +6335,105 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>1</v>
@@ -6444,13 +6447,13 @@
     </row>
     <row r="68" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>1</v>
@@ -6458,13 +6461,13 @@
     </row>
     <row r="69" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B69" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>1270</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>1269</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>1</v>
@@ -6472,13 +6475,13 @@
     </row>
     <row r="70" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>1</v>
@@ -6486,7 +6489,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>1</v>
@@ -6500,7 +6503,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>1</v>
@@ -6514,7 +6517,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>1</v>
@@ -6528,7 +6531,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>1</v>
@@ -6542,7 +6545,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>1</v>
@@ -6556,7 +6559,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>1</v>
@@ -6570,7 +6573,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>1</v>
@@ -6584,7 +6587,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>1</v>
@@ -6598,13 +6601,13 @@
     </row>
     <row r="79" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>1</v>
@@ -6612,7 +6615,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>1</v>
@@ -6626,7 +6629,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>1</v>
@@ -6640,7 +6643,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>1</v>
@@ -6654,7 +6657,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>1</v>
@@ -6668,7 +6671,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>1</v>
@@ -6682,7 +6685,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>1</v>
@@ -6696,7 +6699,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>1</v>
@@ -6710,7 +6713,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>1</v>
@@ -6724,7 +6727,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>1</v>
@@ -6737,14 +6740,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D88" xr:uid="{240FD444-DAC9-4B25-AE74-68F09E2F2627}"/>
+  <autoFilter ref="A1:D88" xr:uid="{070C6150-43B0-4D6E-9890-80FB69DFC2EC}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A3A3A5-DB13-433C-AFC5-F80D4537D016}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B65E706-62F1-42C6-A2D9-EF2C3EDA7E9E}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10300,14 +10303,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{46A3A3A5-DB13-433C-AFC5-F80D4537D016}"/>
+  <autoFilter ref="A1:T57" xr:uid="{3B65E706-62F1-42C6-A2D9-EF2C3EDA7E9E}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3049D6D4-FC52-4EBC-8031-5D9EE1692144}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B7669C-4495-4730-9F2A-982B2311E9B2}">
   <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11061,7 +11064,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>85</v>
       </c>
@@ -11081,22 +11084,22 @@
         <v>113</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>265</v>
+        <v>411</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>415</v>
+        <v>108</v>
       </c>
       <c r="M19" s="8" t="s">
         <v>416</v>
@@ -11143,7 +11146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>85</v>
       </c>
@@ -11163,25 +11166,25 @@
         <v>265</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>418</v>
+        <v>251</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>421</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>345</v>
+        <v>422</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>345</v>
+        <v>422</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>1</v>
+        <v>423</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>108</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11189,10 +11192,10 @@
         <v>178</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>88</v>
@@ -11207,13 +11210,13 @@
         <v>418</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>390</v>
@@ -11230,10 +11233,10 @@
         <v>178</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>88</v>
@@ -11248,7 +11251,7 @@
         <v>384</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>345</v>
@@ -11263,7 +11266,7 @@
         <v>51</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11271,10 +11274,10 @@
         <v>178</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>101</v>
@@ -11286,10 +11289,10 @@
         <v>113</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>345</v>
@@ -11304,7 +11307,7 @@
         <v>108</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="54" x14ac:dyDescent="0.3">
@@ -11312,10 +11315,10 @@
         <v>178</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>88</v>
@@ -11327,10 +11330,10 @@
         <v>113</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>345</v>
@@ -11342,10 +11345,10 @@
         <v>1</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -11353,10 +11356,10 @@
         <v>178</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>88</v>
@@ -11368,10 +11371,10 @@
         <v>113</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>345</v>
@@ -11386,7 +11389,7 @@
         <v>108</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -11394,10 +11397,10 @@
         <v>178</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>88</v>
@@ -11409,25 +11412,25 @@
         <v>113</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>108</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -11435,10 +11438,10 @@
         <v>178</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>88</v>
@@ -11453,7 +11456,7 @@
         <v>384</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>345</v>
@@ -11476,10 +11479,10 @@
         <v>178</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>101</v>
@@ -11494,7 +11497,7 @@
         <v>384</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>345</v>
@@ -11509,7 +11512,7 @@
         <v>108</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="54" x14ac:dyDescent="0.3">
@@ -11517,10 +11520,10 @@
         <v>178</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>88</v>
@@ -11535,7 +11538,7 @@
         <v>384</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>345</v>
@@ -11547,10 +11550,10 @@
         <v>1</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11558,10 +11561,10 @@
         <v>178</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>88</v>
@@ -11573,16 +11576,16 @@
         <v>113</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>390</v>
@@ -11591,7 +11594,7 @@
         <v>108</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11599,10 +11602,10 @@
         <v>178</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>88</v>
@@ -11617,7 +11620,7 @@
         <v>418</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>345</v>
@@ -11632,7 +11635,7 @@
         <v>108</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -11640,10 +11643,10 @@
         <v>178</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>88</v>
@@ -11652,28 +11655,28 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>251</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>1</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11681,10 +11684,10 @@
         <v>178</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>101</v>
@@ -11696,10 +11699,10 @@
         <v>265</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>345</v>
@@ -11714,7 +11717,7 @@
         <v>108</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11722,10 +11725,10 @@
         <v>178</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>88</v>
@@ -11740,22 +11743,22 @@
         <v>418</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>494</v>
+        <v>423</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>108</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -11763,7 +11766,7 @@
         <v>271</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>272</v>
@@ -11781,7 +11784,7 @@
         <v>274</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>345</v>
@@ -11804,7 +11807,7 @@
         <v>271</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>277</v>
@@ -11822,7 +11825,7 @@
         <v>274</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>345</v>
@@ -11848,7 +11851,7 @@
         <v>281</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>1</v>
@@ -11863,13 +11866,13 @@
         <v>274</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>1</v>
@@ -11878,7 +11881,7 @@
         <v>108</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -11889,7 +11892,7 @@
         <v>281</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>1</v>
@@ -11904,7 +11907,7 @@
         <v>274</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>345</v>
@@ -11919,7 +11922,7 @@
         <v>51</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -11930,7 +11933,7 @@
         <v>281</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1</v>
@@ -11945,13 +11948,13 @@
         <v>363</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>1</v>
@@ -11960,7 +11963,7 @@
         <v>51</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -11971,7 +11974,7 @@
         <v>281</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>1</v>
@@ -11986,7 +11989,7 @@
         <v>363</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>345</v>
@@ -12001,7 +12004,7 @@
         <v>51</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -12012,7 +12015,7 @@
         <v>281</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>1</v>
@@ -12027,7 +12030,7 @@
         <v>274</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>345</v>
@@ -12053,7 +12056,7 @@
         <v>281</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>1</v>
@@ -12068,7 +12071,7 @@
         <v>274</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>345</v>
@@ -12083,7 +12086,7 @@
         <v>108</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12094,7 +12097,7 @@
         <v>281</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>1</v>
@@ -12109,7 +12112,7 @@
         <v>274</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>345</v>
@@ -12124,7 +12127,7 @@
         <v>108</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12135,7 +12138,7 @@
         <v>281</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>101</v>
@@ -12150,13 +12153,13 @@
         <v>274</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>1</v>
@@ -12165,7 +12168,7 @@
         <v>108</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12176,13 +12179,13 @@
         <v>303</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>1</v>
@@ -12191,13 +12194,13 @@
         <v>306</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>1</v>
@@ -12217,13 +12220,13 @@
         <v>308</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>1</v>
@@ -12232,7 +12235,7 @@
         <v>306</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>345</v>
@@ -12258,13 +12261,13 @@
         <v>312</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>1</v>
@@ -12273,7 +12276,7 @@
         <v>306</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>345</v>
@@ -12296,10 +12299,10 @@
         <v>316</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>88</v>
@@ -12314,7 +12317,7 @@
         <v>384</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>345</v>
@@ -12329,7 +12332,7 @@
         <v>108</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12337,10 +12340,10 @@
         <v>316</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>88</v>
@@ -12352,10 +12355,10 @@
         <v>265</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>345</v>
@@ -12370,7 +12373,7 @@
         <v>108</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -12378,10 +12381,10 @@
         <v>316</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>88</v>
@@ -12393,10 +12396,10 @@
         <v>265</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>345</v>
@@ -12411,7 +12414,7 @@
         <v>108</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -12419,10 +12422,10 @@
         <v>316</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>88</v>
@@ -12434,10 +12437,10 @@
         <v>265</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>345</v>
@@ -12452,7 +12455,7 @@
         <v>108</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
@@ -12460,10 +12463,10 @@
         <v>316</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>88</v>
@@ -12478,13 +12481,13 @@
         <v>384</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>390</v>
@@ -12493,7 +12496,7 @@
         <v>108</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12501,10 +12504,10 @@
         <v>316</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>88</v>
@@ -12516,16 +12519,16 @@
         <v>265</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>390</v>
@@ -12534,7 +12537,7 @@
         <v>108</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12542,10 +12545,10 @@
         <v>316</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>88</v>
@@ -12557,16 +12560,16 @@
         <v>265</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>390</v>
@@ -12579,14 +12582,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{3049D6D4-FC52-4EBC-8031-5D9EE1692144}"/>
+  <autoFilter ref="A1:M55" xr:uid="{10B7669C-4495-4730-9F2A-982B2311E9B2}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0CE46A-BDFC-4897-B0D6-7ABA82CAF3C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0FEB4C-DDAF-4A91-B4A5-4020B39F7EFB}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12604,201 +12607,201 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>128</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{1A0CE46A-BDFC-4897-B0D6-7ABA82CAF3C0}"/>
+  <autoFilter ref="A1:O4" xr:uid="{BA0FEB4C-DDAF-4A91-B4A5-4020B39F7EFB}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB0C742-3EB3-41A0-A93D-C3BCB7764D3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B4EB47-AF9A-4E74-AFB1-85288A0847F0}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12889,10 +12892,10 @@
         <v>46</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -12931,7 +12934,7 @@
         <v>49</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>1</v>
@@ -12948,10 +12951,10 @@
         <v>69</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -12993,7 +12996,7 @@
         <v>49</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>1</v>
@@ -13013,7 +13016,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
@@ -13052,10 +13055,10 @@
         <v>1</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>1</v>
@@ -13064,7 +13067,7 @@
         <v>51</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13072,10 +13075,10 @@
         <v>52</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>1</v>
@@ -13114,10 +13117,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="R5" s="13" t="s">
         <v>1</v>
@@ -13126,7 +13129,7 @@
         <v>51</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -13137,7 +13140,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1</v>
@@ -13176,10 +13179,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="R6" s="13" t="s">
         <v>1</v>
@@ -13196,10 +13199,10 @@
         <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>1</v>
@@ -13238,10 +13241,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="R7" s="11" t="s">
         <v>1</v>
@@ -13250,7 +13253,7 @@
         <v>51</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13258,10 +13261,10 @@
         <v>69</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>1</v>
@@ -13300,10 +13303,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="R8" s="11" t="s">
         <v>1</v>
@@ -13312,7 +13315,7 @@
         <v>51</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -13323,7 +13326,7 @@
         <v>70</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>1</v>
@@ -13365,7 +13368,7 @@
         <v>76</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R9" s="11" t="s">
         <v>1</v>
@@ -13382,19 +13385,19 @@
         <v>178</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>101</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>138</v>
@@ -13406,37 +13409,37 @@
         <v>102</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S10" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13444,19 +13447,19 @@
         <v>178</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>112</v>
@@ -13465,13 +13468,13 @@
         <v>113</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L11" s="14" t="s">
         <v>1</v>
@@ -13483,22 +13486,22 @@
         <v>1</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13506,10 +13509,10 @@
         <v>178</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>1</v>
@@ -13518,7 +13521,7 @@
         <v>88</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>127</v>
@@ -13530,28 +13533,28 @@
         <v>159</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>133</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="R12" s="13" t="s">
         <v>1</v>
@@ -13560,7 +13563,7 @@
         <v>108</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13568,10 +13571,10 @@
         <v>178</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>1</v>
@@ -13580,13 +13583,13 @@
         <v>88</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>112</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>94</v>
@@ -13613,7 +13616,7 @@
         <v>216</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="R13" s="13" t="s">
         <v>1</v>
@@ -13622,7 +13625,7 @@
         <v>108</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
@@ -13630,10 +13633,10 @@
         <v>178</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -13642,7 +13645,7 @@
         <v>88</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>89</v>
@@ -13672,10 +13675,10 @@
         <v>94</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -13692,10 +13695,10 @@
         <v>178</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -13704,7 +13707,7 @@
         <v>88</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>112</v>
@@ -13734,10 +13737,10 @@
         <v>94</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -13746,7 +13749,7 @@
         <v>108</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13754,10 +13757,10 @@
         <v>178</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -13766,16 +13769,16 @@
         <v>88</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>1</v>
@@ -13793,22 +13796,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P16" s="13" t="s">
         <v>216</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="S16" s="13" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13816,10 +13819,10 @@
         <v>178</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -13828,7 +13831,7 @@
         <v>101</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>89</v>
@@ -13858,19 +13861,19 @@
         <v>94</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>108</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13878,10 +13881,10 @@
         <v>178</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>1</v>
@@ -13890,7 +13893,7 @@
         <v>101</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>112</v>
@@ -13923,7 +13926,7 @@
         <v>192</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="R18" s="13" t="s">
         <v>1</v>
@@ -13940,10 +13943,10 @@
         <v>178</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>1</v>
@@ -13952,7 +13955,7 @@
         <v>101</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>94</v>
@@ -13985,7 +13988,7 @@
         <v>133</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="R19" s="13" t="s">
         <v>1</v>
@@ -14002,10 +14005,10 @@
         <v>178</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>1</v>
@@ -14014,7 +14017,7 @@
         <v>88</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>89</v>
@@ -14047,7 +14050,7 @@
         <v>192</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="R20" s="13" t="s">
         <v>1</v>
@@ -14064,10 +14067,10 @@
         <v>85</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
@@ -14076,7 +14079,7 @@
         <v>88</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>112</v>
@@ -14085,13 +14088,13 @@
         <v>90</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L21" s="12" t="s">
         <v>1</v>
@@ -14103,22 +14106,22 @@
         <v>1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>143</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S21" s="11" t="s">
         <v>108</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -14126,10 +14129,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>1</v>
@@ -14150,13 +14153,13 @@
         <v>114</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>1</v>
@@ -14165,13 +14168,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>1</v>
@@ -14188,10 +14191,10 @@
         <v>85</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>1</v>
@@ -14233,7 +14236,7 @@
         <v>133</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="R23" s="11" t="s">
         <v>1</v>
@@ -14242,7 +14245,7 @@
         <v>108</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -14250,10 +14253,10 @@
         <v>85</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>1</v>
@@ -14262,7 +14265,7 @@
         <v>101</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>89</v>
@@ -14295,10 +14298,10 @@
         <v>143</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>108</v>
@@ -14312,10 +14315,10 @@
         <v>85</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>1</v>
@@ -14324,7 +14327,7 @@
         <v>101</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>112</v>
@@ -14357,10 +14360,10 @@
         <v>216</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>108</v>
@@ -14374,10 +14377,10 @@
         <v>85</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>1</v>
@@ -14386,7 +14389,7 @@
         <v>88</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>112</v>
@@ -14419,10 +14422,10 @@
         <v>133</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>108</v>
@@ -14436,10 +14439,10 @@
         <v>85</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>1</v>
@@ -14481,7 +14484,7 @@
         <v>133</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="R27" s="11" t="s">
         <v>1</v>
@@ -14498,10 +14501,10 @@
         <v>85</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>1</v>
@@ -14510,7 +14513,7 @@
         <v>88</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>89</v>
@@ -14543,7 +14546,7 @@
         <v>133</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>1</v>
@@ -14560,10 +14563,10 @@
         <v>85</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>1</v>
@@ -14605,7 +14608,7 @@
         <v>76</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="R29" s="11" t="s">
         <v>1</v>
@@ -14622,10 +14625,10 @@
         <v>85</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>1</v>
@@ -14664,10 +14667,10 @@
         <v>94</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="R30" s="11" t="s">
         <v>1</v>
@@ -14684,10 +14687,10 @@
         <v>85</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>1</v>
@@ -14726,10 +14729,10 @@
         <v>94</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="R31" s="11" t="s">
         <v>1</v>
@@ -14738,7 +14741,7 @@
         <v>108</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -14746,7 +14749,7 @@
         <v>271</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>272</v>
@@ -14791,7 +14794,7 @@
         <v>133</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="R32" s="13" t="s">
         <v>1</v>
@@ -14808,7 +14811,7 @@
         <v>271</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>277</v>
@@ -14853,7 +14856,7 @@
         <v>133</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R33" s="13" t="s">
         <v>1</v>
@@ -14870,10 +14873,10 @@
         <v>271</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -14915,7 +14918,7 @@
         <v>133</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="R34" s="13" t="s">
         <v>1</v>
@@ -14924,7 +14927,7 @@
         <v>108</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
@@ -14932,10 +14935,10 @@
         <v>271</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>1</v>
@@ -14977,7 +14980,7 @@
         <v>133</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="R35" s="13" t="s">
         <v>1</v>
@@ -14986,7 +14989,7 @@
         <v>108</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
@@ -14994,10 +14997,10 @@
         <v>271</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>1</v>
@@ -15039,7 +15042,7 @@
         <v>133</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="R36" s="13" t="s">
         <v>1</v>
@@ -15056,10 +15059,10 @@
         <v>271</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>1</v>
@@ -15101,7 +15104,7 @@
         <v>133</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="R37" s="13" t="s">
         <v>1</v>
@@ -15110,7 +15113,7 @@
         <v>108</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
@@ -15118,10 +15121,10 @@
         <v>271</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -15163,7 +15166,7 @@
         <v>133</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="R38" s="13" t="s">
         <v>1</v>
@@ -15183,7 +15186,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>1</v>
@@ -15225,7 +15228,7 @@
         <v>133</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="R39" s="13" t="s">
         <v>1</v>
@@ -15242,10 +15245,10 @@
         <v>271</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>1</v>
@@ -15287,7 +15290,7 @@
         <v>133</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="R40" s="13" t="s">
         <v>1</v>
@@ -15304,10 +15307,10 @@
         <v>271</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -15349,7 +15352,7 @@
         <v>133</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="R41" s="13" t="s">
         <v>1</v>
@@ -15369,7 +15372,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -15411,7 +15414,7 @@
         <v>274</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="R42" s="13" t="s">
         <v>1</v>
@@ -15431,7 +15434,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>1</v>
@@ -15473,7 +15476,7 @@
         <v>133</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="R43" s="13" t="s">
         <v>1</v>
@@ -15493,7 +15496,7 @@
         <v>303</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>1</v>
@@ -15502,7 +15505,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>1</v>
@@ -15535,7 +15538,7 @@
         <v>306</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="R44" s="11" t="s">
         <v>1</v>
@@ -15555,7 +15558,7 @@
         <v>308</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>1</v>
@@ -15564,7 +15567,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>1</v>
@@ -15597,7 +15600,7 @@
         <v>306</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="R45" s="11" t="s">
         <v>1</v>
@@ -15617,7 +15620,7 @@
         <v>312</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>1</v>
@@ -15659,7 +15662,7 @@
         <v>306</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>1</v>
@@ -15672,14 +15675,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{0CB0C742-3EB3-41A0-A93D-C3BCB7764D3F}"/>
+  <autoFilter ref="A1:T46" xr:uid="{B9B4EB47-AF9A-4E74-AFB1-85288A0847F0}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEC861D-4BCB-4A23-B967-3EA761DA5B2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D3978F-DD4D-469A-8664-CBB15B6F2ACB}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15694,7 +15697,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>28</v>
@@ -15703,13 +15706,13 @@
         <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -15717,232 +15720,232 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -15953,19 +15956,19 @@
         <v>66</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -15976,148 +15979,148 @@
         <v>352</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>377</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -16126,18 +16129,18 @@
         <v>49</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19" xr:uid="{DCEC861D-4BCB-4A23-B967-3EA761DA5B2B}"/>
+  <autoFilter ref="A1:G19" xr:uid="{60D3978F-DD4D-469A-8664-CBB15B6F2ACB}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A550CB5-5EB6-4379-8B91-81519F9A3647}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD5BBE2-D235-47F6-8405-7374DB6B9919}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16151,19 +16154,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>42</v>
@@ -16174,22 +16177,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>51</v>
@@ -16197,22 +16200,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>51</v>
@@ -16220,22 +16223,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>51</v>
@@ -16243,22 +16246,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
@@ -16266,22 +16269,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>51</v>
@@ -16289,22 +16292,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>51</v>
@@ -16312,22 +16315,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>51</v>
@@ -16335,22 +16338,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>51</v>
@@ -16358,22 +16361,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>51</v>
@@ -16381,22 +16384,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>51</v>
@@ -16404,22 +16407,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>51</v>
@@ -16427,22 +16430,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>51</v>
@@ -16450,22 +16453,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>51</v>
@@ -16473,22 +16476,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>51</v>
@@ -16496,22 +16499,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>51</v>
@@ -16519,45 +16522,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>51</v>
@@ -16565,22 +16568,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>51</v>
@@ -16588,22 +16591,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>51</v>
@@ -16611,22 +16614,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>51</v>
@@ -16634,22 +16637,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>51</v>
@@ -16657,22 +16660,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>51</v>
@@ -16680,22 +16683,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>51</v>
@@ -16703,22 +16706,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>51</v>
@@ -16726,22 +16729,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>51</v>
@@ -16749,22 +16752,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>51</v>
@@ -16772,183 +16775,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E30" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>920</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>921</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>51</v>
@@ -16956,68 +16959,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>51</v>
@@ -17025,22 +17028,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>51</v>
@@ -17048,22 +17051,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>51</v>
@@ -17071,22 +17074,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>51</v>
@@ -17094,22 +17097,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>51</v>
@@ -17117,22 +17120,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>51</v>
@@ -17140,45 +17143,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>51</v>
@@ -17186,22 +17189,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>51</v>
@@ -17209,10 +17212,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>302</v>
@@ -17221,10 +17224,10 @@
         <v>113</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>51</v>
@@ -17232,10 +17235,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>302</v>
@@ -17244,10 +17247,10 @@
         <v>113</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>51</v>
@@ -17255,10 +17258,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>302</v>
@@ -17267,10 +17270,10 @@
         <v>113</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>51</v>
@@ -17278,10 +17281,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>302</v>
@@ -17290,10 +17293,10 @@
         <v>112</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>51</v>
@@ -17301,10 +17304,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>302</v>
@@ -17313,10 +17316,10 @@
         <v>112</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>51</v>
@@ -17324,10 +17327,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>302</v>
@@ -17336,10 +17339,10 @@
         <v>112</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>51</v>
@@ -17347,10 +17350,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>302</v>
@@ -17359,10 +17362,10 @@
         <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>51</v>
@@ -17370,10 +17373,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>302</v>
@@ -17382,10 +17385,10 @@
         <v>89</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>51</v>
@@ -17393,10 +17396,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>302</v>
@@ -17405,10 +17408,10 @@
         <v>89</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>51</v>
@@ -17416,68 +17419,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>981</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>982</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>980</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>981</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>51</v>
@@ -17485,22 +17488,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>51</v>
@@ -17508,22 +17511,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>51</v>
@@ -17531,22 +17534,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>51</v>
@@ -17554,22 +17557,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>51</v>
@@ -17577,22 +17580,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>51</v>
@@ -17600,36 +17603,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{9A550CB5-5EB6-4379-8B91-81519F9A3647}"/>
+  <autoFilter ref="A1:G64" xr:uid="{0DD5BBE2-D235-47F6-8405-7374DB6B9919}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC1DE6A-FEDD-4017-8948-DCBEA77A4BBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD9708FC-F05A-4163-8705-01E14DBC6C9D}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17643,10 +17646,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>32</v>
@@ -17658,7 +17661,7 @@
         <v>178</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -17666,33 +17669,33 @@
     </row>
     <row r="2" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
@@ -17701,21 +17704,21 @@
         <v>114</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>49</v>
@@ -17727,18 +17730,18 @@
         <v>49</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>49</v>
@@ -17750,18 +17753,18 @@
         <v>49</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>89</v>
@@ -17770,21 +17773,21 @@
         <v>159</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>112</v>
@@ -17793,21 +17796,21 @@
         <v>114</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>49</v>
@@ -17819,21 +17822,21 @@
         <v>49</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{4CC1DE6A-FEDD-4017-8948-DCBEA77A4BBE}"/>
+  <autoFilter ref="A1:G8" xr:uid="{CD9708FC-F05A-4163-8705-01E14DBC6C9D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E4F3EA-0A7C-4DF9-AB60-1703F49EF72F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6154803A-7060-4260-B163-0EC9C1928373}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17843,19 +17846,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -17863,66 +17866,66 @@
     </row>
     <row r="2" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>1038</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>1042</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1041</v>
-      </c>
       <c r="F4" s="10" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{77E4F3EA-0A7C-4DF9-AB60-1703F49EF72F}"/>
+  <autoFilter ref="A1:F4" xr:uid="{6154803A-7060-4260-B163-0EC9C1928373}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-Onedrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31836643-5F51-419C-9251-E45EB88AED1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B89FE08-3B43-4D4F-924C-2401F671972A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{9632B8F0-0750-44F8-A501-4955FF517E26}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{C0EFE753-C5F4-4F21-8667-3F7A9DCD6783}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -537,7 +537,7 @@
     <t>다수전 연쇄형 — 대상을 약화 · 파괴 · 흐트러짐으로 만들면 이번 스킬로 아직 안 친 다른 무작위 생존 적에게 추가타 1회, 조건을 만족하면 다시 이어짐(같은 적 재공격 없음 · 단일 적이면 연쇄 없음)</t>
   </si>
   <si>
-    <t>재굴림 아님 · 추가타 위력 처리 (미정) · 구 균열 / 흐트러짐 증폭 / 3굴림 폐기 · 기존 ID OL-B12</t>
+    <t>재굴림 아님 · 추가타 위력 = 원래 1굴림과 같은 위력식 · 범위로 추가타마다 새로 굴림(감쇠 없음) · 추가타 부위 (미정) · 구 균열 / 흐트러짐 증폭 / 3굴림 폐기 · 기존 ID OL-B12</t>
   </si>
   <si>
     <t>활성 9</t>
@@ -1146,10 +1146,10 @@
     <t>덫 (폭발 덫 · 공명 덫 · 전염 덫)</t>
   </si>
   <si>
-    <t>부위 단위. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발(RED) = 스택 비례 확정 피해 (미정) / 공명(BLUE) = 발화 자체를 강화 발화로 — 백우 흐트러짐 피해 증가 (미정) · 적설 봉인 1턴 그대로 + 쇠약 (미정)/1 · 낙일 확정 체력 피해 증가 (미정) / 전염(RED) = 원본 덫 2턴 · 발화 시 전염을 일으킨 적을 뺀 다른 적들의 생존 부위 중 표식 상위 2개(같은 적 두 부위 허용 · 동률 무작위)에 표식 (미정) + 전염 덫 1 · 전염으로 생긴 덫은 그 턴만 · 연쇄 · 재감염 허용</t>
-  </si>
-  <si>
-    <t>덫은 표식을 주지 않음 · 승리 → 덫 설치 → 낙점 → 발화 → 방금 단 덫도 발동</t>
+    <t>부위 단위. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발(RED) = 스택 비례 확정 피해 (미정) / 공명(BLUE) = 발화 자체를 강화 발화로(스택 수 무관 고정값 1회 · 전 스택 소비) — 백우 흐트러짐 피해 증가 (미정) · 적설 봉인 1턴 그대로 + 쇠약 (미정)/1 · 낙일 확정 체력 피해 증가 (미정) / 전염(RED) = 원본 덫 2턴 · 발화 시 전염을 일으킨 적을 뺀 다른 적들의 생존 부위 중 표식 상위 2개(같은 적 두 부위 허용 · 동률 무작위)에 표식 (미정) + 전염 덫 1 · 전염으로 생긴 덫은 그 턴만 · 연쇄 · 재감염 허용</t>
+  </si>
+  <si>
+    <t>덫은 표식을 주지 않음 · 승리 → 덫 설치 → 낙점 → 발화 → 방금 단 덫도 발동 · 폭발 · 공명 덫 = 스택 + 지속 턴(재설치 시 기본 지속으로 갱신 · 턴 종료 −1 · 0이면 스택 소멸, 기본 지속 (미정))</t>
   </si>
   <si>
     <t>코인 축</t>
@@ -1317,7 +1317,7 @@
     <t>무기별 분기 — 같은 효과를 모든 굴림에 반복하지 않음 · 무기별 패키지 가치를 맞춤</t>
   </si>
   <si>
-    <t>각 굴림은 자기 효과만 · 실제 교환 승리시만 · 다부위 적의 표식 · 지정 부위 = 그 적의 표식 최고 생존 부위(동률 무작위)</t>
+    <t>각 굴림은 자기 효과만 · 실제 교환 승리시만 · 다부위 적의 표식 · 지정 부위 = 그 굴림이 이긴 순간 그 적의 표식 최고 생존 부위(동률 무작위)로 예약과 함께 확정 · 발동 전 그 부위가 파괴되면 예약 소멸</t>
   </si>
   <si>
     <t>은신 부여 평타 (가칭)</t>
@@ -1395,7 +1395,7 @@
     <t>피해 처리 후(각 굴림)</t>
   </si>
   <si>
-    <t>그 굴림이 대상 부위를 약화 · 파괴하면 그 부위의 표식 전부를 다른 생존 부위 중 표식 최소 부위로 전이(동률 무작위 · 맞은 부위 제외 · 다른 생존 부위가 없으면 전이 없음 · 정상 44 발화)</t>
+    <t>그 굴림이 대상 부위를 약화 · 파괴하면 그 부위의 표식 전부를 다른 생존 부위 중 표식 최소 부위로 전이(동률 무작위 · 맞은 부위 제외 · 다른 생존 부위가 없으면 뗀 표식 소멸 · 정상 44 발화)</t>
   </si>
   <si>
     <t>구조 확정</t>
@@ -1410,10 +1410,10 @@
     <t>소문을 내다</t>
   </si>
   <si>
-    <t>그 굴림이 대상 부위를 약화 · 파괴하면 다른 모든 생존 적에게 표식 +(미정), 그중 현재 표식 최고 대상 하나에 표식 +(미정) 추가</t>
-  </si>
-  <si>
-    <t>다부위 적의 표식 부위 (미정) · 전체 확산 + 한 대상 발화 압축</t>
+    <t>그 굴림이 대상 부위를 약화 · 파괴하면 방금 공격한 적을 뺀 다른 모든 생존 적의 모든 생존 부위에 표식 +(미정), 그중 현재 표식 최고 부위 하나에 +(미정) 추가(동률 무작위)</t>
+  </si>
+  <si>
+    <t>광역 표식 확산 · 부위가 많은 적일수록 총량이 큰 것은 다부위 특화로 허용</t>
   </si>
   <si>
     <t>F</t>
@@ -4409,7 +4409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99604371-668C-4F2F-A06F-71A4FA92810C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC3E209-9904-44D0-A58D-9D8935D875D7}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4603,7 +4603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67A3A5F-8CE1-45AD-80D1-812A884CF3DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79469D2-8131-4747-A028-4D1E4056EFB7}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4692,14 +4692,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10" xr:uid="{D67A3A5F-8CE1-45AD-80D1-812A884CF3DE}"/>
+  <autoFilter ref="A1:B10" xr:uid="{B79469D2-8131-4747-A028-4D1E4056EFB7}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCF2CA2F-2787-4110-9F87-F0F789F4DE1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AB3273-5552-46CE-9CCD-3743C4B8F88A}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4868,14 +4868,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{DCF2CA2F-2787-4110-9F87-F0F789F4DE1C}"/>
+  <autoFilter ref="A1:F8" xr:uid="{18AB3273-5552-46CE-9CCD-3743C4B8F88A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6765D0-CF53-4FFF-8FE8-E4306A191142}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E719D87C-8343-4201-9DB3-C60E1C5AAEA5}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4986,14 +4986,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6" xr:uid="{FA6765D0-CF53-4FFF-8FE8-E4306A191142}"/>
+  <autoFilter ref="A1:E6" xr:uid="{E719D87C-8343-4201-9DB3-C60E1C5AAEA5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F2692F-6627-4838-AC04-7D00DBCACD61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069A2594-E84F-4A28-BD11-B89A7011DBF9}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5492,14 +5492,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35" xr:uid="{03F2692F-6627-4838-AC04-7D00DBCACD61}"/>
+  <autoFilter ref="A1:D35" xr:uid="{069A2594-E84F-4A28-BD11-B89A7011DBF9}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070C6150-43B0-4D6E-9890-80FB69DFC2EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B854E31B-3F33-47FB-B346-A0300453448C}">
   <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6740,14 +6740,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D88" xr:uid="{070C6150-43B0-4D6E-9890-80FB69DFC2EC}"/>
+  <autoFilter ref="A1:D88" xr:uid="{B854E31B-3F33-47FB-B346-A0300453448C}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B65E706-62F1-42C6-A2D9-EF2C3EDA7E9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{570F073A-97D0-4536-AD07-ACC99746CBFC}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7760,7 +7760,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>85</v>
       </c>
@@ -10303,14 +10303,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{3B65E706-62F1-42C6-A2D9-EF2C3EDA7E9E}"/>
+  <autoFilter ref="A1:T57" xr:uid="{570F073A-97D0-4536-AD07-ACC99746CBFC}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B7669C-4495-4730-9F2A-982B2311E9B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348DCF87-108A-4E5F-9C26-125BBF9DD526}">
   <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10531,7 +10531,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="135" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>52</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="81" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>85</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>178</v>
       </c>
@@ -12582,14 +12582,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{10B7669C-4495-4730-9F2A-982B2311E9B2}"/>
+  <autoFilter ref="A1:M55" xr:uid="{348DCF87-108A-4E5F-9C26-125BBF9DD526}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0FEB4C-DDAF-4A91-B4A5-4020B39F7EFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE02E03-5F97-4664-9AF7-1F9E08CCCC89}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12794,14 +12794,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{BA0FEB4C-DDAF-4A91-B4A5-4020B39F7EFB}"/>
+  <autoFilter ref="A1:O4" xr:uid="{BFE02E03-5F97-4664-9AF7-1F9E08CCCC89}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B4EB47-AF9A-4E74-AFB1-85288A0847F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED75720-E0C1-417E-BA6B-E684EB23892B}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15675,14 +15675,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{B9B4EB47-AF9A-4E74-AFB1-85288A0847F0}"/>
+  <autoFilter ref="A1:T46" xr:uid="{7ED75720-E0C1-417E-BA6B-E684EB23892B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D3978F-DD4D-469A-8664-CBB15B6F2ACB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544B8A02-3A35-43EC-94D2-9FDD05DB0201}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16133,14 +16133,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19" xr:uid="{60D3978F-DD4D-469A-8664-CBB15B6F2ACB}"/>
+  <autoFilter ref="A1:G19" xr:uid="{544B8A02-3A35-43EC-94D2-9FDD05DB0201}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD5BBE2-D235-47F6-8405-7374DB6B9919}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626DDAF4-9589-42C8-896A-69C1A75E70D1}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17625,14 +17625,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{0DD5BBE2-D235-47F6-8405-7374DB6B9919}"/>
+  <autoFilter ref="A1:G64" xr:uid="{626DDAF4-9589-42C8-896A-69C1A75E70D1}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD9708FC-F05A-4163-8705-01E14DBC6C9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8F779D-DACF-4ECF-9819-03D089873F2D}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17829,14 +17829,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{CD9708FC-F05A-4163-8705-01E14DBC6C9D}"/>
+  <autoFilter ref="A1:G8" xr:uid="{1F8F779D-DACF-4ECF-9819-03D089873F2D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6154803A-7060-4260-B163-0EC9C1928373}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B193DF7-5665-4AFC-8DC0-476BE69FB7FC}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17925,7 +17925,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{6154803A-7060-4260-B163-0EC9C1928373}"/>
+  <autoFilter ref="A1:F4" xr:uid="{8B193DF7-5665-4AFC-8DC0-476BE69FB7FC}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FECFA206-6590-42CF-A23C-3B7A5173C555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3214089B-91AE-406D-829C-5991528A38FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{D239F87F-122D-49B6-9F38-1C3D26FAAE66}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{ACAADCDD-4637-4BC2-8AFC-B40A1D8DDA7B}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -1167,10 +1167,10 @@
     <t>덫 (폭발 덫 · 공명 덫 · 전염 덫)</t>
   </si>
   <si>
-    <t>부위 단위. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발(RED) = 스택 비례 확정 피해 (미정) / 공명(BLUE) = 발화 자체를 강화 발화로(스택 수 무관 고정값 1회 · 전 스택 소비) — 백우 흐트러짐 피해 증가 (미정) · 적설 봉인 1턴 그대로 + 쇠약 (미정)/1 · 낙일 확정 체력 피해 증가 (미정) / 전염(RED) = 원본 덫 2턴 · 발화 시 전염을 일으킨 적을 뺀 다른 적들의 생존 부위 중 표식 상위 2개(같은 적 두 부위 허용 · 동률 무작위)에 표식 (미정) + 전염 덫 1 · 전염으로 생긴 덫은 그 턴만 · 연쇄 · 재감염 허용</t>
-  </si>
-  <si>
-    <t>덫은 표식을 주지 않음 · 승리 → 덫 설치 → 낙점 → 발화 → 방금 단 덫도 발동 · 폭발 · 공명 덫 = 스택 + 지속 턴(재설치 시 기본 지속으로 갱신 · 턴 종료 −1 · 0이면 스택 소멸, 기본 지속 (미정))</t>
+    <t>부위 단위. 그 부위 표식이 44에서 발화할 때 함께 발동하고 그 종류를 전부 소비. 폭발(RED) = 살아 있는 폭발 덫 수 × 스택당 확정 피해 (미정) 한 번 / 공명(BLUE) = 발화 자체를 강화 발화로(스택 수 무관 고정값 1회 · 전 스택 소비) — 백우 흐트러짐 피해 증가 (미정) · 적설 봉인 1턴 그대로 + 쇠약 (미정)/1 · 낙일 확정 체력 피해 증가 (미정) / 전염(RED) = 원본 덫 2턴 · 발화 시 전염을 일으킨 적을 뺀 다른 적들의 생존 부위 중 표식 상위 2개(같은 적 두 부위 허용 · 동률 무작위)에 표식 (미정) + 전염 덫 1 · 전염으로 생긴 덫은 그 턴만 · 연쇄 · 재감염 허용</t>
+  </si>
+  <si>
+    <t>덫은 표식을 주지 않음 · 승리 → 덫 설치 → 낙점 → 발화 → 방금 단 덫도 발동 · 폭발 · 공명 덫 = 설치 1회마다 독립 덫 1개 · 덫마다 지속 따로(턴 종료 −1 · 0이 된 덫만 소멸 · 재설치가 기존 지속을 갱신하지 않음, 기본 지속 (미정)) · 발화 시 같은 종류 전부 한 사건으로 발동 후 전부 소비</t>
   </si>
   <si>
     <t>코인 축</t>
@@ -4430,7 +4430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C230E1F5-BF2B-419B-8643-891E172E6290}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9759BCEA-1FF5-49E0-8B7C-F93C79D28A89}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4624,7 +4624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A10BB8-1BC5-4FDD-9310-FE5C938B4DB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A01D55-BD55-40EA-9A0C-983FB95C98A6}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4713,14 +4713,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10" xr:uid="{E2A10BB8-1BC5-4FDD-9310-FE5C938B4DB5}"/>
+  <autoFilter ref="A1:B10" xr:uid="{71A01D55-BD55-40EA-9A0C-983FB95C98A6}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0921646-15F4-47E0-B5F5-16D67188A061}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC00CACD-0FDC-4753-A269-77008F22403D}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4889,14 +4889,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{E0921646-15F4-47E0-B5F5-16D67188A061}"/>
+  <autoFilter ref="A1:F8" xr:uid="{FC00CACD-0FDC-4753-A269-77008F22403D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD063870-836A-4E57-8721-C7BC792091F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4D4A8D-32C8-4064-8B3C-2CA81C1F745F}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5007,14 +5007,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6" xr:uid="{DD063870-836A-4E57-8721-C7BC792091F2}"/>
+  <autoFilter ref="A1:E6" xr:uid="{1A4D4A8D-32C8-4064-8B3C-2CA81C1F745F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E2E128-DD5C-4F40-8643-C5618B9D82BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA396A7-33C2-49CD-8702-551CC57C9A01}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5513,14 +5513,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35" xr:uid="{35E2E128-DD5C-4F40-8643-C5618B9D82BD}"/>
+  <autoFilter ref="A1:D35" xr:uid="{9AA396A7-33C2-49CD-8702-551CC57C9A01}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C050CE3-46DF-467F-9325-F59334B6407B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A07E2E-402B-4019-AA5E-3D40B532FB89}">
   <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6761,14 +6761,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D88" xr:uid="{5C050CE3-46DF-467F-9325-F59334B6407B}"/>
+  <autoFilter ref="A1:D88" xr:uid="{96A07E2E-402B-4019-AA5E-3D40B532FB89}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0982D01-5A18-4572-A717-2545360A89E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF52461-8B9B-4C88-8111-9A3645349B3A}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10324,14 +10324,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{B0982D01-5A18-4572-A717-2545360A89E0}"/>
+  <autoFilter ref="A1:T57" xr:uid="{CFF52461-8B9B-4C88-8111-9A3645349B3A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A60AED-23B9-4FE5-8F5A-83FCEBB1DFD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A10065F-DB4C-4289-809D-321F842ACF00}">
   <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12603,14 +12603,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{F7A60AED-23B9-4FE5-8F5A-83FCEBB1DFD8}"/>
+  <autoFilter ref="A1:M55" xr:uid="{8A10065F-DB4C-4289-809D-321F842ACF00}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81C47FE-92C6-4620-AD80-7AC1B546A7AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FB53DD-B059-489C-8B31-526D48BCA5F9}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12815,14 +12815,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{D81C47FE-92C6-4620-AD80-7AC1B546A7AA}"/>
+  <autoFilter ref="A1:O4" xr:uid="{F7FB53DD-B059-489C-8B31-526D48BCA5F9}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F50FBB9-67D5-421D-A6DF-078318554BA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B3D028-0FA9-4EB4-ADF3-7CEF71E292A6}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15696,14 +15696,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{0F50FBB9-67D5-421D-A6DF-078318554BA4}"/>
+  <autoFilter ref="A1:T46" xr:uid="{77B3D028-0FA9-4EB4-ADF3-7CEF71E292A6}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588D8467-FC1F-4894-BF76-F52064971E4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9A9F8F-6CC5-4FAC-B460-7896B9D6CCE1}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16154,14 +16154,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19" xr:uid="{588D8467-FC1F-4894-BF76-F52064971E4C}"/>
+  <autoFilter ref="A1:G19" xr:uid="{8B9A9F8F-6CC5-4FAC-B460-7896B9D6CCE1}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FDDA69-A26A-41A3-9E27-0EC479971E82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7CC5F02-ACAC-4E91-8581-825D5499ACF8}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17646,14 +17646,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{75FDDA69-A26A-41A3-9E27-0EC479971E82}"/>
+  <autoFilter ref="A1:G64" xr:uid="{E7CC5F02-ACAC-4E91-8581-825D5499ACF8}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF3FB79-12B9-4A08-BE63-D4E48FB0A57B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066E5819-F51D-4ACE-850A-4C33677B2731}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17850,14 +17850,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{3DF3FB79-12B9-4A08-BE63-D4E48FB0A57B}"/>
+  <autoFilter ref="A1:G8" xr:uid="{066E5819-F51D-4ACE-850A-4C33677B2731}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61F63045-3400-4742-A2BC-5AF51F7540EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D65F09C-C37E-485C-ACA4-D68FF0FD9AD1}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17946,7 +17946,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{61F63045-3400-4742-A2BC-5AF51F7540EE}"/>
+  <autoFilter ref="A1:F4" xr:uid="{3D65F09C-C37E-485C-ACA4-D68FF0FD9AD1}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/전투 콘텐츠 명세.xlsx
+++ b/Docs/전투 콘텐츠 명세.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{711AAB88-FC1D-4092-A215-9ED3FFA73789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1406D0A1-658E-4FC5-BBB7-5E58D6DCA5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{9AB0FFF3-1DA2-4483-AEB5-36891EF5C814}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{648B497A-C8B1-4EA4-AF23-AA54D6185F1C}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="1293">
   <si>
     <t>Project Abyss — 전투 콘텐츠 명세 (2026-09-25)</t>
   </si>
@@ -765,216 +765,219 @@
     <t>굳히기</t>
   </si>
   <si>
-    <t>각 굴림 사용시 현재 상대 출혈이 8 이상이면 자신에게 다음 턴 힘 1만큼 1턴</t>
+    <t>1굴림 사용시 상대 출혈 2 이상이면 출혈 2 소모 → 자신에게 힘 1만큼 1턴 · 2굴림 사용시 상대 출혈 2 이상이면 출혈 2 소모 → 자신에게 신속 1만큼 2턴(둘 다 즉시 적용) · 3굴림 사용시 자신이 힘과 신속을 동시에 보유 중이면 위세 게이지 +10. 출혈이 모자라면 그 효과와 출혈 소모만 불발(굴림은 정상)</t>
+  </si>
+  <si>
+    <t>구조 확정 (10-08) · 수치 채택(실측 가능)</t>
+  </si>
+  <si>
+    <t>구 출혈 문턱 → 다음 턴 힘 폐기 · 신속은 그 턴 속도 굴림 뒤에 적용되므로 2턴 · 기존 ID OL-D11</t>
+  </si>
+  <si>
+    <t>피의 대가</t>
+  </si>
+  <si>
+    <t>자기 출혈 (미정) 추가 → 증가 후 현재 자기 출혈 구간 판정 → 자신에게 힘 (미정) 부여</t>
+  </si>
+  <si>
+    <t>구조 확정 · 위력 −3 확정(10-07) · 출혈 · 힘 미정</t>
+  </si>
+  <si>
+    <t>순서 고정 · 기존 ID OL-D15</t>
+  </si>
+  <si>
+    <t>활성 12</t>
+  </si>
+  <si>
+    <t>피의 맹세</t>
+  </si>
+  <si>
+    <t>파괴형(조건부)</t>
+  </si>
+  <si>
+    <t>14~19</t>
+  </si>
+  <si>
+    <t>자기 출혈 전부 제거 → 제거량 구간별 보상: 0~4 없음 / 5~9 위력 +2 · 재생 2만큼 3턴 · 1굴림 승리시 출혈 2 / 10+ 위력 +4 · 각 굴림 승리시 출혈 2 · 빛 +1 · 처형 권한</t>
+  </si>
+  <si>
+    <t>파괴 권한(조건부) · 처형(10+)</t>
+  </si>
+  <si>
+    <t>기존 ID OL-D19</t>
+  </si>
+  <si>
+    <t>활성 13</t>
+  </si>
+  <si>
+    <t>닥치는 대로</t>
+  </si>
+  <si>
+    <t>4 (가변)</t>
+  </si>
+  <si>
+    <t>1굴림 사용시 광기 1 획득 + 다음 사용부터 비용 −1(전투 내 누적, 최저 1)</t>
+  </si>
+  <si>
+    <t>기존 ID OL-D17</t>
+  </si>
+  <si>
+    <t>활성 14</t>
+  </si>
+  <si>
+    <t>명예로운 전투</t>
+  </si>
+  <si>
+    <t>17~23</t>
+  </si>
+  <si>
+    <t>전투 시작시</t>
+  </si>
+  <si>
+    <t>상대 스킬을 전용 대응 스킬로 강제 교체 → 양쪽 전용 1굴림 교환. 버프·디버프 정상 적용. 동점은 공통 재굴림. 어느 한쪽 대상 부위가 약화 · 파괴되면 종료, 둘 다 아니면 같은 교환 반복. 일반 몹은 처치 = 파괴</t>
+  </si>
+  <si>
+    <t>구조 확정 (09-28) · 수치 미정</t>
+  </si>
+  <si>
+    <t>기존 ID OL-D18</t>
+  </si>
+  <si>
+    <t>활성 15</t>
+  </si>
+  <si>
+    <t>일기토</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10~17</t>
+  </si>
+  <si>
+    <t>조준 규칙 / 사용시</t>
+  </si>
+  <si>
+    <t>대상 슬롯 독점. 기존 조준 해제 · 대상 변경/취소 시 잠금 해제 · 자동 복구 없음 · 해결 단계 조준 고정. 각 굴림 사용시 상대 출혈 2</t>
+  </si>
+  <si>
+    <t>파괴 권한 · 타겟 독점</t>
+  </si>
+  <si>
+    <t>기존 ID OL-D21</t>
+  </si>
+  <si>
+    <t>활성 16</t>
+  </si>
+  <si>
+    <t>중형 광기 소비 결투(이름 미정)</t>
+  </si>
+  <si>
+    <t>(미정)</t>
+  </si>
+  <si>
+    <t>광기 N 소비 시도. 성공 시 공포 + 이후 이 스킬에서 실제 교환 승리마다 추가 출혈 N. 실패 시 rider만 불발하고 카드·결투 정상 진행</t>
+  </si>
+  <si>
+    <t>구조 확정 · 수치 미정</t>
+  </si>
+  <si>
+    <t>활성 17</t>
+  </si>
+  <si>
+    <t>대형 광기 전량 소비 결투(이름 미정)</t>
+  </si>
+  <si>
+    <t>현재 광기 전부 소비 → 실제 소비량 기록 → 소비량 구간에 따라 최종 굴림 수 확정. 광기 8 전량 소비(최고 구간)면 이 스킬의 각 공격 적중마다 상대 출혈 +1 — 만개가 풀린 뒤라 만개 출혈과 겹치지 않음</t>
+  </si>
+  <si>
+    <t>합 도중 광기 변화로 굴림 수 재계산하지 않음</t>
+  </si>
+  <si>
+    <t>도사림</t>
+  </si>
+  <si>
+    <t>웅크리기</t>
+  </si>
+  <si>
+    <t>약한</t>
+  </si>
+  <si>
+    <t>도사림 발동시</t>
+  </si>
+  <si>
+    <t>방어도 12</t>
+  </si>
+  <si>
+    <t>전 캐릭터 공용</t>
+  </si>
+  <si>
+    <t>노려보기</t>
+  </si>
+  <si>
+    <t>이번 턴 전체 판정 +1</t>
+  </si>
+  <si>
+    <t>블로토</t>
+  </si>
+  <si>
+    <t>blót</t>
+  </si>
+  <si>
+    <t>강한</t>
+  </si>
+  <si>
+    <t>자기 최저 체력 부위 약화 + 광기 2 + 적에게 공포 3턴</t>
+  </si>
+  <si>
+    <t>피의 서약</t>
+  </si>
+  <si>
+    <t>현재 HP 70% 미만이고 피의 서약 재생이 활성 아니면 자신에게 자기 출혈 2 + 재생 4만큼 3턴. 아니면 효과만 불발</t>
+  </si>
+  <si>
+    <t>HP 70%는 효과 조건(직접 회복 카드)</t>
+  </si>
+  <si>
+    <t>피로 사는 숨</t>
+  </si>
+  <si>
+    <t>자신에게 자기 출혈 2 + 빛 1</t>
+  </si>
+  <si>
+    <t>광기를 가라앉히다</t>
+  </si>
+  <si>
+    <t>현재 HP 70% 미만이면 광기 2 소모 → 체력 30 회복 + 위세 게이지 +10. HP 조건 불충족 · 광기 부족이면 효과만 불발하고 도사림 사용 유지</t>
+  </si>
+  <si>
+    <t>HP 70%는 효과 조건(직접 회복)</t>
+  </si>
+  <si>
+    <t>구조 확정 (10-08) · 회복 30 · 위세 10은 임시값(측정 대상)</t>
+  </si>
+  <si>
+    <t>구 광기 2 → 빛 +1 · 구 승리 출혈 구조 폐기</t>
+  </si>
+  <si>
+    <t>상처를 지우다</t>
+  </si>
+  <si>
+    <t>자기 출혈 최대 4 소비 → 실제 소비 1 ~ 2 = 이번 턴 위력 +1 / 3 ~ 4 = +2. 0이면 효과 없음</t>
+  </si>
+  <si>
+    <t>HP 조건 없음 · 구 5 소비 위력 +2 폐기</t>
+  </si>
+  <si>
+    <t>흐트러짐을 삼키다</t>
+  </si>
+  <si>
+    <t>현재 HP 70% 미만이면 자기 흐트러짐 20 소비 → 체력 30 회복. 아니면 효과만 불발</t>
   </si>
   <si>
     <t>확정 (10-07)</t>
   </si>
   <si>
-    <t>단일 문턱 — 구 0~4 / 5~9 / 10+ → 힘 0 / 1 / 2 사다리 폐기 · 기존 ID OL-D11</t>
-  </si>
-  <si>
-    <t>피의 대가</t>
-  </si>
-  <si>
-    <t>자기 출혈 (미정) 추가 → 증가 후 현재 자기 출혈 구간 판정 → 자신에게 힘 (미정) 부여</t>
-  </si>
-  <si>
-    <t>구조 확정 · 위력 −3 확정(10-07) · 출혈 · 힘 미정</t>
-  </si>
-  <si>
-    <t>순서 고정 · 기존 ID OL-D15</t>
-  </si>
-  <si>
-    <t>활성 12</t>
-  </si>
-  <si>
-    <t>피의 맹세</t>
-  </si>
-  <si>
-    <t>파괴형(조건부)</t>
-  </si>
-  <si>
-    <t>14~19</t>
-  </si>
-  <si>
-    <t>자기 출혈 전부 제거 → 제거량 구간별 보상: 0~4 없음 / 5~9 위력 +2 · 재생 2만큼 3턴 · 1굴림 승리시 출혈 2 / 10+ 위력 +4 · 각 굴림 승리시 출혈 2 · 빛 +1 · 처형 권한</t>
-  </si>
-  <si>
-    <t>파괴 권한(조건부) · 처형(10+)</t>
-  </si>
-  <si>
-    <t>기존 ID OL-D19</t>
-  </si>
-  <si>
-    <t>활성 13</t>
-  </si>
-  <si>
-    <t>닥치는 대로</t>
-  </si>
-  <si>
-    <t>4 (가변)</t>
-  </si>
-  <si>
-    <t>1굴림 사용시 광기 1 획득 + 다음 사용부터 비용 −1(전투 내 누적, 최저 1)</t>
-  </si>
-  <si>
-    <t>기존 ID OL-D17</t>
-  </si>
-  <si>
-    <t>활성 14</t>
-  </si>
-  <si>
-    <t>명예로운 전투</t>
-  </si>
-  <si>
-    <t>17~23</t>
-  </si>
-  <si>
-    <t>전투 시작시</t>
-  </si>
-  <si>
-    <t>상대 스킬을 전용 대응 스킬로 강제 교체 → 양쪽 전용 1굴림 교환. 버프·디버프 정상 적용. 동점은 공통 재굴림. 어느 한쪽 대상 부위가 약화 · 파괴되면 종료, 둘 다 아니면 같은 교환 반복. 일반 몹은 처치 = 파괴</t>
-  </si>
-  <si>
-    <t>구조 확정 (09-28) · 수치 미정</t>
-  </si>
-  <si>
-    <t>기존 ID OL-D18</t>
-  </si>
-  <si>
-    <t>활성 15</t>
-  </si>
-  <si>
-    <t>일기토</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10~17</t>
-  </si>
-  <si>
-    <t>조준 규칙 / 사용시</t>
-  </si>
-  <si>
-    <t>대상 슬롯 독점. 기존 조준 해제 · 대상 변경/취소 시 잠금 해제 · 자동 복구 없음 · 해결 단계 조준 고정. 각 굴림 사용시 상대 출혈 2</t>
-  </si>
-  <si>
-    <t>파괴 권한 · 타겟 독점</t>
-  </si>
-  <si>
-    <t>기존 ID OL-D21</t>
-  </si>
-  <si>
-    <t>활성 16</t>
-  </si>
-  <si>
-    <t>중형 광기 소비 결투(이름 미정)</t>
-  </si>
-  <si>
-    <t>(미정)</t>
-  </si>
-  <si>
-    <t>광기 N 소비 시도. 성공 시 공포 + 이후 이 스킬에서 실제 교환 승리마다 추가 출혈 N. 실패 시 rider만 불발하고 카드·결투 정상 진행</t>
-  </si>
-  <si>
-    <t>구조 확정 · 수치 미정</t>
-  </si>
-  <si>
-    <t>활성 17</t>
-  </si>
-  <si>
-    <t>대형 광기 전량 소비 결투(이름 미정)</t>
-  </si>
-  <si>
-    <t>현재 광기 전부 소비 → 실제 소비량 기록 → 소비량 구간에 따라 최종 굴림 수 확정. 광기 8 전량 소비(최고 구간)면 이 스킬의 각 공격 적중마다 상대 출혈 +1 — 만개가 풀린 뒤라 만개 출혈과 겹치지 않음</t>
-  </si>
-  <si>
-    <t>합 도중 광기 변화로 굴림 수 재계산하지 않음</t>
-  </si>
-  <si>
-    <t>도사림</t>
-  </si>
-  <si>
-    <t>웅크리기</t>
-  </si>
-  <si>
-    <t>약한</t>
-  </si>
-  <si>
-    <t>도사림 발동시</t>
-  </si>
-  <si>
-    <t>방어도 12</t>
-  </si>
-  <si>
-    <t>전 캐릭터 공용</t>
-  </si>
-  <si>
-    <t>노려보기</t>
-  </si>
-  <si>
-    <t>이번 턴 전체 판정 +1</t>
-  </si>
-  <si>
-    <t>블로토</t>
-  </si>
-  <si>
-    <t>blót</t>
-  </si>
-  <si>
-    <t>강한</t>
-  </si>
-  <si>
-    <t>자기 최저 체력 부위 약화 + 광기 2 + 적에게 공포 3턴</t>
-  </si>
-  <si>
-    <t>피의 서약</t>
-  </si>
-  <si>
-    <t>현재 HP 70% 미만이고 피의 서약 재생이 활성 아니면 자신에게 자기 출혈 2 + 재생 4만큼 3턴. 아니면 효과만 불발</t>
-  </si>
-  <si>
-    <t>HP 70%는 효과 조건(직접 회복 카드)</t>
-  </si>
-  <si>
-    <t>피로 사는 숨</t>
-  </si>
-  <si>
-    <t>자신에게 자기 출혈 2 + 빛 1</t>
-  </si>
-  <si>
-    <t>광기를 가라앉히다</t>
-  </si>
-  <si>
-    <t>현재 HP 70% 미만이면 광기 (미정) 소비 시도. 성공하면 체력 30 회복. HP 조건 불충족 · 광기 부족이면 효과만 불발하고 도사림 사용 유지</t>
-  </si>
-  <si>
-    <t>HP 70%는 효과 조건(직접 회복)</t>
-  </si>
-  <si>
-    <t>구조 확정 · 광기 소비량 미정(2 / 3 / 4 비교)</t>
-  </si>
-  <si>
-    <t>구 승리 출혈 구조 폐기</t>
-  </si>
-  <si>
-    <t>상처를 지우다</t>
-  </si>
-  <si>
-    <t>자기 출혈 최대 4 소비 → 실제 소비 1 ~ 2 = 이번 턴 위력 +1 / 3 ~ 4 = +2. 0이면 효과 없음</t>
-  </si>
-  <si>
-    <t>HP 조건 없음 · 구 5 소비 위력 +2 폐기</t>
-  </si>
-  <si>
-    <t>흐트러짐을 삼키다</t>
-  </si>
-  <si>
-    <t>현재 HP 70% 미만이면 자기 흐트러짐 20 소비 → 체력 30 회복. 아니면 효과만 불발</t>
-  </si>
-  <si>
     <t>구 체력 20</t>
   </si>
   <si>
@@ -993,13 +996,13 @@
     <t>자기 출혈 소비 방어형(이름 미정)</t>
   </si>
   <si>
-    <t>자기 출혈 최대 4 소비 → 실제 소비 1당 방어도 +(미정). 자기 출혈 0이면 효과 없음</t>
+    <t>자기 출혈 최대 4 소비 → 실제 소비 1당 방어도 +10. 자기 출혈 0이면 효과 없음</t>
   </si>
   <si>
     <t>HP 조건 없음</t>
   </si>
   <si>
-    <t>구조 확정 · 1당 방어도 미정(8 / 10 / 12 비교)</t>
+    <t>확정 (10-08)</t>
   </si>
   <si>
     <t>구 HP 50% · 전부 제거 · 1당 방어도 1 폐기</t>
@@ -3156,7 +3159,7 @@
     <t>개체 체력 역할별 (미정) — 인원수 · 플레이어 캐릭터와 무관 · 흐트러짐 100 · 부위 없음</t>
   </si>
   <si>
-    <t>소스 균등 1~8 · 발악 없음 · 1층 12종(개발용 가명)은 규칙서 12.3 · 1층 파괴 권한은 파쇄병만 · 각 몹이 자기 행동 로직으로 공격 · 결투 · 지원 결정</t>
+    <t>소스 균등 1~8 · 발악 없음 · 1층 12종(개발용 가명)은 규칙서 12.3 · 1층 파괴 권한은 파쇄병(빛 2 파쇄 결투)만 · 행동마다 빛 비용(대개 일반 공격 0 · 기본 결투 1 · 강한 결투 2) — 빛은 행동을 가능하게 할 뿐 강제하지 않는다 · 행동 선택은 몹마다 AI 확률</t>
   </si>
   <si>
     <t>적 공통</t>
@@ -4460,7 +4463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E860081D-21E0-43F0-9A38-2074324B3131}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53754AAC-3A00-40BE-A449-325F32E6F605}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4654,7 +4657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDE9207-5C40-459D-9BF0-03BACCF2DC80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1076E61-642B-44A3-92D8-56E1147C82F2}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4664,93 +4667,93 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10" xr:uid="{8FDE9207-5C40-459D-9BF0-03BACCF2DC80}"/>
+  <autoFilter ref="A1:B10" xr:uid="{D1076E61-642B-44A3-92D8-56E1147C82F2}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D9D2B04-3A31-4BCA-AC22-34063ED70A63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938E2BAC-22B4-4DD8-8390-9D93DACDC3BB}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4760,19 +4763,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -4780,56 +4783,56 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -4840,93 +4843,93 @@
     </row>
     <row r="5" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{2D9D2B04-3A31-4BCA-AC22-34063ED70A63}"/>
+  <autoFilter ref="A1:F8" xr:uid="{938E2BAC-22B4-4DD8-8390-9D93DACDC3BB}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DD5135-C7D4-48CF-90DC-2682C822948B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F52BAA3-3393-4A4B-975A-A4C89802D564}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4936,16 +4939,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>45</v>
@@ -4953,16 +4956,16 @@
     </row>
     <row r="2" spans="1:5" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -4970,81 +4973,81 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6" xr:uid="{98DD5135-C7D4-48CF-90DC-2682C822948B}"/>
+  <autoFilter ref="A1:E6" xr:uid="{0F52BAA3-3393-4A4B-975A-A4C89802D564}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85927B4A-EA88-4AFA-9571-390C76DF1CA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91130843-0C98-4A9C-AD13-ECFD23D55D54}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5054,10 +5057,10 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -5068,7 +5071,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -5082,27 +5085,27 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>1</v>
@@ -5110,13 +5113,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5124,13 +5127,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1</v>
@@ -5138,13 +5141,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>1</v>
@@ -5152,13 +5155,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>1</v>
@@ -5166,7 +5169,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>1</v>
@@ -5180,13 +5183,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1</v>
@@ -5194,13 +5197,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>1</v>
@@ -5208,13 +5211,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>1</v>
@@ -5222,7 +5225,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1</v>
@@ -5236,41 +5239,41 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>1</v>
@@ -5278,13 +5281,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>1</v>
@@ -5292,13 +5295,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>1</v>
@@ -5306,13 +5309,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>1</v>
@@ -5320,13 +5323,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>1</v>
@@ -5334,7 +5337,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>1</v>
@@ -5348,13 +5351,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>1</v>
@@ -5362,13 +5365,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>1</v>
@@ -5376,13 +5379,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1</v>
@@ -5390,7 +5393,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>1</v>
@@ -5404,13 +5407,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1</v>
@@ -5418,27 +5421,27 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1</v>
@@ -5446,13 +5449,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1</v>
@@ -5460,13 +5463,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1</v>
@@ -5474,13 +5477,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1</v>
@@ -5488,13 +5491,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1</v>
@@ -5502,7 +5505,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>1</v>
@@ -5516,13 +5519,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1</v>
@@ -5530,27 +5533,27 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35" xr:uid="{85927B4A-EA88-4AFA-9571-390C76DF1CA5}"/>
+  <autoFilter ref="A1:D35" xr:uid="{91130843-0C98-4A9C-AD13-ECFD23D55D54}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1659DC20-5058-4D8F-A708-DEBC572FFDA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68940045-0926-403B-892A-1CBCD4EC91CD}">
   <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5563,7 +5566,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>42</v>
@@ -5574,7 +5577,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -5588,13 +5591,13 @@
     </row>
     <row r="3" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1</v>
@@ -5602,27 +5605,27 @@
     </row>
     <row r="4" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
@@ -5630,97 +5633,97 @@
     </row>
     <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>1</v>
@@ -5728,13 +5731,13 @@
     </row>
     <row r="13" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1</v>
@@ -5742,21 +5745,21 @@
     </row>
     <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>1</v>
@@ -5770,49 +5773,49 @@
     </row>
     <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>1</v>
@@ -5826,7 +5829,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1</v>
@@ -5840,7 +5843,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>1</v>
@@ -5854,7 +5857,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>1</v>
@@ -5868,7 +5871,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>1</v>
@@ -5882,7 +5885,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>1</v>
@@ -5896,7 +5899,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>1</v>
@@ -5910,7 +5913,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>1</v>
@@ -5924,7 +5927,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>1</v>
@@ -5938,7 +5941,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>1</v>
@@ -5952,7 +5955,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>1</v>
@@ -5966,7 +5969,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>1</v>
@@ -5980,7 +5983,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>1</v>
@@ -5994,7 +5997,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>1</v>
@@ -6008,7 +6011,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>1</v>
@@ -6022,7 +6025,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>1</v>
@@ -6036,7 +6039,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>1</v>
@@ -6050,7 +6053,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>1</v>
@@ -6064,7 +6067,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>1</v>
@@ -6078,7 +6081,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>1</v>
@@ -6092,7 +6095,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>1</v>
@@ -6106,7 +6109,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>1</v>
@@ -6120,7 +6123,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>1</v>
@@ -6134,7 +6137,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>1</v>
@@ -6148,7 +6151,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>1</v>
@@ -6162,7 +6165,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>1</v>
@@ -6176,7 +6179,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>1</v>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>1</v>
@@ -6204,7 +6207,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>1</v>
@@ -6218,7 +6221,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>1</v>
@@ -6232,7 +6235,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>1</v>
@@ -6246,7 +6249,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>1</v>
@@ -6260,7 +6263,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>1</v>
@@ -6274,7 +6277,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>1</v>
@@ -6288,7 +6291,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>1</v>
@@ -6302,7 +6305,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>1</v>
@@ -6316,7 +6319,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>1</v>
@@ -6330,55 +6333,55 @@
     </row>
     <row r="56" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>1</v>
@@ -6386,105 +6389,105 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>1</v>
@@ -6498,13 +6501,13 @@
     </row>
     <row r="68" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>1</v>
@@ -6512,13 +6515,13 @@
     </row>
     <row r="69" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B69" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>1288</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>1287</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>1</v>
@@ -6526,13 +6529,13 @@
     </row>
     <row r="70" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>1</v>
@@ -6540,7 +6543,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>1</v>
@@ -6554,7 +6557,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>1</v>
@@ -6568,7 +6571,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>1</v>
@@ -6582,7 +6585,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>1</v>
@@ -6596,7 +6599,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>1</v>
@@ -6610,7 +6613,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>1</v>
@@ -6624,7 +6627,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>1</v>
@@ -6638,7 +6641,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>1</v>
@@ -6652,13 +6655,13 @@
     </row>
     <row r="79" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>1</v>
@@ -6666,7 +6669,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>1</v>
@@ -6680,7 +6683,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>1</v>
@@ -6694,7 +6697,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>1</v>
@@ -6708,7 +6711,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>1</v>
@@ -6722,7 +6725,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>1</v>
@@ -6736,7 +6739,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>1</v>
@@ -6750,7 +6753,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>1</v>
@@ -6764,7 +6767,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>1</v>
@@ -6778,7 +6781,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>1</v>
@@ -6791,14 +6794,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D88" xr:uid="{1659DC20-5058-4D8F-A708-DEBC572FFDA9}"/>
+  <autoFilter ref="A1:D88" xr:uid="{68940045-0926-403B-892A-1CBCD4EC91CD}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6C0FCD-37B7-4C5A-975A-7E319A993F59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED479E9-C2C0-4D0C-927C-F502DA0F000C}">
   <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8617,7 +8620,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="54" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>180</v>
       </c>
@@ -9603,10 +9606,10 @@
         <v>294</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>233</v>
+        <v>302</v>
       </c>
       <c r="T45" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="40.5" x14ac:dyDescent="0.3">
@@ -9617,7 +9620,7 @@
         <v>159</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>1</v>
@@ -9656,13 +9659,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q46" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S46" s="7" t="s">
         <v>270</v>
@@ -9679,7 +9682,7 @@
         <v>165</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>1</v>
@@ -9721,27 +9724,27 @@
         <v>278</v>
       </c>
       <c r="Q47" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R47" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="T47" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>1</v>
@@ -9750,7 +9753,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>1</v>
@@ -9780,10 +9783,10 @@
         <v>1</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q48" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R48" s="9" t="s">
         <v>1</v>
@@ -9797,13 +9800,13 @@
     </row>
     <row r="49" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>1</v>
@@ -9812,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>1</v>
@@ -9842,10 +9845,10 @@
         <v>1</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q49" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R49" s="9" t="s">
         <v>1</v>
@@ -9859,13 +9862,13 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>1</v>
@@ -9874,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>1</v>
@@ -9904,10 +9907,10 @@
         <v>1</v>
       </c>
       <c r="P50" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q50" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R50" s="9" t="s">
         <v>1</v>
@@ -9921,13 +9924,13 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>1</v>
@@ -9969,7 +9972,7 @@
         <v>177</v>
       </c>
       <c r="Q51" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>1</v>
@@ -9978,18 +9981,18 @@
         <v>270</v>
       </c>
       <c r="T51" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>1</v>
@@ -10028,10 +10031,10 @@
         <v>94</v>
       </c>
       <c r="P52" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q52" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>1</v>
@@ -10040,18 +10043,18 @@
         <v>270</v>
       </c>
       <c r="T52" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>1</v>
@@ -10090,10 +10093,10 @@
         <v>94</v>
       </c>
       <c r="P53" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q53" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>1</v>
@@ -10107,13 +10110,13 @@
     </row>
     <row r="54" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>1</v>
@@ -10152,10 +10155,10 @@
         <v>94</v>
       </c>
       <c r="P54" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q54" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>1</v>
@@ -10164,18 +10167,18 @@
         <v>270</v>
       </c>
       <c r="T54" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>1</v>
@@ -10214,10 +10217,10 @@
         <v>94</v>
       </c>
       <c r="P55" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q55" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R55" s="7" t="s">
         <v>1</v>
@@ -10226,18 +10229,18 @@
         <v>270</v>
       </c>
       <c r="T55" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>1</v>
@@ -10276,10 +10279,10 @@
         <v>94</v>
       </c>
       <c r="P56" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q56" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R56" s="7" t="s">
         <v>1</v>
@@ -10293,13 +10296,13 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>1</v>
@@ -10338,10 +10341,10 @@
         <v>94</v>
       </c>
       <c r="P57" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q57" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R57" s="7" t="s">
         <v>1</v>
@@ -10354,14 +10357,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T57" xr:uid="{5F6C0FCD-37B7-4C5A-975A-7E319A993F59}"/>
+  <autoFilter ref="A1:T57" xr:uid="{0ED479E9-C2C0-4D0C-927C-F502DA0F000C}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F40C8A-9C5E-4034-9FCD-0116881D43A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C7351B-B3DF-49E7-9CE5-F710284C9119}">
   <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10400,13 +10403,13 @@
         <v>41</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>43</v>
@@ -10426,7 +10429,7 @@
         <v>46</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>1</v>
@@ -10441,13 +10444,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>1</v>
@@ -10456,7 +10459,7 @@
         <v>51</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -10467,7 +10470,7 @@
         <v>53</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>1</v>
@@ -10482,13 +10485,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>1</v>
@@ -10497,7 +10500,7 @@
         <v>51</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -10508,7 +10511,7 @@
         <v>53</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>1</v>
@@ -10520,16 +10523,16 @@
         <v>1</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>1</v>
@@ -10549,7 +10552,7 @@
         <v>53</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>1</v>
@@ -10564,13 +10567,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>1</v>
@@ -10579,7 +10582,7 @@
         <v>270</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="135" x14ac:dyDescent="0.3">
@@ -10590,7 +10593,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>1</v>
@@ -10605,13 +10608,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>1</v>
@@ -10620,7 +10623,7 @@
         <v>270</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -10628,10 +10631,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>1</v>
@@ -10643,16 +10646,16 @@
         <v>112</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>1</v>
@@ -10661,7 +10664,7 @@
         <v>51</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
@@ -10669,10 +10672,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>1</v>
@@ -10687,13 +10690,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>1</v>
@@ -10702,7 +10705,7 @@
         <v>51</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54" x14ac:dyDescent="0.3">
@@ -10710,10 +10713,10 @@
         <v>69</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>1</v>
@@ -10728,13 +10731,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>1</v>
@@ -10743,7 +10746,7 @@
         <v>51</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -10751,10 +10754,10 @@
         <v>69</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>1</v>
@@ -10775,7 +10778,7 @@
         <v>49</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>1</v>
@@ -10792,10 +10795,10 @@
         <v>69</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>1</v>
@@ -10816,7 +10819,7 @@
         <v>49</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>226</v>
@@ -10825,7 +10828,7 @@
         <v>51</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -10836,7 +10839,7 @@
         <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>88</v>
@@ -10851,13 +10854,13 @@
         <v>49</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>1</v>
@@ -10866,7 +10869,7 @@
         <v>51</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -10877,7 +10880,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>101</v>
@@ -10889,16 +10892,16 @@
         <v>111</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>1</v>
@@ -10918,7 +10921,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>88</v>
@@ -10933,22 +10936,22 @@
         <v>194</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>270</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -10959,7 +10962,7 @@
         <v>49</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>88</v>
@@ -10971,25 +10974,25 @@
         <v>112</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>270</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -11000,7 +11003,7 @@
         <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>88</v>
@@ -11012,16 +11015,16 @@
         <v>112</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>1</v>
@@ -11030,7 +11033,7 @@
         <v>270</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -11041,7 +11044,7 @@
         <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>101</v>
@@ -11053,25 +11056,25 @@
         <v>90</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>270</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11082,7 +11085,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>88</v>
@@ -11097,13 +11100,13 @@
         <v>254</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>1</v>
@@ -11112,7 +11115,7 @@
         <v>270</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="81" x14ac:dyDescent="0.3">
@@ -11123,7 +11126,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>101</v>
@@ -11135,25 +11138,25 @@
         <v>112</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>270</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11164,7 +11167,7 @@
         <v>49</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>101</v>
@@ -11176,16 +11179,16 @@
         <v>268</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>1</v>
@@ -11205,7 +11208,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>88</v>
@@ -11220,22 +11223,22 @@
         <v>254</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>270</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11243,10 +11246,10 @@
         <v>180</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>88</v>
@@ -11258,25 +11261,25 @@
         <v>112</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>270</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
@@ -11284,10 +11287,10 @@
         <v>180</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>88</v>
@@ -11299,16 +11302,16 @@
         <v>112</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>1</v>
@@ -11317,7 +11320,7 @@
         <v>51</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11325,10 +11328,10 @@
         <v>180</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>101</v>
@@ -11340,16 +11343,16 @@
         <v>112</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>1</v>
@@ -11358,7 +11361,7 @@
         <v>270</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="54" x14ac:dyDescent="0.3">
@@ -11366,10 +11369,10 @@
         <v>180</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>88</v>
@@ -11381,25 +11384,25 @@
         <v>112</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>1</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="54" x14ac:dyDescent="0.3">
@@ -11407,10 +11410,10 @@
         <v>180</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>88</v>
@@ -11422,16 +11425,16 @@
         <v>112</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>1</v>
@@ -11440,7 +11443,7 @@
         <v>270</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -11448,10 +11451,10 @@
         <v>180</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>88</v>
@@ -11463,25 +11466,25 @@
         <v>112</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>270</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -11489,10 +11492,10 @@
         <v>180</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>88</v>
@@ -11504,16 +11507,16 @@
         <v>112</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>1</v>
@@ -11530,10 +11533,10 @@
         <v>180</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>101</v>
@@ -11545,16 +11548,16 @@
         <v>112</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>1</v>
@@ -11563,7 +11566,7 @@
         <v>270</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="54" x14ac:dyDescent="0.3">
@@ -11571,10 +11574,10 @@
         <v>180</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>88</v>
@@ -11586,25 +11589,25 @@
         <v>268</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>1</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11612,10 +11615,10 @@
         <v>180</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>88</v>
@@ -11627,25 +11630,25 @@
         <v>112</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L31" s="9" t="s">
         <v>270</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11653,10 +11656,10 @@
         <v>180</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>88</v>
@@ -11668,16 +11671,16 @@
         <v>111</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>1</v>
@@ -11686,7 +11689,7 @@
         <v>270</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -11694,10 +11697,10 @@
         <v>180</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>88</v>
@@ -11706,28 +11709,28 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>254</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>1</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11735,10 +11738,10 @@
         <v>180</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>101</v>
@@ -11750,25 +11753,25 @@
         <v>268</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>1</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -11776,10 +11779,10 @@
         <v>180</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>88</v>
@@ -11791,25 +11794,25 @@
         <v>268</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>270</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -11817,7 +11820,7 @@
         <v>275</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>276</v>
@@ -11835,13 +11838,13 @@
         <v>278</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>1</v>
@@ -11858,7 +11861,7 @@
         <v>275</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>281</v>
@@ -11876,13 +11879,13 @@
         <v>278</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>1</v>
@@ -11902,7 +11905,7 @@
         <v>285</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>1</v>
@@ -11917,22 +11920,22 @@
         <v>278</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>1</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>233</v>
+        <v>302</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -11943,7 +11946,7 @@
         <v>285</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>1</v>
@@ -11958,13 +11961,13 @@
         <v>278</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>1</v>
@@ -11973,7 +11976,7 @@
         <v>51</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -11984,7 +11987,7 @@
         <v>285</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1</v>
@@ -11996,16 +11999,16 @@
         <v>112</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>1</v>
@@ -12014,7 +12017,7 @@
         <v>51</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -12025,7 +12028,7 @@
         <v>285</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>1</v>
@@ -12037,16 +12040,16 @@
         <v>112</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>1</v>
@@ -12055,7 +12058,7 @@
         <v>51</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -12066,7 +12069,7 @@
         <v>285</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>1</v>
@@ -12081,22 +12084,22 @@
         <v>278</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>1</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12107,7 +12110,7 @@
         <v>285</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>1</v>
@@ -12122,22 +12125,22 @@
         <v>278</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>1</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
@@ -12148,7 +12151,7 @@
         <v>285</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>1</v>
@@ -12163,22 +12166,22 @@
         <v>278</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>1</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -12189,7 +12192,7 @@
         <v>285</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>101</v>
@@ -12204,13 +12207,13 @@
         <v>278</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>1</v>
@@ -12219,39 +12222,39 @@
         <v>270</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>1</v>
@@ -12265,34 +12268,34 @@
     </row>
     <row r="47" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>1</v>
@@ -12306,34 +12309,34 @@
     </row>
     <row r="48" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>1</v>
@@ -12347,13 +12350,13 @@
     </row>
     <row r="49" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>88</v>
@@ -12365,16 +12368,16 @@
         <v>268</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>1</v>
@@ -12383,18 +12386,18 @@
         <v>270</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>88</v>
@@ -12406,16 +12409,16 @@
         <v>268</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K50" s="7" t="s">
         <v>1</v>
@@ -12424,18 +12427,18 @@
         <v>270</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>88</v>
@@ -12447,16 +12450,16 @@
         <v>268</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>1</v>
@@ -12465,18 +12468,18 @@
         <v>270</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>88</v>
@@ -12488,16 +12491,16 @@
         <v>268</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K52" s="7" t="s">
         <v>1</v>
@@ -12506,18 +12509,18 @@
         <v>270</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>88</v>
@@ -12529,36 +12532,36 @@
         <v>268</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>270</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>88</v>
@@ -12570,36 +12573,36 @@
         <v>268</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>270</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>88</v>
@@ -12611,19 +12614,19 @@
         <v>268</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>270</v>
@@ -12633,14 +12636,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55" xr:uid="{B8F40C8A-9C5E-4034-9FCD-0116881D43A8}"/>
+  <autoFilter ref="A1:M55" xr:uid="{02C7351B-B3DF-49E7-9CE5-F710284C9119}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B404320-EE8B-4D85-A3FA-DCE3C72891AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1CC521-C65D-42C8-9969-783914C091AA}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12658,201 +12661,201 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>140</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>128</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>112</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{6B404320-EE8B-4D85-A3FA-DCE3C72891AD}"/>
+  <autoFilter ref="A1:O4" xr:uid="{0F1CC521-C65D-42C8-9969-783914C091AA}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99363E69-A540-4253-89E9-03FC7491E062}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1B853B-9B38-4131-A985-D4F1B69B829D}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12943,10 +12946,10 @@
         <v>46</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -12985,7 +12988,7 @@
         <v>49</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>1</v>
@@ -13002,10 +13005,10 @@
         <v>69</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -13047,7 +13050,7 @@
         <v>49</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>1</v>
@@ -13067,7 +13070,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
@@ -13106,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>1</v>
@@ -13118,7 +13121,7 @@
         <v>51</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13126,10 +13129,10 @@
         <v>52</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>1</v>
@@ -13168,10 +13171,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="R5" s="13" t="s">
         <v>1</v>
@@ -13180,7 +13183,7 @@
         <v>51</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -13191,7 +13194,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1</v>
@@ -13230,10 +13233,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R6" s="13" t="s">
         <v>1</v>
@@ -13250,10 +13253,10 @@
         <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>1</v>
@@ -13292,10 +13295,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R7" s="11" t="s">
         <v>1</v>
@@ -13304,7 +13307,7 @@
         <v>51</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13312,10 +13315,10 @@
         <v>69</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>1</v>
@@ -13354,10 +13357,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="R8" s="11" t="s">
         <v>1</v>
@@ -13366,7 +13369,7 @@
         <v>51</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -13377,7 +13380,7 @@
         <v>70</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>1</v>
@@ -13419,7 +13422,7 @@
         <v>76</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="R9" s="11" t="s">
         <v>1</v>
@@ -13436,19 +13439,19 @@
         <v>180</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>101</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>139</v>
@@ -13460,37 +13463,37 @@
         <v>120</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S10" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13498,19 +13501,19 @@
         <v>180</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>111</v>
@@ -13519,13 +13522,13 @@
         <v>112</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L11" s="14" t="s">
         <v>1</v>
@@ -13537,22 +13540,22 @@
         <v>1</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>51</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13560,10 +13563,10 @@
         <v>180</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>1</v>
@@ -13572,7 +13575,7 @@
         <v>88</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>127</v>
@@ -13584,28 +13587,28 @@
         <v>161</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>134</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="R12" s="13" t="s">
         <v>1</v>
@@ -13614,7 +13617,7 @@
         <v>270</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13622,10 +13625,10 @@
         <v>180</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>1</v>
@@ -13634,13 +13637,13 @@
         <v>88</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>111</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>94</v>
@@ -13667,7 +13670,7 @@
         <v>218</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="R13" s="13" t="s">
         <v>1</v>
@@ -13676,7 +13679,7 @@
         <v>270</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
@@ -13684,10 +13687,10 @@
         <v>180</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -13696,7 +13699,7 @@
         <v>88</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>89</v>
@@ -13726,10 +13729,10 @@
         <v>94</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -13746,10 +13749,10 @@
         <v>180</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -13758,7 +13761,7 @@
         <v>88</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>111</v>
@@ -13788,10 +13791,10 @@
         <v>94</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -13800,7 +13803,7 @@
         <v>270</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13808,10 +13811,10 @@
         <v>180</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -13820,16 +13823,16 @@
         <v>88</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>1</v>
@@ -13847,22 +13850,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P16" s="13" t="s">
         <v>218</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="S16" s="13" t="s">
         <v>270</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13870,10 +13873,10 @@
         <v>180</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -13882,7 +13885,7 @@
         <v>101</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>89</v>
@@ -13912,19 +13915,19 @@
         <v>94</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>270</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -13932,10 +13935,10 @@
         <v>180</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>1</v>
@@ -13944,7 +13947,7 @@
         <v>101</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>111</v>
@@ -13977,7 +13980,7 @@
         <v>194</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="R18" s="13" t="s">
         <v>1</v>
@@ -13994,10 +13997,10 @@
         <v>180</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>1</v>
@@ -14006,7 +14009,7 @@
         <v>101</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>94</v>
@@ -14039,7 +14042,7 @@
         <v>134</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="R19" s="13" t="s">
         <v>1</v>
@@ -14056,10 +14059,10 @@
         <v>180</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>1</v>
@@ -14068,7 +14071,7 @@
         <v>88</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>89</v>
@@ -14101,7 +14104,7 @@
         <v>194</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="R20" s="13" t="s">
         <v>1</v>
@@ -14118,10 +14121,10 @@
         <v>85</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
@@ -14130,7 +14133,7 @@
         <v>88</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>111</v>
@@ -14139,13 +14142,13 @@
         <v>90</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L21" s="12" t="s">
         <v>1</v>
@@ -14157,22 +14160,22 @@
         <v>1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>143</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S21" s="11" t="s">
         <v>270</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -14180,10 +14183,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>1</v>
@@ -14204,13 +14207,13 @@
         <v>113</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>1</v>
@@ -14219,13 +14222,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>1</v>
@@ -14242,10 +14245,10 @@
         <v>85</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>1</v>
@@ -14287,7 +14290,7 @@
         <v>134</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="R23" s="11" t="s">
         <v>1</v>
@@ -14296,7 +14299,7 @@
         <v>270</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -14304,10 +14307,10 @@
         <v>85</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>1</v>
@@ -14316,7 +14319,7 @@
         <v>101</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>89</v>
@@ -14349,10 +14352,10 @@
         <v>143</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>270</v>
@@ -14366,10 +14369,10 @@
         <v>85</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>1</v>
@@ -14378,7 +14381,7 @@
         <v>101</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>111</v>
@@ -14411,10 +14414,10 @@
         <v>218</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>270</v>
@@ -14428,10 +14431,10 @@
         <v>85</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>1</v>
@@ -14440,7 +14443,7 @@
         <v>88</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>111</v>
@@ -14473,10 +14476,10 @@
         <v>134</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>270</v>
@@ -14490,10 +14493,10 @@
         <v>85</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>1</v>
@@ -14535,7 +14538,7 @@
         <v>134</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="R27" s="11" t="s">
         <v>1</v>
@@ -14552,10 +14555,10 @@
         <v>85</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>1</v>
@@ -14564,7 +14567,7 @@
         <v>88</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>89</v>
@@ -14597,7 +14600,7 @@
         <v>134</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>1</v>
@@ -14614,10 +14617,10 @@
         <v>85</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>1</v>
@@ -14659,7 +14662,7 @@
         <v>76</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="R29" s="11" t="s">
         <v>1</v>
@@ -14676,10 +14679,10 @@
         <v>85</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>1</v>
@@ -14718,10 +14721,10 @@
         <v>94</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="R30" s="11" t="s">
         <v>1</v>
@@ -14738,10 +14741,10 @@
         <v>85</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>1</v>
@@ -14780,10 +14783,10 @@
         <v>94</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="R31" s="11" t="s">
         <v>1</v>
@@ -14792,7 +14795,7 @@
         <v>270</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -14800,7 +14803,7 @@
         <v>275</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>276</v>
@@ -14845,7 +14848,7 @@
         <v>134</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R32" s="13" t="s">
         <v>1</v>
@@ -14862,7 +14865,7 @@
         <v>275</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>281</v>
@@ -14907,7 +14910,7 @@
         <v>134</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="R33" s="13" t="s">
         <v>1</v>
@@ -14924,10 +14927,10 @@
         <v>275</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -14969,7 +14972,7 @@
         <v>134</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="R34" s="13" t="s">
         <v>1</v>
@@ -14978,7 +14981,7 @@
         <v>270</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
@@ -14986,10 +14989,10 @@
         <v>275</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>1</v>
@@ -15031,7 +15034,7 @@
         <v>134</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="R35" s="13" t="s">
         <v>1</v>
@@ -15040,7 +15043,7 @@
         <v>270</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
@@ -15048,10 +15051,10 @@
         <v>275</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>1</v>
@@ -15093,7 +15096,7 @@
         <v>134</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="R36" s="13" t="s">
         <v>1</v>
@@ -15110,10 +15113,10 @@
         <v>275</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>1</v>
@@ -15155,7 +15158,7 @@
         <v>134</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="R37" s="13" t="s">
         <v>1</v>
@@ -15164,7 +15167,7 @@
         <v>270</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
@@ -15172,10 +15175,10 @@
         <v>275</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -15217,7 +15220,7 @@
         <v>134</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="R38" s="13" t="s">
         <v>1</v>
@@ -15237,7 +15240,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>1</v>
@@ -15279,7 +15282,7 @@
         <v>134</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R39" s="13" t="s">
         <v>1</v>
@@ -15296,10 +15299,10 @@
         <v>275</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>1</v>
@@ -15341,7 +15344,7 @@
         <v>134</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="R40" s="13" t="s">
         <v>1</v>
@@ -15358,10 +15361,10 @@
         <v>275</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -15403,7 +15406,7 @@
         <v>134</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="R41" s="13" t="s">
         <v>1</v>
@@ -15423,7 +15426,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -15465,7 +15468,7 @@
         <v>278</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="R42" s="13" t="s">
         <v>1</v>
@@ -15485,7 +15488,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>1</v>
@@ -15527,7 +15530,7 @@
         <v>134</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="R43" s="13" t="s">
         <v>1</v>
@@ -15541,13 +15544,13 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>1</v>
@@ -15556,7 +15559,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>1</v>
@@ -15586,10 +15589,10 @@
         <v>1</v>
       </c>
       <c r="P44" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="R44" s="11" t="s">
         <v>1</v>
@@ -15603,13 +15606,13 @@
     </row>
     <row r="45" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>1</v>
@@ -15618,7 +15621,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>1</v>
@@ -15648,10 +15651,10 @@
         <v>1</v>
       </c>
       <c r="P45" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="R45" s="11" t="s">
         <v>1</v>
@@ -15665,13 +15668,13 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>1</v>
@@ -15680,7 +15683,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>1</v>
@@ -15710,10 +15713,10 @@
         <v>1</v>
       </c>
       <c r="P46" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>1</v>
@@ -15726,14 +15729,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{99363E69-A540-4253-89E9-03FC7491E062}"/>
+  <autoFilter ref="A1:T46" xr:uid="{FC1B853B-9B38-4131-A985-D4F1B69B829D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98632793-6FE6-41CB-819F-8CF03B3867CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D26059-DE16-4240-BF15-0AEB102B16B8}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15748,7 +15751,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>28</v>
@@ -15757,13 +15760,13 @@
         <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
@@ -15771,232 +15774,232 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -16007,19 +16010,19 @@
         <v>66</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -16027,151 +16030,151 @@
         <v>53</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -16180,18 +16183,18 @@
         <v>49</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19" xr:uid="{98632793-6FE6-41CB-819F-8CF03B3867CF}"/>
+  <autoFilter ref="A1:G19" xr:uid="{77D26059-DE16-4240-BF15-0AEB102B16B8}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BEE84F7-7C8E-43FD-86BE-603A75DB675C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323CC540-6ACE-4328-A0E0-400BB03B4AC1}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16205,19 +16208,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>42</v>
@@ -16228,22 +16231,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>51</v>
@@ -16251,22 +16254,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>51</v>
@@ -16274,22 +16277,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>51</v>
@@ -16297,22 +16300,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
@@ -16320,22 +16323,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>51</v>
@@ -16343,22 +16346,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>51</v>
@@ -16366,22 +16369,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>51</v>
@@ -16389,22 +16392,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>51</v>
@@ -16412,22 +16415,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>51</v>
@@ -16435,22 +16438,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>51</v>
@@ -16458,22 +16461,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>51</v>
@@ -16481,22 +16484,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>51</v>
@@ -16504,22 +16507,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>51</v>
@@ -16527,22 +16530,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>51</v>
@@ -16550,22 +16553,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>51</v>
@@ -16573,45 +16576,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>51</v>
@@ -16619,22 +16622,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>51</v>
@@ -16642,22 +16645,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>51</v>
@@ -16665,22 +16668,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>51</v>
@@ -16688,22 +16691,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>51</v>
@@ -16711,22 +16714,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>51</v>
@@ -16734,22 +16737,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>51</v>
@@ -16757,22 +16760,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>51</v>
@@ -16780,22 +16783,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>51</v>
@@ -16803,22 +16806,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>51</v>
@@ -16826,183 +16829,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E30" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>940</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>938</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>939</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>51</v>
@@ -17010,68 +17013,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>51</v>
@@ -17079,22 +17082,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>51</v>
@@ -17102,22 +17105,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>51</v>
@@ -17125,22 +17128,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>51</v>
@@ -17148,22 +17151,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>51</v>
@@ -17171,22 +17174,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>51</v>
@@ -17194,45 +17197,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>51</v>
@@ -17240,22 +17243,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>51</v>
@@ -17263,22 +17266,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>51</v>
@@ -17286,22 +17289,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>51</v>
@@ -17309,22 +17312,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>51</v>
@@ -17332,22 +17335,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>51</v>
@@ -17355,22 +17358,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>51</v>
@@ -17378,22 +17381,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>111</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>51</v>
@@ -17401,22 +17404,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>51</v>
@@ -17424,22 +17427,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>51</v>
@@ -17447,22 +17450,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>51</v>
@@ -17470,68 +17473,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>999</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>998</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>999</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>51</v>
@@ -17539,22 +17542,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>51</v>
@@ -17562,22 +17565,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>51</v>
@@ -17585,22 +17588,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>51</v>
@@ -17608,22 +17611,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>51</v>
@@ -17631,22 +17634,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>51</v>
@@ -17654,36 +17657,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{1BEE84F7-7C8E-43FD-86BE-603A75DB675C}"/>
+  <autoFilter ref="A1:G64" xr:uid="{323CC540-6ACE-4328-A0E0-400BB03B4AC1}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8301973-DCEC-4C75-8CE5-572622654572}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A25595-4961-4EA5-9E22-9B1CB3A9366E}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17697,10 +17700,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>32</v>
@@ -17712,41 +17715,41 @@
         <v>180</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
@@ -17755,21 +17758,21 @@
         <v>113</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>49</v>
@@ -17781,18 +17784,18 @@
         <v>49</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>49</v>
@@ -17804,18 +17807,18 @@
         <v>49</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>89</v>
@@ -17824,21 +17827,21 @@
         <v>161</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>111</v>
@@ -17847,21 +17850,21 @@
         <v>113</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>49</v>
@@ -17873,21 +17876,21 @@
         <v>49</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{F8301973-DCEC-4C75-8CE5-572622654572}"/>
+  <autoFilter ref="A1:G8" xr:uid="{36A25595-4961-4EA5-9E22-9B1CB3A9366E}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4CB6F5-9EE4-4BFF-8213-67894E52FC87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8037269-6072-4E29-867D-E04761207944}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17897,19 +17900,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>45</v>
@@ -17917,66 +17920,66 @@
     </row>
     <row r="2" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>1056</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>1060</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1059</v>
-      </c>
       <c r="F4" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{0E4CB6F5-9EE4-4BFF-8213-67894E52FC87}"/>
+  <autoFilter ref="A1:F4" xr:uid="{C8037269-6072-4E29-867D-E04761207944}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
